--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1168 +510,1062 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B2" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J2" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M2" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O2" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E3" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B4" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E4" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B5" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B6" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B7" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L7" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P7" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B8" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B9" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K9" t="n">
         <v>2.9701</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M9" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B10" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O10" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P10" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B11" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C11" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B12" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D12" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G12" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B13" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H13" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L13" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M13" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1825</v>
+        <v>3.2113</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8474</v>
+        <v>2.8634</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3276</v>
+        <v>2.3241</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9139</v>
+        <v>1.8971</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2074</v>
+        <v>2.2057</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7345</v>
+        <v>2.7544</v>
       </c>
       <c r="H14" t="n">
-        <v>2.829</v>
+        <v>2.85</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8305</v>
+        <v>2.8543</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8734</v>
+        <v>2.9022</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9034</v>
+        <v>2.9366</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9248</v>
+        <v>2.962</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9401</v>
+        <v>2.981</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9682</v>
+        <v>3.0262</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9638</v>
+        <v>3.0388</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9573</v>
+        <v>3.0508</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9686</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1398</v>
+        <v>3.1825</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8351</v>
+        <v>2.8474</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3608</v>
+        <v>2.3276</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9746</v>
+        <v>1.9139</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2256</v>
+        <v>2.2074</v>
       </c>
       <c r="G15" t="n">
-        <v>2.697</v>
+        <v>2.7345</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8135</v>
+        <v>2.829</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8272</v>
+        <v>2.8305</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8702</v>
+        <v>2.8734</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9004</v>
+        <v>2.9034</v>
       </c>
       <c r="L15" t="n">
-        <v>2.922</v>
+        <v>2.9248</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9374</v>
+        <v>2.9401</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9665</v>
+        <v>2.9682</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9633</v>
+        <v>2.9638</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9581</v>
+        <v>2.9573</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9709</v>
+        <v>2.9686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1181</v>
+        <v>3.1398</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8427</v>
+        <v>2.8351</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4094</v>
+        <v>2.3608</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0329</v>
+        <v>1.9746</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2134</v>
+        <v>2.2256</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6093</v>
+        <v>2.697</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7774</v>
+        <v>2.8135</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8152</v>
+        <v>2.8272</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8613</v>
+        <v>2.8702</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8938</v>
+        <v>2.9004</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9172</v>
+        <v>2.922</v>
       </c>
       <c r="M16" t="n">
-        <v>2.934</v>
+        <v>2.9374</v>
       </c>
       <c r="N16" t="n">
-        <v>2.967</v>
+        <v>2.9665</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9653</v>
+        <v>2.9633</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9605</v>
+        <v>2.9581</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9732</v>
+        <v>2.9709</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1106</v>
+        <v>3.1181</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8385</v>
+        <v>2.8427</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4101</v>
+        <v>2.4094</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0366</v>
+        <v>2.0329</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2125</v>
+        <v>2.2134</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6025</v>
+        <v>2.6093</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7739</v>
+        <v>2.7774</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8133</v>
+        <v>2.8152</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8597</v>
+        <v>2.8613</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8924</v>
+        <v>2.8938</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9158</v>
+        <v>2.9172</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9329</v>
+        <v>2.934</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9665</v>
+        <v>2.967</v>
       </c>
       <c r="O17" t="n">
         <v>2.9653</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9611</v>
+        <v>2.9605</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9745</v>
+        <v>2.9732</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1006</v>
+        <v>3.1106</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8313</v>
+        <v>2.8385</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4071</v>
+        <v>2.4101</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0365</v>
+        <v>2.0366</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2088</v>
+        <v>2.2125</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5943</v>
+        <v>2.6025</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7691</v>
+        <v>2.7739</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8105</v>
+        <v>2.8133</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8573</v>
+        <v>2.8597</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8903</v>
+        <v>2.8924</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9141</v>
+        <v>2.9158</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9313</v>
+        <v>2.9329</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9658</v>
+        <v>2.9665</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9652</v>
+        <v>2.9653</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9616</v>
+        <v>2.9611</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9756</v>
+        <v>2.9745</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B19" t="n">
-        <v>3.0828</v>
+        <v>3.1006</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8158</v>
+        <v>2.8313</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3953</v>
+        <v>2.4071</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0285</v>
+        <v>2.0365</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2005</v>
+        <v>2.2088</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5848</v>
+        <v>2.5943</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7613</v>
+        <v>2.7691</v>
       </c>
       <c r="I19" t="n">
-        <v>2.803</v>
+        <v>2.8105</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8495</v>
+        <v>2.8573</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8822</v>
+        <v>2.8903</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9055</v>
+        <v>2.9141</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9222</v>
+        <v>2.9313</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9534</v>
+        <v>2.9658</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9487</v>
+        <v>2.9652</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9403</v>
+        <v>2.9616</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9486</v>
+        <v>2.9756</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B20" t="n">
-        <v>3.0643</v>
+        <v>3.0828</v>
       </c>
       <c r="C20" t="n">
-        <v>2.7967</v>
+        <v>2.8158</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3757</v>
+        <v>2.3953</v>
       </c>
       <c r="E20" t="n">
-        <v>2.01</v>
+        <v>2.0285</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1854</v>
+        <v>2.2005</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5725</v>
+        <v>2.5848</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7435</v>
+        <v>2.7613</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7822</v>
+        <v>2.803</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8274</v>
+        <v>2.8495</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8592</v>
+        <v>2.8822</v>
       </c>
       <c r="L20" t="n">
-        <v>2.8819</v>
+        <v>2.9055</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8982</v>
+        <v>2.9222</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9288</v>
+        <v>2.9534</v>
       </c>
       <c r="O20" t="n">
-        <v>2.925</v>
+        <v>2.9487</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9182</v>
+        <v>2.9403</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9283</v>
+        <v>2.9486</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B21" t="n">
-        <v>2.953</v>
+        <v>3.0643</v>
       </c>
       <c r="C21" t="n">
-        <v>2.7129</v>
+        <v>2.7967</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3366</v>
+        <v>2.3757</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0171</v>
+        <v>2.01</v>
       </c>
       <c r="F21" t="n">
-        <v>2.19</v>
+        <v>2.1854</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5595</v>
+        <v>2.5725</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7362</v>
+        <v>2.7435</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7798</v>
+        <v>2.7822</v>
       </c>
       <c r="J21" t="n">
-        <v>2.826</v>
+        <v>2.8274</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8584</v>
+        <v>2.8592</v>
       </c>
       <c r="L21" t="n">
-        <v>2.8815</v>
+        <v>2.8819</v>
       </c>
       <c r="M21" t="n">
         <v>2.8982</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9296</v>
+        <v>2.9288</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9259</v>
+        <v>2.925</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9187</v>
+        <v>2.9182</v>
       </c>
       <c r="Q21" t="n">
         <v>2.9283</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B22" t="n">
-        <v>2.8989</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.6729</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.3192</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.0209</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.1881</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.5451</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.7288</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.7767</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.8237</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.8567</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.8803</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.8974</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.9298</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.9264</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.9193</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.9288</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B23" t="n">
-        <v>2.8018</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.5969</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.2777</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.0162</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.1836</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.5294</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.7188</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.7713</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.8196</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.8535</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.8779</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.8955</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.9296</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.9269</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.9202</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.9299</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,1211 +1672,1101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C2" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D2" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E2" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F2" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G2" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H2" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I2" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J2" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K2" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L2" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M2" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N2" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O2" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P2" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q2" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C3" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D3" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E3" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F3" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G3" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H3" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I3" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J3" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K3" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L3" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M3" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N3" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O3" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P3" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q3" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C4" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D4" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E4" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F4" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G4" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H4" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I4" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J4" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K4" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L4" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M4" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N4" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O4" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P4" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q4" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C5" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D5" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E5" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F5" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G5" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H5" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I5" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J5" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K5" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L5" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M5" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N5" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O5" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P5" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q5" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C6" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D6" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E6" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F6" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G6" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H6" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I6" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J6" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K6" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L6" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M6" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N6" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O6" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P6" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q6" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C7" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D7" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E7" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F7" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G7" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H7" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I7" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J7" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K7" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L7" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M7" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N7" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O7" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P7" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q7" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C8" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D8" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E8" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F8" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G8" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H8" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I8" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J8" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K8" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L8" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M8" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N8" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O8" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P8" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q8" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C9" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D9" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E9" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F9" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G9" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H9" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I9" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J9" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K9" t="n">
         <v>29701</v>
       </c>
       <c r="L9" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M9" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N9" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O9" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P9" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q9" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C10" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D10" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E10" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F10" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G10" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H10" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I10" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J10" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K10" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L10" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M10" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N10" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O10" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P10" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q10" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C11" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F11" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H11" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I11" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K11" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L11" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M11" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N11" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O11" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P11" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q11" t="n">
         <v>30659</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E11" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F11" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G11" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H11" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I11" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J11" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K11" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L11" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M11" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N11" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O11" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P11" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C12" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D12" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E12" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F12" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G12" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H12" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I12" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J12" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K12" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L12" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M12" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N12" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O12" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P12" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q12" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C13" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D13" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E13" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F13" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G13" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H13" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I13" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J13" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K13" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L13" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M13" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N13" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O13" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P13" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q13" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31825</v>
+        <v>32113</v>
       </c>
       <c r="C14" t="n">
-        <v>28474</v>
+        <v>28634</v>
       </c>
       <c r="D14" t="n">
-        <v>23276</v>
+        <v>23241</v>
       </c>
       <c r="E14" t="n">
-        <v>19139</v>
+        <v>18971</v>
       </c>
       <c r="F14" t="n">
-        <v>22074</v>
+        <v>22057</v>
       </c>
       <c r="G14" t="n">
-        <v>27345</v>
+        <v>27544</v>
       </c>
       <c r="H14" t="n">
-        <v>28290</v>
+        <v>285</v>
       </c>
       <c r="I14" t="n">
-        <v>28305</v>
+        <v>28543</v>
       </c>
       <c r="J14" t="n">
-        <v>28734</v>
+        <v>29022</v>
       </c>
       <c r="K14" t="n">
-        <v>29034</v>
+        <v>29366</v>
       </c>
       <c r="L14" t="n">
-        <v>29248</v>
+        <v>29620</v>
       </c>
       <c r="M14" t="n">
-        <v>29401</v>
+        <v>29810</v>
       </c>
       <c r="N14" t="n">
-        <v>29682</v>
+        <v>30262</v>
       </c>
       <c r="O14" t="n">
-        <v>29638</v>
+        <v>30388</v>
       </c>
       <c r="P14" t="n">
-        <v>29573</v>
+        <v>30508</v>
       </c>
       <c r="Q14" t="n">
-        <v>29686</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31398</v>
+        <v>31825</v>
       </c>
       <c r="C15" t="n">
-        <v>28351</v>
+        <v>28474</v>
       </c>
       <c r="D15" t="n">
-        <v>23608</v>
+        <v>23276</v>
       </c>
       <c r="E15" t="n">
-        <v>19746</v>
+        <v>19139</v>
       </c>
       <c r="F15" t="n">
-        <v>22256</v>
+        <v>22074</v>
       </c>
       <c r="G15" t="n">
-        <v>26970</v>
+        <v>27345</v>
       </c>
       <c r="H15" t="n">
-        <v>28135</v>
+        <v>28290</v>
       </c>
       <c r="I15" t="n">
-        <v>28272</v>
+        <v>28305</v>
       </c>
       <c r="J15" t="n">
-        <v>28702</v>
+        <v>28734</v>
       </c>
       <c r="K15" t="n">
-        <v>29004</v>
+        <v>29034</v>
       </c>
       <c r="L15" t="n">
-        <v>29220</v>
+        <v>29248</v>
       </c>
       <c r="M15" t="n">
-        <v>29374</v>
+        <v>29401</v>
       </c>
       <c r="N15" t="n">
-        <v>29665</v>
+        <v>29682</v>
       </c>
       <c r="O15" t="n">
-        <v>29633</v>
+        <v>29638</v>
       </c>
       <c r="P15" t="n">
-        <v>29581</v>
+        <v>29573</v>
       </c>
       <c r="Q15" t="n">
-        <v>29709</v>
+        <v>29686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31181</v>
+        <v>31398</v>
       </c>
       <c r="C16" t="n">
-        <v>28427</v>
+        <v>28351</v>
       </c>
       <c r="D16" t="n">
-        <v>24094</v>
+        <v>23608</v>
       </c>
       <c r="E16" t="n">
-        <v>20329</v>
+        <v>19746</v>
       </c>
       <c r="F16" t="n">
-        <v>22134</v>
+        <v>22256</v>
       </c>
       <c r="G16" t="n">
-        <v>26093</v>
+        <v>26970</v>
       </c>
       <c r="H16" t="n">
-        <v>27774</v>
+        <v>28135</v>
       </c>
       <c r="I16" t="n">
-        <v>28152</v>
+        <v>28272</v>
       </c>
       <c r="J16" t="n">
-        <v>28613</v>
+        <v>28702</v>
       </c>
       <c r="K16" t="n">
-        <v>28938</v>
+        <v>29004</v>
       </c>
       <c r="L16" t="n">
-        <v>29172</v>
+        <v>29220</v>
       </c>
       <c r="M16" t="n">
-        <v>29340</v>
+        <v>29374</v>
       </c>
       <c r="N16" t="n">
-        <v>29670</v>
+        <v>29665</v>
       </c>
       <c r="O16" t="n">
-        <v>29653</v>
+        <v>29633</v>
       </c>
       <c r="P16" t="n">
-        <v>29605</v>
+        <v>29581</v>
       </c>
       <c r="Q16" t="n">
-        <v>29732</v>
+        <v>29709</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31106</v>
+        <v>31181</v>
       </c>
       <c r="C17" t="n">
-        <v>28385</v>
+        <v>28427</v>
       </c>
       <c r="D17" t="n">
-        <v>24101</v>
+        <v>24094</v>
       </c>
       <c r="E17" t="n">
-        <v>20366</v>
+        <v>20329</v>
       </c>
       <c r="F17" t="n">
-        <v>22125</v>
+        <v>22134</v>
       </c>
       <c r="G17" t="n">
-        <v>26025</v>
+        <v>26093</v>
       </c>
       <c r="H17" t="n">
-        <v>27739</v>
+        <v>27774</v>
       </c>
       <c r="I17" t="n">
-        <v>28133</v>
+        <v>28152</v>
       </c>
       <c r="J17" t="n">
-        <v>28597</v>
+        <v>28613</v>
       </c>
       <c r="K17" t="n">
-        <v>28924</v>
+        <v>28938</v>
       </c>
       <c r="L17" t="n">
-        <v>29158</v>
+        <v>29172</v>
       </c>
       <c r="M17" t="n">
-        <v>29329</v>
+        <v>29340</v>
       </c>
       <c r="N17" t="n">
-        <v>29665</v>
+        <v>29670</v>
       </c>
       <c r="O17" t="n">
         <v>29653</v>
       </c>
       <c r="P17" t="n">
-        <v>29611</v>
+        <v>29605</v>
       </c>
       <c r="Q17" t="n">
-        <v>29745</v>
+        <v>29732</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31006</v>
+        <v>31106</v>
       </c>
       <c r="C18" t="n">
-        <v>28313</v>
+        <v>28385</v>
       </c>
       <c r="D18" t="n">
-        <v>24071</v>
+        <v>24101</v>
       </c>
       <c r="E18" t="n">
-        <v>20365</v>
+        <v>20366</v>
       </c>
       <c r="F18" t="n">
-        <v>22088</v>
+        <v>22125</v>
       </c>
       <c r="G18" t="n">
-        <v>25943</v>
+        <v>26025</v>
       </c>
       <c r="H18" t="n">
-        <v>27691</v>
+        <v>27739</v>
       </c>
       <c r="I18" t="n">
-        <v>28105</v>
+        <v>28133</v>
       </c>
       <c r="J18" t="n">
-        <v>28573</v>
+        <v>28597</v>
       </c>
       <c r="K18" t="n">
-        <v>28903</v>
+        <v>28924</v>
       </c>
       <c r="L18" t="n">
-        <v>29141</v>
+        <v>29158</v>
       </c>
       <c r="M18" t="n">
-        <v>29313</v>
+        <v>29329</v>
       </c>
       <c r="N18" t="n">
-        <v>29658</v>
+        <v>29665</v>
       </c>
       <c r="O18" t="n">
-        <v>29652</v>
+        <v>29653</v>
       </c>
       <c r="P18" t="n">
-        <v>29616</v>
+        <v>29611</v>
       </c>
       <c r="Q18" t="n">
-        <v>29756</v>
+        <v>29745</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30828</v>
+        <v>31006</v>
       </c>
       <c r="C19" t="n">
-        <v>28158</v>
+        <v>28313</v>
       </c>
       <c r="D19" t="n">
-        <v>23953</v>
+        <v>24071</v>
       </c>
       <c r="E19" t="n">
-        <v>20285</v>
+        <v>20365</v>
       </c>
       <c r="F19" t="n">
-        <v>22005</v>
+        <v>22088</v>
       </c>
       <c r="G19" t="n">
-        <v>25848</v>
+        <v>25943</v>
       </c>
       <c r="H19" t="n">
-        <v>27613</v>
+        <v>27691</v>
       </c>
       <c r="I19" t="n">
-        <v>28030</v>
+        <v>28105</v>
       </c>
       <c r="J19" t="n">
-        <v>28495</v>
+        <v>28573</v>
       </c>
       <c r="K19" t="n">
-        <v>28822</v>
+        <v>28903</v>
       </c>
       <c r="L19" t="n">
-        <v>29055</v>
+        <v>29141</v>
       </c>
       <c r="M19" t="n">
-        <v>29222</v>
+        <v>29313</v>
       </c>
       <c r="N19" t="n">
-        <v>29534</v>
+        <v>29658</v>
       </c>
       <c r="O19" t="n">
-        <v>29487</v>
+        <v>29652</v>
       </c>
       <c r="P19" t="n">
-        <v>29403</v>
+        <v>29616</v>
       </c>
       <c r="Q19" t="n">
-        <v>29486</v>
+        <v>29756</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30643</v>
+        <v>30828</v>
       </c>
       <c r="C20" t="n">
-        <v>27967</v>
+        <v>28158</v>
       </c>
       <c r="D20" t="n">
-        <v>23757</v>
+        <v>23953</v>
       </c>
       <c r="E20" t="n">
-        <v>201</v>
+        <v>20285</v>
       </c>
       <c r="F20" t="n">
-        <v>21854</v>
+        <v>22005</v>
       </c>
       <c r="G20" t="n">
-        <v>25725</v>
+        <v>25848</v>
       </c>
       <c r="H20" t="n">
-        <v>27435</v>
+        <v>27613</v>
       </c>
       <c r="I20" t="n">
-        <v>27822</v>
+        <v>28030</v>
       </c>
       <c r="J20" t="n">
-        <v>28274</v>
+        <v>28495</v>
       </c>
       <c r="K20" t="n">
-        <v>28592</v>
+        <v>28822</v>
       </c>
       <c r="L20" t="n">
-        <v>28819</v>
+        <v>29055</v>
       </c>
       <c r="M20" t="n">
-        <v>28982</v>
+        <v>29222</v>
       </c>
       <c r="N20" t="n">
-        <v>29288</v>
+        <v>29534</v>
       </c>
       <c r="O20" t="n">
-        <v>29250</v>
+        <v>29487</v>
       </c>
       <c r="P20" t="n">
-        <v>29182</v>
+        <v>29403</v>
       </c>
       <c r="Q20" t="n">
-        <v>29283</v>
+        <v>29486</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29530</v>
+        <v>30643</v>
       </c>
       <c r="C21" t="n">
-        <v>27129</v>
+        <v>27967</v>
       </c>
       <c r="D21" t="n">
-        <v>23366</v>
+        <v>23757</v>
       </c>
       <c r="E21" t="n">
-        <v>20171</v>
+        <v>201</v>
       </c>
       <c r="F21" t="n">
-        <v>219</v>
+        <v>21854</v>
       </c>
       <c r="G21" t="n">
-        <v>25595</v>
+        <v>25725</v>
       </c>
       <c r="H21" t="n">
-        <v>27362</v>
+        <v>27435</v>
       </c>
       <c r="I21" t="n">
-        <v>27798</v>
+        <v>27822</v>
       </c>
       <c r="J21" t="n">
-        <v>28260</v>
+        <v>28274</v>
       </c>
       <c r="K21" t="n">
-        <v>28584</v>
+        <v>28592</v>
       </c>
       <c r="L21" t="n">
-        <v>28815</v>
+        <v>28819</v>
       </c>
       <c r="M21" t="n">
         <v>28982</v>
       </c>
       <c r="N21" t="n">
-        <v>29296</v>
+        <v>29288</v>
       </c>
       <c r="O21" t="n">
-        <v>29259</v>
+        <v>29250</v>
       </c>
       <c r="P21" t="n">
-        <v>29187</v>
+        <v>29182</v>
       </c>
       <c r="Q21" t="n">
         <v>29283</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>28989</v>
-      </c>
-      <c r="C22" t="n">
-        <v>26729</v>
-      </c>
-      <c r="D22" t="n">
-        <v>23192</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20209</v>
-      </c>
-      <c r="F22" t="n">
-        <v>21881</v>
-      </c>
-      <c r="G22" t="n">
-        <v>25451</v>
-      </c>
-      <c r="H22" t="n">
-        <v>27288</v>
-      </c>
-      <c r="I22" t="n">
-        <v>27767</v>
-      </c>
-      <c r="J22" t="n">
-        <v>28237</v>
-      </c>
-      <c r="K22" t="n">
-        <v>28567</v>
-      </c>
-      <c r="L22" t="n">
-        <v>28803</v>
-      </c>
-      <c r="M22" t="n">
-        <v>28974</v>
-      </c>
-      <c r="N22" t="n">
-        <v>29298</v>
-      </c>
-      <c r="O22" t="n">
-        <v>29264</v>
-      </c>
-      <c r="P22" t="n">
-        <v>29193</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>29288</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>28018</v>
-      </c>
-      <c r="C23" t="n">
-        <v>25969</v>
-      </c>
-      <c r="D23" t="n">
-        <v>22777</v>
-      </c>
-      <c r="E23" t="n">
-        <v>20162</v>
-      </c>
-      <c r="F23" t="n">
-        <v>21836</v>
-      </c>
-      <c r="G23" t="n">
-        <v>25294</v>
-      </c>
-      <c r="H23" t="n">
-        <v>27188</v>
-      </c>
-      <c r="I23" t="n">
-        <v>27713</v>
-      </c>
-      <c r="J23" t="n">
-        <v>28196</v>
-      </c>
-      <c r="K23" t="n">
-        <v>28535</v>
-      </c>
-      <c r="L23" t="n">
-        <v>28779</v>
-      </c>
-      <c r="M23" t="n">
-        <v>28955</v>
-      </c>
-      <c r="N23" t="n">
-        <v>29296</v>
-      </c>
-      <c r="O23" t="n">
-        <v>29269</v>
-      </c>
-      <c r="P23" t="n">
-        <v>29202</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>29299</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1062 +510,1062 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J3" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M3" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O3" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E4" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B5" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E5" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B6" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B7" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B8" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L8" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P8" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B9" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B10" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K10" t="n">
         <v>2.9701</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M10" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B11" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O11" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P11" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B12" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C12" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B13" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G13" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B14" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H14" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L14" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M14" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1825</v>
+        <v>3.2113</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8474</v>
+        <v>2.8634</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3276</v>
+        <v>2.3241</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9139</v>
+        <v>1.8971</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2074</v>
+        <v>2.2057</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7345</v>
+        <v>2.7544</v>
       </c>
       <c r="H15" t="n">
-        <v>2.829</v>
+        <v>2.85</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8305</v>
+        <v>2.8543</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8734</v>
+        <v>2.9022</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9034</v>
+        <v>2.9366</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9248</v>
+        <v>2.962</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9401</v>
+        <v>2.981</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9682</v>
+        <v>3.0262</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9638</v>
+        <v>3.0388</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9573</v>
+        <v>3.0508</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9686</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1398</v>
+        <v>3.1825</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8351</v>
+        <v>2.8474</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3608</v>
+        <v>2.3276</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9746</v>
+        <v>1.9139</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2256</v>
+        <v>2.2074</v>
       </c>
       <c r="G16" t="n">
-        <v>2.697</v>
+        <v>2.7345</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8135</v>
+        <v>2.829</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8272</v>
+        <v>2.8305</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8702</v>
+        <v>2.8734</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9004</v>
+        <v>2.9034</v>
       </c>
       <c r="L16" t="n">
-        <v>2.922</v>
+        <v>2.9248</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9374</v>
+        <v>2.9401</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9665</v>
+        <v>2.9682</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9633</v>
+        <v>2.9638</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9581</v>
+        <v>2.9573</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9709</v>
+        <v>2.9686</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1181</v>
+        <v>3.1398</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8427</v>
+        <v>2.8351</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4094</v>
+        <v>2.3608</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0329</v>
+        <v>1.9746</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2134</v>
+        <v>2.2256</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6093</v>
+        <v>2.697</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7774</v>
+        <v>2.8135</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8152</v>
+        <v>2.8272</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8613</v>
+        <v>2.8702</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8938</v>
+        <v>2.9004</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9172</v>
+        <v>2.922</v>
       </c>
       <c r="M17" t="n">
-        <v>2.934</v>
+        <v>2.9374</v>
       </c>
       <c r="N17" t="n">
-        <v>2.967</v>
+        <v>2.9665</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9653</v>
+        <v>2.9633</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9605</v>
+        <v>2.9581</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9732</v>
+        <v>2.9709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1106</v>
+        <v>3.1181</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8385</v>
+        <v>2.8427</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4101</v>
+        <v>2.4094</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0366</v>
+        <v>2.0329</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2125</v>
+        <v>2.2134</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6025</v>
+        <v>2.6093</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7739</v>
+        <v>2.7774</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8133</v>
+        <v>2.8152</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8597</v>
+        <v>2.8613</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8924</v>
+        <v>2.8938</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9158</v>
+        <v>2.9172</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9329</v>
+        <v>2.934</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9665</v>
+        <v>2.967</v>
       </c>
       <c r="O18" t="n">
         <v>2.9653</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9611</v>
+        <v>2.9605</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9745</v>
+        <v>2.9732</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1006</v>
+        <v>3.1106</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8313</v>
+        <v>2.8385</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4071</v>
+        <v>2.4101</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0365</v>
+        <v>2.0366</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2088</v>
+        <v>2.2125</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5943</v>
+        <v>2.6025</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7691</v>
+        <v>2.7739</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8105</v>
+        <v>2.8133</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8573</v>
+        <v>2.8597</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8903</v>
+        <v>2.8924</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9141</v>
+        <v>2.9158</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9313</v>
+        <v>2.9329</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9658</v>
+        <v>2.9665</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9652</v>
+        <v>2.9653</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9616</v>
+        <v>2.9611</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9756</v>
+        <v>2.9745</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B20" t="n">
-        <v>3.0828</v>
+        <v>3.1006</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8158</v>
+        <v>2.8313</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3953</v>
+        <v>2.4071</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0285</v>
+        <v>2.0365</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2005</v>
+        <v>2.2088</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5848</v>
+        <v>2.5943</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7613</v>
+        <v>2.7691</v>
       </c>
       <c r="I20" t="n">
-        <v>2.803</v>
+        <v>2.8105</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8495</v>
+        <v>2.8573</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8822</v>
+        <v>2.8903</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9055</v>
+        <v>2.9141</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9222</v>
+        <v>2.9313</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9534</v>
+        <v>2.9658</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9487</v>
+        <v>2.9652</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9403</v>
+        <v>2.9616</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9486</v>
+        <v>2.9756</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B21" t="n">
-        <v>3.0643</v>
+        <v>3.0828</v>
       </c>
       <c r="C21" t="n">
-        <v>2.7967</v>
+        <v>2.8158</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3757</v>
+        <v>2.3953</v>
       </c>
       <c r="E21" t="n">
-        <v>2.01</v>
+        <v>2.0285</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1854</v>
+        <v>2.2005</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5725</v>
+        <v>2.5848</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7435</v>
+        <v>2.7613</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7822</v>
+        <v>2.803</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8274</v>
+        <v>2.8495</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8592</v>
+        <v>2.8822</v>
       </c>
       <c r="L21" t="n">
-        <v>2.8819</v>
+        <v>2.9055</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8982</v>
+        <v>2.9222</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9288</v>
+        <v>2.9534</v>
       </c>
       <c r="O21" t="n">
-        <v>2.925</v>
+        <v>2.9487</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9182</v>
+        <v>2.9403</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9283</v>
+        <v>2.9486</v>
       </c>
     </row>
   </sheetData>
@@ -1672,1101 +1672,1101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C2" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D2" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E2" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F2" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G2" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H2" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I2" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J2" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K2" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L2" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M2" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N2" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O2" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P2" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q2" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C3" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D3" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E3" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F3" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G3" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H3" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I3" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J3" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K3" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L3" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M3" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N3" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O3" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P3" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q3" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C4" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D4" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E4" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F4" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G4" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H4" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I4" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J4" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K4" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L4" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M4" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N4" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O4" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P4" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q4" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C5" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D5" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E5" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F5" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G5" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H5" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I5" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J5" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K5" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L5" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M5" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N5" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O5" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P5" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q5" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C6" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D6" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E6" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F6" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G6" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H6" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I6" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J6" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K6" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L6" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M6" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N6" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O6" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P6" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q6" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C7" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D7" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E7" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F7" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G7" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H7" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I7" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J7" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K7" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L7" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M7" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N7" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O7" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P7" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q7" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C8" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D8" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E8" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F8" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G8" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H8" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I8" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J8" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K8" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L8" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M8" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N8" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O8" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P8" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q8" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C9" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D9" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E9" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F9" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G9" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H9" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I9" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J9" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K9" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L9" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M9" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N9" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O9" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P9" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q9" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C10" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D10" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E10" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F10" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G10" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H10" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I10" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J10" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K10" t="n">
         <v>29701</v>
       </c>
       <c r="L10" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M10" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N10" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O10" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P10" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q10" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C11" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D11" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E11" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F11" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G11" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H11" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I11" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J11" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K11" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L11" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M11" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N11" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O11" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P11" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q11" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C12" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F12" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G12" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H12" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I12" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K12" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L12" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N12" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O12" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P12" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q12" t="n">
         <v>30659</v>
-      </c>
-      <c r="D12" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E12" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G12" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H12" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I12" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J12" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K12" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L12" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M12" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N12" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O12" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P12" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C13" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D13" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E13" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F13" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G13" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H13" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I13" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J13" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K13" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L13" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M13" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N13" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O13" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P13" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q13" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C14" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D14" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E14" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F14" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G14" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H14" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I14" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J14" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K14" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L14" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M14" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N14" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O14" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P14" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q14" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31825</v>
+        <v>32113</v>
       </c>
       <c r="C15" t="n">
-        <v>28474</v>
+        <v>28634</v>
       </c>
       <c r="D15" t="n">
-        <v>23276</v>
+        <v>23241</v>
       </c>
       <c r="E15" t="n">
-        <v>19139</v>
+        <v>18971</v>
       </c>
       <c r="F15" t="n">
-        <v>22074</v>
+        <v>22057</v>
       </c>
       <c r="G15" t="n">
-        <v>27345</v>
+        <v>27544</v>
       </c>
       <c r="H15" t="n">
-        <v>28290</v>
+        <v>285</v>
       </c>
       <c r="I15" t="n">
-        <v>28305</v>
+        <v>28543</v>
       </c>
       <c r="J15" t="n">
-        <v>28734</v>
+        <v>29022</v>
       </c>
       <c r="K15" t="n">
-        <v>29034</v>
+        <v>29366</v>
       </c>
       <c r="L15" t="n">
-        <v>29248</v>
+        <v>29620</v>
       </c>
       <c r="M15" t="n">
-        <v>29401</v>
+        <v>29810</v>
       </c>
       <c r="N15" t="n">
-        <v>29682</v>
+        <v>30262</v>
       </c>
       <c r="O15" t="n">
-        <v>29638</v>
+        <v>30388</v>
       </c>
       <c r="P15" t="n">
-        <v>29573</v>
+        <v>30508</v>
       </c>
       <c r="Q15" t="n">
-        <v>29686</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31398</v>
+        <v>31825</v>
       </c>
       <c r="C16" t="n">
-        <v>28351</v>
+        <v>28474</v>
       </c>
       <c r="D16" t="n">
-        <v>23608</v>
+        <v>23276</v>
       </c>
       <c r="E16" t="n">
-        <v>19746</v>
+        <v>19139</v>
       </c>
       <c r="F16" t="n">
-        <v>22256</v>
+        <v>22074</v>
       </c>
       <c r="G16" t="n">
-        <v>26970</v>
+        <v>27345</v>
       </c>
       <c r="H16" t="n">
-        <v>28135</v>
+        <v>28290</v>
       </c>
       <c r="I16" t="n">
-        <v>28272</v>
+        <v>28305</v>
       </c>
       <c r="J16" t="n">
-        <v>28702</v>
+        <v>28734</v>
       </c>
       <c r="K16" t="n">
-        <v>29004</v>
+        <v>29034</v>
       </c>
       <c r="L16" t="n">
-        <v>29220</v>
+        <v>29248</v>
       </c>
       <c r="M16" t="n">
-        <v>29374</v>
+        <v>29401</v>
       </c>
       <c r="N16" t="n">
-        <v>29665</v>
+        <v>29682</v>
       </c>
       <c r="O16" t="n">
-        <v>29633</v>
+        <v>29638</v>
       </c>
       <c r="P16" t="n">
-        <v>29581</v>
+        <v>29573</v>
       </c>
       <c r="Q16" t="n">
-        <v>29709</v>
+        <v>29686</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31181</v>
+        <v>31398</v>
       </c>
       <c r="C17" t="n">
-        <v>28427</v>
+        <v>28351</v>
       </c>
       <c r="D17" t="n">
-        <v>24094</v>
+        <v>23608</v>
       </c>
       <c r="E17" t="n">
-        <v>20329</v>
+        <v>19746</v>
       </c>
       <c r="F17" t="n">
-        <v>22134</v>
+        <v>22256</v>
       </c>
       <c r="G17" t="n">
-        <v>26093</v>
+        <v>26970</v>
       </c>
       <c r="H17" t="n">
-        <v>27774</v>
+        <v>28135</v>
       </c>
       <c r="I17" t="n">
-        <v>28152</v>
+        <v>28272</v>
       </c>
       <c r="J17" t="n">
-        <v>28613</v>
+        <v>28702</v>
       </c>
       <c r="K17" t="n">
-        <v>28938</v>
+        <v>29004</v>
       </c>
       <c r="L17" t="n">
-        <v>29172</v>
+        <v>29220</v>
       </c>
       <c r="M17" t="n">
-        <v>29340</v>
+        <v>29374</v>
       </c>
       <c r="N17" t="n">
-        <v>29670</v>
+        <v>29665</v>
       </c>
       <c r="O17" t="n">
-        <v>29653</v>
+        <v>29633</v>
       </c>
       <c r="P17" t="n">
-        <v>29605</v>
+        <v>29581</v>
       </c>
       <c r="Q17" t="n">
-        <v>29732</v>
+        <v>29709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31106</v>
+        <v>31181</v>
       </c>
       <c r="C18" t="n">
-        <v>28385</v>
+        <v>28427</v>
       </c>
       <c r="D18" t="n">
-        <v>24101</v>
+        <v>24094</v>
       </c>
       <c r="E18" t="n">
-        <v>20366</v>
+        <v>20329</v>
       </c>
       <c r="F18" t="n">
-        <v>22125</v>
+        <v>22134</v>
       </c>
       <c r="G18" t="n">
-        <v>26025</v>
+        <v>26093</v>
       </c>
       <c r="H18" t="n">
-        <v>27739</v>
+        <v>27774</v>
       </c>
       <c r="I18" t="n">
-        <v>28133</v>
+        <v>28152</v>
       </c>
       <c r="J18" t="n">
-        <v>28597</v>
+        <v>28613</v>
       </c>
       <c r="K18" t="n">
-        <v>28924</v>
+        <v>28938</v>
       </c>
       <c r="L18" t="n">
-        <v>29158</v>
+        <v>29172</v>
       </c>
       <c r="M18" t="n">
-        <v>29329</v>
+        <v>29340</v>
       </c>
       <c r="N18" t="n">
-        <v>29665</v>
+        <v>29670</v>
       </c>
       <c r="O18" t="n">
         <v>29653</v>
       </c>
       <c r="P18" t="n">
-        <v>29611</v>
+        <v>29605</v>
       </c>
       <c r="Q18" t="n">
-        <v>29745</v>
+        <v>29732</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31006</v>
+        <v>31106</v>
       </c>
       <c r="C19" t="n">
-        <v>28313</v>
+        <v>28385</v>
       </c>
       <c r="D19" t="n">
-        <v>24071</v>
+        <v>24101</v>
       </c>
       <c r="E19" t="n">
-        <v>20365</v>
+        <v>20366</v>
       </c>
       <c r="F19" t="n">
-        <v>22088</v>
+        <v>22125</v>
       </c>
       <c r="G19" t="n">
-        <v>25943</v>
+        <v>26025</v>
       </c>
       <c r="H19" t="n">
-        <v>27691</v>
+        <v>27739</v>
       </c>
       <c r="I19" t="n">
-        <v>28105</v>
+        <v>28133</v>
       </c>
       <c r="J19" t="n">
-        <v>28573</v>
+        <v>28597</v>
       </c>
       <c r="K19" t="n">
-        <v>28903</v>
+        <v>28924</v>
       </c>
       <c r="L19" t="n">
-        <v>29141</v>
+        <v>29158</v>
       </c>
       <c r="M19" t="n">
-        <v>29313</v>
+        <v>29329</v>
       </c>
       <c r="N19" t="n">
-        <v>29658</v>
+        <v>29665</v>
       </c>
       <c r="O19" t="n">
-        <v>29652</v>
+        <v>29653</v>
       </c>
       <c r="P19" t="n">
-        <v>29616</v>
+        <v>29611</v>
       </c>
       <c r="Q19" t="n">
-        <v>29756</v>
+        <v>29745</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30828</v>
+        <v>31006</v>
       </c>
       <c r="C20" t="n">
-        <v>28158</v>
+        <v>28313</v>
       </c>
       <c r="D20" t="n">
-        <v>23953</v>
+        <v>24071</v>
       </c>
       <c r="E20" t="n">
-        <v>20285</v>
+        <v>20365</v>
       </c>
       <c r="F20" t="n">
-        <v>22005</v>
+        <v>22088</v>
       </c>
       <c r="G20" t="n">
-        <v>25848</v>
+        <v>25943</v>
       </c>
       <c r="H20" t="n">
-        <v>27613</v>
+        <v>27691</v>
       </c>
       <c r="I20" t="n">
-        <v>28030</v>
+        <v>28105</v>
       </c>
       <c r="J20" t="n">
-        <v>28495</v>
+        <v>28573</v>
       </c>
       <c r="K20" t="n">
-        <v>28822</v>
+        <v>28903</v>
       </c>
       <c r="L20" t="n">
-        <v>29055</v>
+        <v>29141</v>
       </c>
       <c r="M20" t="n">
-        <v>29222</v>
+        <v>29313</v>
       </c>
       <c r="N20" t="n">
-        <v>29534</v>
+        <v>29658</v>
       </c>
       <c r="O20" t="n">
-        <v>29487</v>
+        <v>29652</v>
       </c>
       <c r="P20" t="n">
-        <v>29403</v>
+        <v>29616</v>
       </c>
       <c r="Q20" t="n">
-        <v>29486</v>
+        <v>29756</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30643</v>
+        <v>30828</v>
       </c>
       <c r="C21" t="n">
-        <v>27967</v>
+        <v>28158</v>
       </c>
       <c r="D21" t="n">
-        <v>23757</v>
+        <v>23953</v>
       </c>
       <c r="E21" t="n">
-        <v>201</v>
+        <v>20285</v>
       </c>
       <c r="F21" t="n">
-        <v>21854</v>
+        <v>22005</v>
       </c>
       <c r="G21" t="n">
-        <v>25725</v>
+        <v>25848</v>
       </c>
       <c r="H21" t="n">
-        <v>27435</v>
+        <v>27613</v>
       </c>
       <c r="I21" t="n">
-        <v>27822</v>
+        <v>28030</v>
       </c>
       <c r="J21" t="n">
-        <v>28274</v>
+        <v>28495</v>
       </c>
       <c r="K21" t="n">
-        <v>28592</v>
+        <v>28822</v>
       </c>
       <c r="L21" t="n">
-        <v>28819</v>
+        <v>29055</v>
       </c>
       <c r="M21" t="n">
-        <v>28982</v>
+        <v>29222</v>
       </c>
       <c r="N21" t="n">
-        <v>29288</v>
+        <v>29534</v>
       </c>
       <c r="O21" t="n">
-        <v>29250</v>
+        <v>29487</v>
       </c>
       <c r="P21" t="n">
-        <v>29182</v>
+        <v>29403</v>
       </c>
       <c r="Q21" t="n">
-        <v>29283</v>
+        <v>29486</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1061 +510,1114 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J4" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M4" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O4" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E5" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B6" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E6" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B7" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B8" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B9" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L9" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P9" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B10" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B11" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K11" t="n">
         <v>2.9701</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M11" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B12" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O12" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P12" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B13" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C13" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B14" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G14" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B15" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H15" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L15" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M15" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1825</v>
+        <v>3.2113</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8474</v>
+        <v>2.8634</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3276</v>
+        <v>2.3241</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9139</v>
+        <v>1.8971</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2074</v>
+        <v>2.2057</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7345</v>
+        <v>2.7544</v>
       </c>
       <c r="H16" t="n">
-        <v>2.829</v>
+        <v>2.85</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8305</v>
+        <v>2.8543</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8734</v>
+        <v>2.9022</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9034</v>
+        <v>2.9366</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9248</v>
+        <v>2.962</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9401</v>
+        <v>2.981</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9682</v>
+        <v>3.0262</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9638</v>
+        <v>3.0388</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9573</v>
+        <v>3.0508</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9686</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1398</v>
+        <v>3.1825</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8351</v>
+        <v>2.8474</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3608</v>
+        <v>2.3276</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9746</v>
+        <v>1.9139</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2256</v>
+        <v>2.2074</v>
       </c>
       <c r="G17" t="n">
-        <v>2.697</v>
+        <v>2.7345</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8135</v>
+        <v>2.829</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8272</v>
+        <v>2.8305</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8702</v>
+        <v>2.8734</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9004</v>
+        <v>2.9034</v>
       </c>
       <c r="L17" t="n">
-        <v>2.922</v>
+        <v>2.9248</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9374</v>
+        <v>2.9401</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9665</v>
+        <v>2.9682</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9633</v>
+        <v>2.9638</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9581</v>
+        <v>2.9573</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9709</v>
+        <v>2.9686</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1181</v>
+        <v>3.1398</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8427</v>
+        <v>2.8351</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4094</v>
+        <v>2.3608</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0329</v>
+        <v>1.9746</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2134</v>
+        <v>2.2256</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6093</v>
+        <v>2.697</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7774</v>
+        <v>2.8135</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8152</v>
+        <v>2.8272</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8613</v>
+        <v>2.8702</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8938</v>
+        <v>2.9004</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9172</v>
+        <v>2.922</v>
       </c>
       <c r="M18" t="n">
-        <v>2.934</v>
+        <v>2.9374</v>
       </c>
       <c r="N18" t="n">
-        <v>2.967</v>
+        <v>2.9665</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9653</v>
+        <v>2.9633</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9605</v>
+        <v>2.9581</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9732</v>
+        <v>2.9709</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1106</v>
+        <v>3.1181</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8385</v>
+        <v>2.8427</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4101</v>
+        <v>2.4094</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0366</v>
+        <v>2.0329</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2125</v>
+        <v>2.2134</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6025</v>
+        <v>2.6093</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7739</v>
+        <v>2.7774</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8133</v>
+        <v>2.8152</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8597</v>
+        <v>2.8613</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8924</v>
+        <v>2.8938</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9158</v>
+        <v>2.9172</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9329</v>
+        <v>2.934</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9665</v>
+        <v>2.967</v>
       </c>
       <c r="O19" t="n">
         <v>2.9653</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9611</v>
+        <v>2.9605</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9745</v>
+        <v>2.9732</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1006</v>
+        <v>3.1106</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8313</v>
+        <v>2.8385</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4071</v>
+        <v>2.4101</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0365</v>
+        <v>2.0366</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2088</v>
+        <v>2.2125</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5943</v>
+        <v>2.6025</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7691</v>
+        <v>2.7739</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8105</v>
+        <v>2.8133</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8573</v>
+        <v>2.8597</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8903</v>
+        <v>2.8924</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9141</v>
+        <v>2.9158</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9313</v>
+        <v>2.9329</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9658</v>
+        <v>2.9665</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9652</v>
+        <v>2.9653</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9616</v>
+        <v>2.9611</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9756</v>
+        <v>2.9745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.1006</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.8313</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.4071</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.0365</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2088</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.5943</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.7691</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8105</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.8573</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.8903</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.9141</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.9313</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.9658</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.9652</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.9616</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.9756</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>3.0828</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>2.8158</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>2.3953</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>2.0285</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>2.2005</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>2.5848</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>2.7613</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>2.803</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2.8495</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2.8822</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>2.9055</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>2.9222</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>2.9534</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>2.9487</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>2.9403</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>2.9486</v>
       </c>
     </row>
@@ -1579,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,1100 +1725,1155 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C2" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D2" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E2" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F2" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G2" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H2" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I2" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J2" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K2" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L2" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M2" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N2" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O2" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P2" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q2" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C3" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D3" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E3" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F3" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G3" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H3" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I3" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J3" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K3" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L3" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M3" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N3" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O3" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P3" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q3" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C4" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D4" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E4" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F4" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G4" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H4" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I4" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J4" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K4" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L4" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M4" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N4" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O4" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P4" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q4" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C5" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D5" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E5" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F5" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G5" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H5" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I5" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J5" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K5" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L5" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M5" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N5" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O5" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P5" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q5" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C6" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D6" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E6" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F6" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G6" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H6" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I6" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J6" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K6" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L6" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M6" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N6" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O6" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P6" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q6" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C7" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D7" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E7" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F7" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G7" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H7" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I7" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J7" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K7" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L7" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M7" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N7" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O7" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P7" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q7" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C8" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D8" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E8" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F8" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G8" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H8" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I8" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J8" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K8" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L8" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M8" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N8" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O8" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P8" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q8" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C9" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D9" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E9" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F9" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G9" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H9" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I9" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J9" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K9" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L9" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M9" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N9" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O9" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P9" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q9" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C10" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D10" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E10" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F10" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G10" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H10" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I10" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J10" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K10" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L10" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M10" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N10" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O10" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P10" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q10" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C11" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D11" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E11" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F11" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G11" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H11" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I11" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J11" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K11" t="n">
         <v>29701</v>
       </c>
       <c r="L11" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M11" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N11" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O11" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P11" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q11" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C12" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D12" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E12" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F12" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G12" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H12" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I12" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J12" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K12" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L12" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M12" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N12" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O12" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P12" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q12" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C13" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G13" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H13" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J13" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K13" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L13" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M13" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N13" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O13" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P13" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q13" t="n">
         <v>30659</v>
-      </c>
-      <c r="D13" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E13" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F13" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G13" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H13" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I13" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J13" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K13" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L13" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M13" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N13" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O13" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P13" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C14" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D14" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E14" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F14" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G14" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H14" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I14" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J14" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K14" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L14" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M14" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N14" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O14" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P14" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q14" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C15" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D15" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E15" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F15" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G15" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H15" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I15" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J15" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K15" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L15" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M15" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N15" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O15" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P15" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q15" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31825</v>
+        <v>32113</v>
       </c>
       <c r="C16" t="n">
-        <v>28474</v>
+        <v>28634</v>
       </c>
       <c r="D16" t="n">
-        <v>23276</v>
+        <v>23241</v>
       </c>
       <c r="E16" t="n">
-        <v>19139</v>
+        <v>18971</v>
       </c>
       <c r="F16" t="n">
-        <v>22074</v>
+        <v>22057</v>
       </c>
       <c r="G16" t="n">
-        <v>27345</v>
+        <v>27544</v>
       </c>
       <c r="H16" t="n">
-        <v>28290</v>
+        <v>285</v>
       </c>
       <c r="I16" t="n">
-        <v>28305</v>
+        <v>28543</v>
       </c>
       <c r="J16" t="n">
-        <v>28734</v>
+        <v>29022</v>
       </c>
       <c r="K16" t="n">
-        <v>29034</v>
+        <v>29366</v>
       </c>
       <c r="L16" t="n">
-        <v>29248</v>
+        <v>29620</v>
       </c>
       <c r="M16" t="n">
-        <v>29401</v>
+        <v>29810</v>
       </c>
       <c r="N16" t="n">
-        <v>29682</v>
+        <v>30262</v>
       </c>
       <c r="O16" t="n">
-        <v>29638</v>
+        <v>30388</v>
       </c>
       <c r="P16" t="n">
-        <v>29573</v>
+        <v>30508</v>
       </c>
       <c r="Q16" t="n">
-        <v>29686</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31398</v>
+        <v>31825</v>
       </c>
       <c r="C17" t="n">
-        <v>28351</v>
+        <v>28474</v>
       </c>
       <c r="D17" t="n">
-        <v>23608</v>
+        <v>23276</v>
       </c>
       <c r="E17" t="n">
-        <v>19746</v>
+        <v>19139</v>
       </c>
       <c r="F17" t="n">
-        <v>22256</v>
+        <v>22074</v>
       </c>
       <c r="G17" t="n">
-        <v>26970</v>
+        <v>27345</v>
       </c>
       <c r="H17" t="n">
-        <v>28135</v>
+        <v>28290</v>
       </c>
       <c r="I17" t="n">
-        <v>28272</v>
+        <v>28305</v>
       </c>
       <c r="J17" t="n">
-        <v>28702</v>
+        <v>28734</v>
       </c>
       <c r="K17" t="n">
-        <v>29004</v>
+        <v>29034</v>
       </c>
       <c r="L17" t="n">
-        <v>29220</v>
+        <v>29248</v>
       </c>
       <c r="M17" t="n">
-        <v>29374</v>
+        <v>29401</v>
       </c>
       <c r="N17" t="n">
-        <v>29665</v>
+        <v>29682</v>
       </c>
       <c r="O17" t="n">
-        <v>29633</v>
+        <v>29638</v>
       </c>
       <c r="P17" t="n">
-        <v>29581</v>
+        <v>29573</v>
       </c>
       <c r="Q17" t="n">
-        <v>29709</v>
+        <v>29686</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31181</v>
+        <v>31398</v>
       </c>
       <c r="C18" t="n">
-        <v>28427</v>
+        <v>28351</v>
       </c>
       <c r="D18" t="n">
-        <v>24094</v>
+        <v>23608</v>
       </c>
       <c r="E18" t="n">
-        <v>20329</v>
+        <v>19746</v>
       </c>
       <c r="F18" t="n">
-        <v>22134</v>
+        <v>22256</v>
       </c>
       <c r="G18" t="n">
-        <v>26093</v>
+        <v>26970</v>
       </c>
       <c r="H18" t="n">
-        <v>27774</v>
+        <v>28135</v>
       </c>
       <c r="I18" t="n">
-        <v>28152</v>
+        <v>28272</v>
       </c>
       <c r="J18" t="n">
-        <v>28613</v>
+        <v>28702</v>
       </c>
       <c r="K18" t="n">
-        <v>28938</v>
+        <v>29004</v>
       </c>
       <c r="L18" t="n">
-        <v>29172</v>
+        <v>29220</v>
       </c>
       <c r="M18" t="n">
-        <v>29340</v>
+        <v>29374</v>
       </c>
       <c r="N18" t="n">
-        <v>29670</v>
+        <v>29665</v>
       </c>
       <c r="O18" t="n">
-        <v>29653</v>
+        <v>29633</v>
       </c>
       <c r="P18" t="n">
-        <v>29605</v>
+        <v>29581</v>
       </c>
       <c r="Q18" t="n">
-        <v>29732</v>
+        <v>29709</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31106</v>
+        <v>31181</v>
       </c>
       <c r="C19" t="n">
-        <v>28385</v>
+        <v>28427</v>
       </c>
       <c r="D19" t="n">
-        <v>24101</v>
+        <v>24094</v>
       </c>
       <c r="E19" t="n">
-        <v>20366</v>
+        <v>20329</v>
       </c>
       <c r="F19" t="n">
-        <v>22125</v>
+        <v>22134</v>
       </c>
       <c r="G19" t="n">
-        <v>26025</v>
+        <v>26093</v>
       </c>
       <c r="H19" t="n">
-        <v>27739</v>
+        <v>27774</v>
       </c>
       <c r="I19" t="n">
-        <v>28133</v>
+        <v>28152</v>
       </c>
       <c r="J19" t="n">
-        <v>28597</v>
+        <v>28613</v>
       </c>
       <c r="K19" t="n">
-        <v>28924</v>
+        <v>28938</v>
       </c>
       <c r="L19" t="n">
-        <v>29158</v>
+        <v>29172</v>
       </c>
       <c r="M19" t="n">
-        <v>29329</v>
+        <v>29340</v>
       </c>
       <c r="N19" t="n">
-        <v>29665</v>
+        <v>29670</v>
       </c>
       <c r="O19" t="n">
         <v>29653</v>
       </c>
       <c r="P19" t="n">
-        <v>29611</v>
+        <v>29605</v>
       </c>
       <c r="Q19" t="n">
-        <v>29745</v>
+        <v>29732</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31006</v>
+        <v>31106</v>
       </c>
       <c r="C20" t="n">
-        <v>28313</v>
+        <v>28385</v>
       </c>
       <c r="D20" t="n">
-        <v>24071</v>
+        <v>24101</v>
       </c>
       <c r="E20" t="n">
-        <v>20365</v>
+        <v>20366</v>
       </c>
       <c r="F20" t="n">
-        <v>22088</v>
+        <v>22125</v>
       </c>
       <c r="G20" t="n">
-        <v>25943</v>
+        <v>26025</v>
       </c>
       <c r="H20" t="n">
-        <v>27691</v>
+        <v>27739</v>
       </c>
       <c r="I20" t="n">
-        <v>28105</v>
+        <v>28133</v>
       </c>
       <c r="J20" t="n">
-        <v>28573</v>
+        <v>28597</v>
       </c>
       <c r="K20" t="n">
-        <v>28903</v>
+        <v>28924</v>
       </c>
       <c r="L20" t="n">
-        <v>29141</v>
+        <v>29158</v>
       </c>
       <c r="M20" t="n">
-        <v>29313</v>
+        <v>29329</v>
       </c>
       <c r="N20" t="n">
-        <v>29658</v>
+        <v>29665</v>
       </c>
       <c r="O20" t="n">
-        <v>29652</v>
+        <v>29653</v>
       </c>
       <c r="P20" t="n">
-        <v>29616</v>
+        <v>29611</v>
       </c>
       <c r="Q20" t="n">
-        <v>29756</v>
+        <v>29745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>31006</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28313</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24071</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20365</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22088</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25943</v>
+      </c>
+      <c r="H21" t="n">
+        <v>27691</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28105</v>
+      </c>
+      <c r="J21" t="n">
+        <v>28573</v>
+      </c>
+      <c r="K21" t="n">
+        <v>28903</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29141</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29313</v>
+      </c>
+      <c r="N21" t="n">
+        <v>29658</v>
+      </c>
+      <c r="O21" t="n">
+        <v>29652</v>
+      </c>
+      <c r="P21" t="n">
+        <v>29616</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>29756</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>30828</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>28158</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>23953</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>20285</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>22005</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>25848</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>27613</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>28030</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>28495</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>28822</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>29055</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>29222</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>29534</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>29487</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>29403</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>29486</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1114 +510,1167 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I2" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J2" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J5" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M5" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O5" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E6" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B7" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E7" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B8" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B9" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B10" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L10" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P10" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B11" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B12" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K12" t="n">
         <v>2.9701</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M12" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B13" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C13" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O13" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P13" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B14" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C14" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B15" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G15" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B16" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H16" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L16" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M16" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1825</v>
+        <v>3.2113</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8474</v>
+        <v>2.8634</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3276</v>
+        <v>2.3241</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9139</v>
+        <v>1.8971</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2074</v>
+        <v>2.2057</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7345</v>
+        <v>2.7544</v>
       </c>
       <c r="H17" t="n">
-        <v>2.829</v>
+        <v>2.85</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8305</v>
+        <v>2.8543</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8734</v>
+        <v>2.9022</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9034</v>
+        <v>2.9366</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9248</v>
+        <v>2.962</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9401</v>
+        <v>2.981</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9682</v>
+        <v>3.0262</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9638</v>
+        <v>3.0388</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9573</v>
+        <v>3.0508</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9686</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1398</v>
+        <v>3.1825</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8351</v>
+        <v>2.8474</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3608</v>
+        <v>2.3276</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9746</v>
+        <v>1.9139</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2256</v>
+        <v>2.2074</v>
       </c>
       <c r="G18" t="n">
-        <v>2.697</v>
+        <v>2.7345</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8135</v>
+        <v>2.829</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8272</v>
+        <v>2.8305</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8702</v>
+        <v>2.8734</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9004</v>
+        <v>2.9034</v>
       </c>
       <c r="L18" t="n">
-        <v>2.922</v>
+        <v>2.9248</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9374</v>
+        <v>2.9401</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9665</v>
+        <v>2.9682</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9633</v>
+        <v>2.9638</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9581</v>
+        <v>2.9573</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9709</v>
+        <v>2.9686</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1181</v>
+        <v>3.1398</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8427</v>
+        <v>2.8351</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4094</v>
+        <v>2.3608</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0329</v>
+        <v>1.9746</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2134</v>
+        <v>2.2256</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6093</v>
+        <v>2.697</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7774</v>
+        <v>2.8135</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8152</v>
+        <v>2.8272</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8613</v>
+        <v>2.8702</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8938</v>
+        <v>2.9004</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9172</v>
+        <v>2.922</v>
       </c>
       <c r="M19" t="n">
-        <v>2.934</v>
+        <v>2.9374</v>
       </c>
       <c r="N19" t="n">
-        <v>2.967</v>
+        <v>2.9665</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9653</v>
+        <v>2.9633</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9605</v>
+        <v>2.9581</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9732</v>
+        <v>2.9709</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1106</v>
+        <v>3.1181</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8385</v>
+        <v>2.8427</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4101</v>
+        <v>2.4094</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0366</v>
+        <v>2.0329</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2125</v>
+        <v>2.2134</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6025</v>
+        <v>2.6093</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7739</v>
+        <v>2.7774</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8133</v>
+        <v>2.8152</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8597</v>
+        <v>2.8613</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8924</v>
+        <v>2.8938</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9158</v>
+        <v>2.9172</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9329</v>
+        <v>2.934</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9665</v>
+        <v>2.967</v>
       </c>
       <c r="O20" t="n">
         <v>2.9653</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9611</v>
+        <v>2.9605</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9745</v>
+        <v>2.9732</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B21" t="n">
-        <v>3.1006</v>
+        <v>3.1106</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8313</v>
+        <v>2.8385</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4071</v>
+        <v>2.4101</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0365</v>
+        <v>2.0366</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2088</v>
+        <v>2.2125</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5943</v>
+        <v>2.6025</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7691</v>
+        <v>2.7739</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8105</v>
+        <v>2.8133</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8573</v>
+        <v>2.8597</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8903</v>
+        <v>2.8924</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9141</v>
+        <v>2.9158</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9313</v>
+        <v>2.9329</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9658</v>
+        <v>2.9665</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9652</v>
+        <v>2.9653</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9616</v>
+        <v>2.9611</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9756</v>
+        <v>2.9745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.1006</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.8313</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.4071</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.0365</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.2088</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.5943</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.7691</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8105</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.8573</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.8903</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.9141</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.9313</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.9658</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.9652</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.9616</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.9756</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>3.0828</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>2.8158</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>2.3953</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>2.0285</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>2.2005</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>2.5848</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>2.7613</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>2.803</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2.8495</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>2.8822</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>2.9055</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>2.9222</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>2.9534</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>2.9487</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>2.9403</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>2.9486</v>
       </c>
     </row>
@@ -1632,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,1155 +1778,1210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C2" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D2" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E2" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F2" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G2" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H2" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I2" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J2" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K2" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L2" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M2" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N2" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O2" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P2" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q2" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C3" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D3" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E3" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F3" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G3" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H3" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I3" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J3" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K3" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L3" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M3" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N3" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O3" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P3" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q3" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C4" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D4" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E4" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F4" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G4" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H4" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I4" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J4" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K4" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L4" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M4" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N4" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O4" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P4" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q4" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C5" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D5" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E5" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F5" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G5" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H5" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I5" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J5" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K5" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L5" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M5" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N5" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O5" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P5" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q5" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C6" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D6" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E6" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F6" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G6" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H6" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I6" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J6" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K6" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L6" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M6" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N6" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O6" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P6" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q6" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C7" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D7" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E7" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F7" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G7" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H7" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I7" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J7" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K7" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L7" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M7" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N7" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O7" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P7" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q7" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C8" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D8" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E8" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F8" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G8" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H8" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I8" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J8" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K8" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L8" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M8" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N8" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O8" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P8" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q8" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C9" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D9" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E9" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F9" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G9" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H9" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I9" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J9" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K9" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L9" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M9" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N9" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O9" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P9" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q9" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C10" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D10" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E10" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F10" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G10" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H10" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I10" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J10" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K10" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L10" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M10" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N10" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O10" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P10" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q10" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C11" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D11" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E11" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F11" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G11" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H11" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I11" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J11" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K11" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L11" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M11" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N11" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O11" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P11" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q11" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C12" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D12" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E12" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F12" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G12" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H12" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I12" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J12" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K12" t="n">
         <v>29701</v>
       </c>
       <c r="L12" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M12" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N12" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O12" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P12" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q12" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C13" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D13" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E13" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F13" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G13" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H13" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I13" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J13" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K13" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L13" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M13" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N13" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O13" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P13" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q13" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C14" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F14" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H14" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K14" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M14" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N14" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O14" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P14" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q14" t="n">
         <v>30659</v>
-      </c>
-      <c r="D14" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E14" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F14" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G14" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H14" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I14" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J14" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K14" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L14" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M14" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N14" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O14" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P14" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C15" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D15" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E15" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F15" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G15" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H15" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I15" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J15" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K15" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L15" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M15" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N15" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O15" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P15" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q15" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C16" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D16" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E16" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F16" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G16" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H16" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I16" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J16" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K16" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L16" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M16" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N16" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O16" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P16" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q16" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31825</v>
+        <v>32113</v>
       </c>
       <c r="C17" t="n">
-        <v>28474</v>
+        <v>28634</v>
       </c>
       <c r="D17" t="n">
-        <v>23276</v>
+        <v>23241</v>
       </c>
       <c r="E17" t="n">
-        <v>19139</v>
+        <v>18971</v>
       </c>
       <c r="F17" t="n">
-        <v>22074</v>
+        <v>22057</v>
       </c>
       <c r="G17" t="n">
-        <v>27345</v>
+        <v>27544</v>
       </c>
       <c r="H17" t="n">
-        <v>28290</v>
+        <v>285</v>
       </c>
       <c r="I17" t="n">
-        <v>28305</v>
+        <v>28543</v>
       </c>
       <c r="J17" t="n">
-        <v>28734</v>
+        <v>29022</v>
       </c>
       <c r="K17" t="n">
-        <v>29034</v>
+        <v>29366</v>
       </c>
       <c r="L17" t="n">
-        <v>29248</v>
+        <v>29620</v>
       </c>
       <c r="M17" t="n">
-        <v>29401</v>
+        <v>29810</v>
       </c>
       <c r="N17" t="n">
-        <v>29682</v>
+        <v>30262</v>
       </c>
       <c r="O17" t="n">
-        <v>29638</v>
+        <v>30388</v>
       </c>
       <c r="P17" t="n">
-        <v>29573</v>
+        <v>30508</v>
       </c>
       <c r="Q17" t="n">
-        <v>29686</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31398</v>
+        <v>31825</v>
       </c>
       <c r="C18" t="n">
-        <v>28351</v>
+        <v>28474</v>
       </c>
       <c r="D18" t="n">
-        <v>23608</v>
+        <v>23276</v>
       </c>
       <c r="E18" t="n">
-        <v>19746</v>
+        <v>19139</v>
       </c>
       <c r="F18" t="n">
-        <v>22256</v>
+        <v>22074</v>
       </c>
       <c r="G18" t="n">
-        <v>26970</v>
+        <v>27345</v>
       </c>
       <c r="H18" t="n">
-        <v>28135</v>
+        <v>28290</v>
       </c>
       <c r="I18" t="n">
-        <v>28272</v>
+        <v>28305</v>
       </c>
       <c r="J18" t="n">
-        <v>28702</v>
+        <v>28734</v>
       </c>
       <c r="K18" t="n">
-        <v>29004</v>
+        <v>29034</v>
       </c>
       <c r="L18" t="n">
-        <v>29220</v>
+        <v>29248</v>
       </c>
       <c r="M18" t="n">
-        <v>29374</v>
+        <v>29401</v>
       </c>
       <c r="N18" t="n">
-        <v>29665</v>
+        <v>29682</v>
       </c>
       <c r="O18" t="n">
-        <v>29633</v>
+        <v>29638</v>
       </c>
       <c r="P18" t="n">
-        <v>29581</v>
+        <v>29573</v>
       </c>
       <c r="Q18" t="n">
-        <v>29709</v>
+        <v>29686</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31181</v>
+        <v>31398</v>
       </c>
       <c r="C19" t="n">
-        <v>28427</v>
+        <v>28351</v>
       </c>
       <c r="D19" t="n">
-        <v>24094</v>
+        <v>23608</v>
       </c>
       <c r="E19" t="n">
-        <v>20329</v>
+        <v>19746</v>
       </c>
       <c r="F19" t="n">
-        <v>22134</v>
+        <v>22256</v>
       </c>
       <c r="G19" t="n">
-        <v>26093</v>
+        <v>26970</v>
       </c>
       <c r="H19" t="n">
-        <v>27774</v>
+        <v>28135</v>
       </c>
       <c r="I19" t="n">
-        <v>28152</v>
+        <v>28272</v>
       </c>
       <c r="J19" t="n">
-        <v>28613</v>
+        <v>28702</v>
       </c>
       <c r="K19" t="n">
-        <v>28938</v>
+        <v>29004</v>
       </c>
       <c r="L19" t="n">
-        <v>29172</v>
+        <v>29220</v>
       </c>
       <c r="M19" t="n">
-        <v>29340</v>
+        <v>29374</v>
       </c>
       <c r="N19" t="n">
-        <v>29670</v>
+        <v>29665</v>
       </c>
       <c r="O19" t="n">
-        <v>29653</v>
+        <v>29633</v>
       </c>
       <c r="P19" t="n">
-        <v>29605</v>
+        <v>29581</v>
       </c>
       <c r="Q19" t="n">
-        <v>29732</v>
+        <v>29709</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31106</v>
+        <v>31181</v>
       </c>
       <c r="C20" t="n">
-        <v>28385</v>
+        <v>28427</v>
       </c>
       <c r="D20" t="n">
-        <v>24101</v>
+        <v>24094</v>
       </c>
       <c r="E20" t="n">
-        <v>20366</v>
+        <v>20329</v>
       </c>
       <c r="F20" t="n">
-        <v>22125</v>
+        <v>22134</v>
       </c>
       <c r="G20" t="n">
-        <v>26025</v>
+        <v>26093</v>
       </c>
       <c r="H20" t="n">
-        <v>27739</v>
+        <v>27774</v>
       </c>
       <c r="I20" t="n">
-        <v>28133</v>
+        <v>28152</v>
       </c>
       <c r="J20" t="n">
-        <v>28597</v>
+        <v>28613</v>
       </c>
       <c r="K20" t="n">
-        <v>28924</v>
+        <v>28938</v>
       </c>
       <c r="L20" t="n">
-        <v>29158</v>
+        <v>29172</v>
       </c>
       <c r="M20" t="n">
-        <v>29329</v>
+        <v>29340</v>
       </c>
       <c r="N20" t="n">
-        <v>29665</v>
+        <v>29670</v>
       </c>
       <c r="O20" t="n">
         <v>29653</v>
       </c>
       <c r="P20" t="n">
-        <v>29611</v>
+        <v>29605</v>
       </c>
       <c r="Q20" t="n">
-        <v>29745</v>
+        <v>29732</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31006</v>
+        <v>31106</v>
       </c>
       <c r="C21" t="n">
-        <v>28313</v>
+        <v>28385</v>
       </c>
       <c r="D21" t="n">
-        <v>24071</v>
+        <v>24101</v>
       </c>
       <c r="E21" t="n">
-        <v>20365</v>
+        <v>20366</v>
       </c>
       <c r="F21" t="n">
-        <v>22088</v>
+        <v>22125</v>
       </c>
       <c r="G21" t="n">
-        <v>25943</v>
+        <v>26025</v>
       </c>
       <c r="H21" t="n">
-        <v>27691</v>
+        <v>27739</v>
       </c>
       <c r="I21" t="n">
-        <v>28105</v>
+        <v>28133</v>
       </c>
       <c r="J21" t="n">
-        <v>28573</v>
+        <v>28597</v>
       </c>
       <c r="K21" t="n">
-        <v>28903</v>
+        <v>28924</v>
       </c>
       <c r="L21" t="n">
-        <v>29141</v>
+        <v>29158</v>
       </c>
       <c r="M21" t="n">
-        <v>29313</v>
+        <v>29329</v>
       </c>
       <c r="N21" t="n">
-        <v>29658</v>
+        <v>29665</v>
       </c>
       <c r="O21" t="n">
-        <v>29652</v>
+        <v>29653</v>
       </c>
       <c r="P21" t="n">
-        <v>29616</v>
+        <v>29611</v>
       </c>
       <c r="Q21" t="n">
-        <v>29756</v>
+        <v>29745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>31006</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28313</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24071</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20365</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22088</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25943</v>
+      </c>
+      <c r="H22" t="n">
+        <v>27691</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28105</v>
+      </c>
+      <c r="J22" t="n">
+        <v>28573</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28903</v>
+      </c>
+      <c r="L22" t="n">
+        <v>29141</v>
+      </c>
+      <c r="M22" t="n">
+        <v>29313</v>
+      </c>
+      <c r="N22" t="n">
+        <v>29658</v>
+      </c>
+      <c r="O22" t="n">
+        <v>29652</v>
+      </c>
+      <c r="P22" t="n">
+        <v>29616</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>29756</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>30828</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>28158</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>23953</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>20285</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>22005</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>25848</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>27613</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>28030</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>28495</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>28822</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>29055</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>29222</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>29534</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>29487</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>29403</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>29486</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1168 +510,1168 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E2" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I3" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J3" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B6" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J6" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M6" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O6" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E7" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B8" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E8" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B9" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B10" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B11" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L11" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P11" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B12" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B13" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C13" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K13" t="n">
         <v>2.9701</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M13" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B14" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C14" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O14" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P14" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B15" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C15" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B16" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G16" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B17" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H17" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L17" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M17" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1825</v>
+        <v>3.2113</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8474</v>
+        <v>2.8634</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3276</v>
+        <v>2.3241</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9139</v>
+        <v>1.8971</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2074</v>
+        <v>2.2057</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7345</v>
+        <v>2.7544</v>
       </c>
       <c r="H18" t="n">
-        <v>2.829</v>
+        <v>2.85</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8305</v>
+        <v>2.8543</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8734</v>
+        <v>2.9022</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9034</v>
+        <v>2.9366</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9248</v>
+        <v>2.962</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9401</v>
+        <v>2.981</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9682</v>
+        <v>3.0262</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9638</v>
+        <v>3.0388</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9573</v>
+        <v>3.0508</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9686</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1398</v>
+        <v>3.1825</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8351</v>
+        <v>2.8474</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3608</v>
+        <v>2.3276</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9746</v>
+        <v>1.9139</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2256</v>
+        <v>2.2074</v>
       </c>
       <c r="G19" t="n">
-        <v>2.697</v>
+        <v>2.7345</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8135</v>
+        <v>2.829</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8272</v>
+        <v>2.8305</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8702</v>
+        <v>2.8734</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9004</v>
+        <v>2.9034</v>
       </c>
       <c r="L19" t="n">
-        <v>2.922</v>
+        <v>2.9248</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9374</v>
+        <v>2.9401</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9665</v>
+        <v>2.9682</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9633</v>
+        <v>2.9638</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9581</v>
+        <v>2.9573</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9709</v>
+        <v>2.9686</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1181</v>
+        <v>3.1398</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8427</v>
+        <v>2.8351</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4094</v>
+        <v>2.3608</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0329</v>
+        <v>1.9746</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2134</v>
+        <v>2.2256</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6093</v>
+        <v>2.697</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7774</v>
+        <v>2.8135</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8152</v>
+        <v>2.8272</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8613</v>
+        <v>2.8702</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8938</v>
+        <v>2.9004</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9172</v>
+        <v>2.922</v>
       </c>
       <c r="M20" t="n">
-        <v>2.934</v>
+        <v>2.9374</v>
       </c>
       <c r="N20" t="n">
-        <v>2.967</v>
+        <v>2.9665</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9653</v>
+        <v>2.9633</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9605</v>
+        <v>2.9581</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9732</v>
+        <v>2.9709</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B21" t="n">
-        <v>3.1106</v>
+        <v>3.1181</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8385</v>
+        <v>2.8427</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4101</v>
+        <v>2.4094</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0366</v>
+        <v>2.0329</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2125</v>
+        <v>2.2134</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6025</v>
+        <v>2.6093</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7739</v>
+        <v>2.7774</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8133</v>
+        <v>2.8152</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8597</v>
+        <v>2.8613</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8924</v>
+        <v>2.8938</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9158</v>
+        <v>2.9172</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9329</v>
+        <v>2.934</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9665</v>
+        <v>2.967</v>
       </c>
       <c r="O21" t="n">
         <v>2.9653</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9611</v>
+        <v>2.9605</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9745</v>
+        <v>2.9732</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B22" t="n">
-        <v>3.1006</v>
+        <v>3.1106</v>
       </c>
       <c r="C22" t="n">
-        <v>2.8313</v>
+        <v>2.8385</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4071</v>
+        <v>2.4101</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0365</v>
+        <v>2.0366</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2088</v>
+        <v>2.2125</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5943</v>
+        <v>2.6025</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7691</v>
+        <v>2.7739</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8105</v>
+        <v>2.8133</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8573</v>
+        <v>2.8597</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8903</v>
+        <v>2.8924</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9141</v>
+        <v>2.9158</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9313</v>
+        <v>2.9329</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9658</v>
+        <v>2.9665</v>
       </c>
       <c r="O22" t="n">
-        <v>2.9652</v>
+        <v>2.9653</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9616</v>
+        <v>2.9611</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9756</v>
+        <v>2.9745</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B23" t="n">
-        <v>3.0828</v>
+        <v>3.1006</v>
       </c>
       <c r="C23" t="n">
-        <v>2.8158</v>
+        <v>2.8313</v>
       </c>
       <c r="D23" t="n">
-        <v>2.3953</v>
+        <v>2.4071</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0285</v>
+        <v>2.0365</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2005</v>
+        <v>2.2088</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5848</v>
+        <v>2.5943</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7613</v>
+        <v>2.7691</v>
       </c>
       <c r="I23" t="n">
-        <v>2.803</v>
+        <v>2.8105</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8495</v>
+        <v>2.8573</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8822</v>
+        <v>2.8903</v>
       </c>
       <c r="L23" t="n">
-        <v>2.9055</v>
+        <v>2.9141</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9222</v>
+        <v>2.9313</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9534</v>
+        <v>2.9658</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9487</v>
+        <v>2.9652</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9403</v>
+        <v>2.9616</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9486</v>
+        <v>2.9756</v>
       </c>
     </row>
   </sheetData>
@@ -1778,1211 +1778,1211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C2" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D2" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E2" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F2" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G2" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H2" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I2" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J2" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K2" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L2" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M2" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N2" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O2" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P2" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q2" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C3" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D3" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E3" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F3" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G3" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H3" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I3" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J3" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K3" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L3" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M3" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N3" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O3" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P3" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q3" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C4" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D4" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E4" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F4" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G4" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H4" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I4" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J4" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K4" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L4" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M4" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N4" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O4" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P4" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q4" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C5" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D5" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E5" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F5" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G5" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H5" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I5" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J5" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K5" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L5" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M5" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N5" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O5" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P5" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q5" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C6" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D6" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E6" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F6" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G6" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H6" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I6" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J6" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K6" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L6" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M6" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N6" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O6" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P6" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q6" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C7" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D7" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E7" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F7" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G7" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H7" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I7" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J7" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K7" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L7" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M7" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N7" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O7" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P7" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q7" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C8" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D8" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E8" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F8" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G8" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H8" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I8" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J8" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K8" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L8" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M8" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N8" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O8" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P8" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q8" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C9" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D9" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E9" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F9" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G9" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H9" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I9" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J9" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K9" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L9" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M9" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N9" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O9" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P9" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q9" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C10" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D10" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E10" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F10" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G10" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H10" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I10" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J10" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K10" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L10" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M10" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N10" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O10" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P10" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q10" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C11" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D11" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E11" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F11" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G11" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H11" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I11" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J11" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K11" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L11" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M11" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N11" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O11" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P11" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q11" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C12" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D12" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E12" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F12" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G12" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H12" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I12" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J12" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K12" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L12" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M12" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N12" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O12" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P12" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q12" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C13" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D13" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E13" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F13" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G13" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H13" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I13" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J13" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K13" t="n">
         <v>29701</v>
       </c>
       <c r="L13" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M13" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N13" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O13" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P13" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q13" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C14" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D14" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E14" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F14" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G14" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H14" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I14" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J14" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K14" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L14" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M14" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N14" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O14" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P14" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q14" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C15" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G15" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H15" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I15" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K15" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L15" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M15" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N15" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O15" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P15" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q15" t="n">
         <v>30659</v>
-      </c>
-      <c r="D15" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E15" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G15" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H15" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I15" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J15" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K15" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L15" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M15" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N15" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O15" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P15" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C16" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D16" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E16" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F16" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G16" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H16" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I16" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J16" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K16" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L16" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M16" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N16" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O16" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P16" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q16" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C17" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D17" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E17" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F17" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G17" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H17" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I17" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J17" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K17" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L17" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M17" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N17" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O17" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P17" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q17" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31825</v>
+        <v>32113</v>
       </c>
       <c r="C18" t="n">
-        <v>28474</v>
+        <v>28634</v>
       </c>
       <c r="D18" t="n">
-        <v>23276</v>
+        <v>23241</v>
       </c>
       <c r="E18" t="n">
-        <v>19139</v>
+        <v>18971</v>
       </c>
       <c r="F18" t="n">
-        <v>22074</v>
+        <v>22057</v>
       </c>
       <c r="G18" t="n">
-        <v>27345</v>
+        <v>27544</v>
       </c>
       <c r="H18" t="n">
-        <v>28290</v>
+        <v>285</v>
       </c>
       <c r="I18" t="n">
-        <v>28305</v>
+        <v>28543</v>
       </c>
       <c r="J18" t="n">
-        <v>28734</v>
+        <v>29022</v>
       </c>
       <c r="K18" t="n">
-        <v>29034</v>
+        <v>29366</v>
       </c>
       <c r="L18" t="n">
-        <v>29248</v>
+        <v>29620</v>
       </c>
       <c r="M18" t="n">
-        <v>29401</v>
+        <v>29810</v>
       </c>
       <c r="N18" t="n">
-        <v>29682</v>
+        <v>30262</v>
       </c>
       <c r="O18" t="n">
-        <v>29638</v>
+        <v>30388</v>
       </c>
       <c r="P18" t="n">
-        <v>29573</v>
+        <v>30508</v>
       </c>
       <c r="Q18" t="n">
-        <v>29686</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31398</v>
+        <v>31825</v>
       </c>
       <c r="C19" t="n">
-        <v>28351</v>
+        <v>28474</v>
       </c>
       <c r="D19" t="n">
-        <v>23608</v>
+        <v>23276</v>
       </c>
       <c r="E19" t="n">
-        <v>19746</v>
+        <v>19139</v>
       </c>
       <c r="F19" t="n">
-        <v>22256</v>
+        <v>22074</v>
       </c>
       <c r="G19" t="n">
-        <v>26970</v>
+        <v>27345</v>
       </c>
       <c r="H19" t="n">
-        <v>28135</v>
+        <v>28290</v>
       </c>
       <c r="I19" t="n">
-        <v>28272</v>
+        <v>28305</v>
       </c>
       <c r="J19" t="n">
-        <v>28702</v>
+        <v>28734</v>
       </c>
       <c r="K19" t="n">
-        <v>29004</v>
+        <v>29034</v>
       </c>
       <c r="L19" t="n">
-        <v>29220</v>
+        <v>29248</v>
       </c>
       <c r="M19" t="n">
-        <v>29374</v>
+        <v>29401</v>
       </c>
       <c r="N19" t="n">
-        <v>29665</v>
+        <v>29682</v>
       </c>
       <c r="O19" t="n">
-        <v>29633</v>
+        <v>29638</v>
       </c>
       <c r="P19" t="n">
-        <v>29581</v>
+        <v>29573</v>
       </c>
       <c r="Q19" t="n">
-        <v>29709</v>
+        <v>29686</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31181</v>
+        <v>31398</v>
       </c>
       <c r="C20" t="n">
-        <v>28427</v>
+        <v>28351</v>
       </c>
       <c r="D20" t="n">
-        <v>24094</v>
+        <v>23608</v>
       </c>
       <c r="E20" t="n">
-        <v>20329</v>
+        <v>19746</v>
       </c>
       <c r="F20" t="n">
-        <v>22134</v>
+        <v>22256</v>
       </c>
       <c r="G20" t="n">
-        <v>26093</v>
+        <v>26970</v>
       </c>
       <c r="H20" t="n">
-        <v>27774</v>
+        <v>28135</v>
       </c>
       <c r="I20" t="n">
-        <v>28152</v>
+        <v>28272</v>
       </c>
       <c r="J20" t="n">
-        <v>28613</v>
+        <v>28702</v>
       </c>
       <c r="K20" t="n">
-        <v>28938</v>
+        <v>29004</v>
       </c>
       <c r="L20" t="n">
-        <v>29172</v>
+        <v>29220</v>
       </c>
       <c r="M20" t="n">
-        <v>29340</v>
+        <v>29374</v>
       </c>
       <c r="N20" t="n">
-        <v>29670</v>
+        <v>29665</v>
       </c>
       <c r="O20" t="n">
-        <v>29653</v>
+        <v>29633</v>
       </c>
       <c r="P20" t="n">
-        <v>29605</v>
+        <v>29581</v>
       </c>
       <c r="Q20" t="n">
-        <v>29732</v>
+        <v>29709</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31106</v>
+        <v>31181</v>
       </c>
       <c r="C21" t="n">
-        <v>28385</v>
+        <v>28427</v>
       </c>
       <c r="D21" t="n">
-        <v>24101</v>
+        <v>24094</v>
       </c>
       <c r="E21" t="n">
-        <v>20366</v>
+        <v>20329</v>
       </c>
       <c r="F21" t="n">
-        <v>22125</v>
+        <v>22134</v>
       </c>
       <c r="G21" t="n">
-        <v>26025</v>
+        <v>26093</v>
       </c>
       <c r="H21" t="n">
-        <v>27739</v>
+        <v>27774</v>
       </c>
       <c r="I21" t="n">
-        <v>28133</v>
+        <v>28152</v>
       </c>
       <c r="J21" t="n">
-        <v>28597</v>
+        <v>28613</v>
       </c>
       <c r="K21" t="n">
-        <v>28924</v>
+        <v>28938</v>
       </c>
       <c r="L21" t="n">
-        <v>29158</v>
+        <v>29172</v>
       </c>
       <c r="M21" t="n">
-        <v>29329</v>
+        <v>29340</v>
       </c>
       <c r="N21" t="n">
-        <v>29665</v>
+        <v>29670</v>
       </c>
       <c r="O21" t="n">
         <v>29653</v>
       </c>
       <c r="P21" t="n">
-        <v>29611</v>
+        <v>29605</v>
       </c>
       <c r="Q21" t="n">
-        <v>29745</v>
+        <v>29732</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31006</v>
+        <v>31106</v>
       </c>
       <c r="C22" t="n">
-        <v>28313</v>
+        <v>28385</v>
       </c>
       <c r="D22" t="n">
-        <v>24071</v>
+        <v>24101</v>
       </c>
       <c r="E22" t="n">
-        <v>20365</v>
+        <v>20366</v>
       </c>
       <c r="F22" t="n">
-        <v>22088</v>
+        <v>22125</v>
       </c>
       <c r="G22" t="n">
-        <v>25943</v>
+        <v>26025</v>
       </c>
       <c r="H22" t="n">
-        <v>27691</v>
+        <v>27739</v>
       </c>
       <c r="I22" t="n">
-        <v>28105</v>
+        <v>28133</v>
       </c>
       <c r="J22" t="n">
-        <v>28573</v>
+        <v>28597</v>
       </c>
       <c r="K22" t="n">
-        <v>28903</v>
+        <v>28924</v>
       </c>
       <c r="L22" t="n">
-        <v>29141</v>
+        <v>29158</v>
       </c>
       <c r="M22" t="n">
-        <v>29313</v>
+        <v>29329</v>
       </c>
       <c r="N22" t="n">
-        <v>29658</v>
+        <v>29665</v>
       </c>
       <c r="O22" t="n">
-        <v>29652</v>
+        <v>29653</v>
       </c>
       <c r="P22" t="n">
-        <v>29616</v>
+        <v>29611</v>
       </c>
       <c r="Q22" t="n">
-        <v>29756</v>
+        <v>29745</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30828</v>
+        <v>31006</v>
       </c>
       <c r="C23" t="n">
-        <v>28158</v>
+        <v>28313</v>
       </c>
       <c r="D23" t="n">
-        <v>23953</v>
+        <v>24071</v>
       </c>
       <c r="E23" t="n">
-        <v>20285</v>
+        <v>20365</v>
       </c>
       <c r="F23" t="n">
-        <v>22005</v>
+        <v>22088</v>
       </c>
       <c r="G23" t="n">
-        <v>25848</v>
+        <v>25943</v>
       </c>
       <c r="H23" t="n">
-        <v>27613</v>
+        <v>27691</v>
       </c>
       <c r="I23" t="n">
-        <v>28030</v>
+        <v>28105</v>
       </c>
       <c r="J23" t="n">
-        <v>28495</v>
+        <v>28573</v>
       </c>
       <c r="K23" t="n">
-        <v>28822</v>
+        <v>28903</v>
       </c>
       <c r="L23" t="n">
-        <v>29055</v>
+        <v>29141</v>
       </c>
       <c r="M23" t="n">
-        <v>29222</v>
+        <v>29313</v>
       </c>
       <c r="N23" t="n">
-        <v>29534</v>
+        <v>29658</v>
       </c>
       <c r="O23" t="n">
-        <v>29487</v>
+        <v>29652</v>
       </c>
       <c r="P23" t="n">
-        <v>29403</v>
+        <v>29616</v>
       </c>
       <c r="Q23" t="n">
-        <v>29486</v>
+        <v>29756</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1168 +510,1062 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O2" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E3" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I4" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J4" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B7" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J7" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M7" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O7" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E8" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B9" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E9" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B10" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B11" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L12" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P12" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B13" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B14" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C14" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K14" t="n">
         <v>2.9701</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M14" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B15" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C15" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O15" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P15" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B16" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C16" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B17" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G17" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B18" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H18" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L18" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M18" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1825</v>
+        <v>3.2113</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8474</v>
+        <v>2.8634</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3276</v>
+        <v>2.3241</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9139</v>
+        <v>1.8971</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2074</v>
+        <v>2.2057</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7345</v>
+        <v>2.7544</v>
       </c>
       <c r="H19" t="n">
-        <v>2.829</v>
+        <v>2.85</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8305</v>
+        <v>2.8543</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8734</v>
+        <v>2.9022</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9034</v>
+        <v>2.9366</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9248</v>
+        <v>2.962</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9401</v>
+        <v>2.981</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9682</v>
+        <v>3.0262</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9638</v>
+        <v>3.0388</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9573</v>
+        <v>3.0508</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9686</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1398</v>
+        <v>3.1825</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8351</v>
+        <v>2.8474</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3608</v>
+        <v>2.3276</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9746</v>
+        <v>1.9139</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2256</v>
+        <v>2.2074</v>
       </c>
       <c r="G20" t="n">
-        <v>2.697</v>
+        <v>2.7345</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8135</v>
+        <v>2.829</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8272</v>
+        <v>2.8305</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8702</v>
+        <v>2.8734</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9004</v>
+        <v>2.9034</v>
       </c>
       <c r="L20" t="n">
-        <v>2.922</v>
+        <v>2.9248</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9374</v>
+        <v>2.9401</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9665</v>
+        <v>2.9682</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9633</v>
+        <v>2.9638</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9581</v>
+        <v>2.9573</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9709</v>
+        <v>2.9686</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B21" t="n">
-        <v>3.1181</v>
+        <v>3.1398</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8427</v>
+        <v>2.8351</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4094</v>
+        <v>2.3608</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0329</v>
+        <v>1.9746</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2134</v>
+        <v>2.2256</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6093</v>
+        <v>2.697</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7774</v>
+        <v>2.8135</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8152</v>
+        <v>2.8272</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8613</v>
+        <v>2.8702</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8938</v>
+        <v>2.9004</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9172</v>
+        <v>2.922</v>
       </c>
       <c r="M21" t="n">
-        <v>2.934</v>
+        <v>2.9374</v>
       </c>
       <c r="N21" t="n">
-        <v>2.967</v>
+        <v>2.9665</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9653</v>
+        <v>2.9633</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9605</v>
+        <v>2.9581</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9732</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3.1106</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.8385</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.4101</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.0366</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.2125</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.6025</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.7739</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8133</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.8597</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.8924</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.9158</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.9329</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.9665</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.9611</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.9745</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3.1006</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.8313</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.4071</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.0365</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.2088</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.5943</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.7691</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.8105</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.8573</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.8903</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.9141</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.9313</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.9658</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.9652</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.9616</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.9756</v>
+        <v>2.9709</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,1211 +1672,1101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C2" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D2" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E2" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F2" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G2" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H2" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I2" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J2" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K2" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L2" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M2" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N2" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O2" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P2" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q2" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C3" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D3" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E3" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F3" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G3" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H3" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I3" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J3" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K3" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L3" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M3" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N3" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O3" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P3" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q3" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C4" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D4" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E4" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F4" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G4" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H4" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I4" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J4" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K4" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L4" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M4" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N4" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O4" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P4" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q4" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C5" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D5" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E5" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F5" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G5" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H5" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I5" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J5" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K5" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L5" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M5" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N5" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O5" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P5" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q5" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C6" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D6" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E6" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F6" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G6" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H6" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I6" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J6" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K6" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L6" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M6" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N6" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O6" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P6" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q6" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C7" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D7" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E7" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F7" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G7" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H7" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I7" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J7" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K7" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L7" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M7" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N7" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O7" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P7" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q7" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C8" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D8" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E8" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F8" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G8" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H8" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I8" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J8" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K8" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L8" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M8" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N8" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O8" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P8" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q8" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C9" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D9" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E9" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F9" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G9" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H9" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I9" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J9" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K9" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L9" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M9" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N9" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O9" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P9" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q9" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C10" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D10" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E10" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F10" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G10" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H10" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I10" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J10" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K10" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L10" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M10" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N10" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O10" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P10" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q10" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C11" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D11" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E11" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F11" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G11" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H11" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I11" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J11" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K11" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L11" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M11" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N11" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O11" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P11" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q11" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C12" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D12" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E12" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F12" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G12" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H12" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I12" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J12" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K12" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L12" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M12" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N12" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O12" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P12" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q12" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C13" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D13" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E13" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F13" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G13" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H13" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I13" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J13" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K13" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L13" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M13" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N13" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O13" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P13" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q13" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C14" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D14" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E14" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F14" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G14" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H14" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I14" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J14" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K14" t="n">
         <v>29701</v>
       </c>
       <c r="L14" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M14" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N14" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O14" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P14" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q14" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C15" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D15" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E15" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F15" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G15" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H15" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I15" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J15" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K15" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L15" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M15" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N15" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O15" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P15" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q15" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C16" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E16" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F16" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H16" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I16" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J16" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L16" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M16" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O16" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P16" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q16" t="n">
         <v>30659</v>
-      </c>
-      <c r="D16" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E16" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F16" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G16" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H16" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I16" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J16" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K16" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L16" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M16" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N16" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O16" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P16" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C17" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D17" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E17" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F17" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G17" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H17" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I17" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J17" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K17" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L17" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M17" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N17" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O17" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P17" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q17" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C18" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D18" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E18" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F18" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G18" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H18" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I18" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J18" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K18" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L18" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M18" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N18" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O18" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P18" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q18" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31825</v>
+        <v>32113</v>
       </c>
       <c r="C19" t="n">
-        <v>28474</v>
+        <v>28634</v>
       </c>
       <c r="D19" t="n">
-        <v>23276</v>
+        <v>23241</v>
       </c>
       <c r="E19" t="n">
-        <v>19139</v>
+        <v>18971</v>
       </c>
       <c r="F19" t="n">
-        <v>22074</v>
+        <v>22057</v>
       </c>
       <c r="G19" t="n">
-        <v>27345</v>
+        <v>27544</v>
       </c>
       <c r="H19" t="n">
-        <v>28290</v>
+        <v>285</v>
       </c>
       <c r="I19" t="n">
-        <v>28305</v>
+        <v>28543</v>
       </c>
       <c r="J19" t="n">
-        <v>28734</v>
+        <v>29022</v>
       </c>
       <c r="K19" t="n">
-        <v>29034</v>
+        <v>29366</v>
       </c>
       <c r="L19" t="n">
-        <v>29248</v>
+        <v>29620</v>
       </c>
       <c r="M19" t="n">
-        <v>29401</v>
+        <v>29810</v>
       </c>
       <c r="N19" t="n">
-        <v>29682</v>
+        <v>30262</v>
       </c>
       <c r="O19" t="n">
-        <v>29638</v>
+        <v>30388</v>
       </c>
       <c r="P19" t="n">
-        <v>29573</v>
+        <v>30508</v>
       </c>
       <c r="Q19" t="n">
-        <v>29686</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31398</v>
+        <v>31825</v>
       </c>
       <c r="C20" t="n">
-        <v>28351</v>
+        <v>28474</v>
       </c>
       <c r="D20" t="n">
-        <v>23608</v>
+        <v>23276</v>
       </c>
       <c r="E20" t="n">
-        <v>19746</v>
+        <v>19139</v>
       </c>
       <c r="F20" t="n">
-        <v>22256</v>
+        <v>22074</v>
       </c>
       <c r="G20" t="n">
-        <v>26970</v>
+        <v>27345</v>
       </c>
       <c r="H20" t="n">
-        <v>28135</v>
+        <v>28290</v>
       </c>
       <c r="I20" t="n">
-        <v>28272</v>
+        <v>28305</v>
       </c>
       <c r="J20" t="n">
-        <v>28702</v>
+        <v>28734</v>
       </c>
       <c r="K20" t="n">
-        <v>29004</v>
+        <v>29034</v>
       </c>
       <c r="L20" t="n">
-        <v>29220</v>
+        <v>29248</v>
       </c>
       <c r="M20" t="n">
-        <v>29374</v>
+        <v>29401</v>
       </c>
       <c r="N20" t="n">
-        <v>29665</v>
+        <v>29682</v>
       </c>
       <c r="O20" t="n">
-        <v>29633</v>
+        <v>29638</v>
       </c>
       <c r="P20" t="n">
-        <v>29581</v>
+        <v>29573</v>
       </c>
       <c r="Q20" t="n">
-        <v>29709</v>
+        <v>29686</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31181</v>
+        <v>31398</v>
       </c>
       <c r="C21" t="n">
-        <v>28427</v>
+        <v>28351</v>
       </c>
       <c r="D21" t="n">
-        <v>24094</v>
+        <v>23608</v>
       </c>
       <c r="E21" t="n">
-        <v>20329</v>
+        <v>19746</v>
       </c>
       <c r="F21" t="n">
-        <v>22134</v>
+        <v>22256</v>
       </c>
       <c r="G21" t="n">
-        <v>26093</v>
+        <v>26970</v>
       </c>
       <c r="H21" t="n">
-        <v>27774</v>
+        <v>28135</v>
       </c>
       <c r="I21" t="n">
-        <v>28152</v>
+        <v>28272</v>
       </c>
       <c r="J21" t="n">
-        <v>28613</v>
+        <v>28702</v>
       </c>
       <c r="K21" t="n">
-        <v>28938</v>
+        <v>29004</v>
       </c>
       <c r="L21" t="n">
-        <v>29172</v>
+        <v>29220</v>
       </c>
       <c r="M21" t="n">
-        <v>29340</v>
+        <v>29374</v>
       </c>
       <c r="N21" t="n">
-        <v>29670</v>
+        <v>29665</v>
       </c>
       <c r="O21" t="n">
-        <v>29653</v>
+        <v>29633</v>
       </c>
       <c r="P21" t="n">
-        <v>29605</v>
+        <v>29581</v>
       </c>
       <c r="Q21" t="n">
-        <v>29732</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>19/08/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>31106</v>
-      </c>
-      <c r="C22" t="n">
-        <v>28385</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24101</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20366</v>
-      </c>
-      <c r="F22" t="n">
-        <v>22125</v>
-      </c>
-      <c r="G22" t="n">
-        <v>26025</v>
-      </c>
-      <c r="H22" t="n">
-        <v>27739</v>
-      </c>
-      <c r="I22" t="n">
-        <v>28133</v>
-      </c>
-      <c r="J22" t="n">
-        <v>28597</v>
-      </c>
-      <c r="K22" t="n">
-        <v>28924</v>
-      </c>
-      <c r="L22" t="n">
-        <v>29158</v>
-      </c>
-      <c r="M22" t="n">
-        <v>29329</v>
-      </c>
-      <c r="N22" t="n">
-        <v>29665</v>
-      </c>
-      <c r="O22" t="n">
-        <v>29653</v>
-      </c>
-      <c r="P22" t="n">
-        <v>29611</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>29745</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>18/08/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>31006</v>
-      </c>
-      <c r="C23" t="n">
-        <v>28313</v>
-      </c>
-      <c r="D23" t="n">
-        <v>24071</v>
-      </c>
-      <c r="E23" t="n">
-        <v>20365</v>
-      </c>
-      <c r="F23" t="n">
-        <v>22088</v>
-      </c>
-      <c r="G23" t="n">
-        <v>25943</v>
-      </c>
-      <c r="H23" t="n">
-        <v>27691</v>
-      </c>
-      <c r="I23" t="n">
-        <v>28105</v>
-      </c>
-      <c r="J23" t="n">
-        <v>28573</v>
-      </c>
-      <c r="K23" t="n">
-        <v>28903</v>
-      </c>
-      <c r="L23" t="n">
-        <v>29141</v>
-      </c>
-      <c r="M23" t="n">
-        <v>29313</v>
-      </c>
-      <c r="N23" t="n">
-        <v>29658</v>
-      </c>
-      <c r="O23" t="n">
-        <v>29652</v>
-      </c>
-      <c r="P23" t="n">
-        <v>29616</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>29756</v>
+        <v>29709</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1062 +510,1062 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O3" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E4" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I5" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J5" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J8" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M8" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O8" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E9" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B10" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E10" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B11" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B12" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B13" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L13" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P13" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B14" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B15" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C15" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K15" t="n">
         <v>2.9701</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M15" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B16" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C16" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O16" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P16" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B17" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C17" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B18" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G18" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B19" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H19" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L19" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M19" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1825</v>
+        <v>3.2113</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8474</v>
+        <v>2.8634</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3276</v>
+        <v>2.3241</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9139</v>
+        <v>1.8971</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2074</v>
+        <v>2.2057</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7345</v>
+        <v>2.7544</v>
       </c>
       <c r="H20" t="n">
-        <v>2.829</v>
+        <v>2.85</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8305</v>
+        <v>2.8543</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8734</v>
+        <v>2.9022</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9034</v>
+        <v>2.9366</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9248</v>
+        <v>2.962</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9401</v>
+        <v>2.981</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9682</v>
+        <v>3.0262</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9638</v>
+        <v>3.0388</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9573</v>
+        <v>3.0508</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9686</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B21" t="n">
-        <v>3.1398</v>
+        <v>3.1825</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8351</v>
+        <v>2.8474</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3608</v>
+        <v>2.3276</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9746</v>
+        <v>1.9139</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2256</v>
+        <v>2.2074</v>
       </c>
       <c r="G21" t="n">
-        <v>2.697</v>
+        <v>2.7345</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8135</v>
+        <v>2.829</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8272</v>
+        <v>2.8305</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8702</v>
+        <v>2.8734</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9004</v>
+        <v>2.9034</v>
       </c>
       <c r="L21" t="n">
-        <v>2.922</v>
+        <v>2.9248</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9374</v>
+        <v>2.9401</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9665</v>
+        <v>2.9682</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9633</v>
+        <v>2.9638</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9581</v>
+        <v>2.9573</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9709</v>
+        <v>2.9686</v>
       </c>
     </row>
   </sheetData>
@@ -1672,1101 +1672,1101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C2" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D2" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E2" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F2" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G2" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H2" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I2" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J2" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K2" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L2" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M2" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N2" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O2" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P2" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q2" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C3" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D3" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E3" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F3" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G3" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H3" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I3" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J3" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K3" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L3" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M3" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N3" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O3" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P3" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q3" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C4" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D4" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E4" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F4" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G4" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H4" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I4" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J4" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K4" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L4" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M4" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N4" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O4" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P4" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q4" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C5" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D5" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E5" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F5" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G5" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H5" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I5" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J5" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K5" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L5" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M5" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N5" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O5" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P5" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q5" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C6" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D6" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E6" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F6" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G6" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H6" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I6" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J6" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K6" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L6" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M6" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N6" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O6" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P6" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q6" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C7" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D7" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E7" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F7" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G7" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H7" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I7" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J7" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K7" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L7" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M7" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N7" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O7" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P7" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q7" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C8" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D8" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E8" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F8" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G8" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H8" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I8" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J8" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K8" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L8" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M8" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N8" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O8" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P8" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q8" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C9" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D9" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E9" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F9" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G9" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H9" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I9" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J9" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K9" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L9" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M9" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N9" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O9" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P9" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q9" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C10" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D10" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E10" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F10" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G10" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H10" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I10" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J10" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K10" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L10" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M10" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N10" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O10" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P10" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q10" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C11" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D11" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E11" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F11" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G11" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H11" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I11" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J11" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K11" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L11" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M11" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N11" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O11" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P11" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q11" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C12" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D12" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E12" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F12" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G12" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H12" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I12" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J12" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K12" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L12" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M12" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N12" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O12" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P12" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q12" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C13" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D13" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E13" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F13" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G13" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H13" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I13" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J13" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K13" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L13" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M13" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N13" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O13" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P13" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q13" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C14" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D14" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E14" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F14" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G14" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H14" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I14" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J14" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K14" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L14" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M14" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N14" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O14" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P14" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q14" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C15" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D15" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E15" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F15" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G15" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H15" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I15" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J15" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K15" t="n">
         <v>29701</v>
       </c>
       <c r="L15" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M15" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N15" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O15" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P15" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q15" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C16" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D16" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E16" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F16" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G16" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H16" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I16" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J16" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K16" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L16" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M16" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N16" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O16" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P16" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q16" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C17" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E17" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F17" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G17" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H17" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I17" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J17" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K17" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L17" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M17" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N17" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O17" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P17" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q17" t="n">
         <v>30659</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E17" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F17" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G17" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H17" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I17" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J17" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K17" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L17" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M17" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N17" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O17" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P17" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C18" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D18" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E18" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F18" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G18" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H18" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I18" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J18" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K18" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L18" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M18" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N18" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O18" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P18" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q18" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C19" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D19" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E19" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F19" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G19" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H19" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I19" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J19" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K19" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L19" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M19" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N19" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O19" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P19" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q19" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31825</v>
+        <v>32113</v>
       </c>
       <c r="C20" t="n">
-        <v>28474</v>
+        <v>28634</v>
       </c>
       <c r="D20" t="n">
-        <v>23276</v>
+        <v>23241</v>
       </c>
       <c r="E20" t="n">
-        <v>19139</v>
+        <v>18971</v>
       </c>
       <c r="F20" t="n">
-        <v>22074</v>
+        <v>22057</v>
       </c>
       <c r="G20" t="n">
-        <v>27345</v>
+        <v>27544</v>
       </c>
       <c r="H20" t="n">
-        <v>28290</v>
+        <v>285</v>
       </c>
       <c r="I20" t="n">
-        <v>28305</v>
+        <v>28543</v>
       </c>
       <c r="J20" t="n">
-        <v>28734</v>
+        <v>29022</v>
       </c>
       <c r="K20" t="n">
-        <v>29034</v>
+        <v>29366</v>
       </c>
       <c r="L20" t="n">
-        <v>29248</v>
+        <v>29620</v>
       </c>
       <c r="M20" t="n">
-        <v>29401</v>
+        <v>29810</v>
       </c>
       <c r="N20" t="n">
-        <v>29682</v>
+        <v>30262</v>
       </c>
       <c r="O20" t="n">
-        <v>29638</v>
+        <v>30388</v>
       </c>
       <c r="P20" t="n">
-        <v>29573</v>
+        <v>30508</v>
       </c>
       <c r="Q20" t="n">
-        <v>29686</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31398</v>
+        <v>31825</v>
       </c>
       <c r="C21" t="n">
-        <v>28351</v>
+        <v>28474</v>
       </c>
       <c r="D21" t="n">
-        <v>23608</v>
+        <v>23276</v>
       </c>
       <c r="E21" t="n">
-        <v>19746</v>
+        <v>19139</v>
       </c>
       <c r="F21" t="n">
-        <v>22256</v>
+        <v>22074</v>
       </c>
       <c r="G21" t="n">
-        <v>26970</v>
+        <v>27345</v>
       </c>
       <c r="H21" t="n">
-        <v>28135</v>
+        <v>28290</v>
       </c>
       <c r="I21" t="n">
-        <v>28272</v>
+        <v>28305</v>
       </c>
       <c r="J21" t="n">
-        <v>28702</v>
+        <v>28734</v>
       </c>
       <c r="K21" t="n">
-        <v>29004</v>
+        <v>29034</v>
       </c>
       <c r="L21" t="n">
-        <v>29220</v>
+        <v>29248</v>
       </c>
       <c r="M21" t="n">
-        <v>29374</v>
+        <v>29401</v>
       </c>
       <c r="N21" t="n">
-        <v>29665</v>
+        <v>29682</v>
       </c>
       <c r="O21" t="n">
-        <v>29633</v>
+        <v>29638</v>
       </c>
       <c r="P21" t="n">
-        <v>29581</v>
+        <v>29573</v>
       </c>
       <c r="Q21" t="n">
-        <v>29709</v>
+        <v>29686</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1061 +510,1114 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J2" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M2" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O2" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O4" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E5" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I6" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J6" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B9" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J9" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M9" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O9" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E10" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B11" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E11" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B12" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B13" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B14" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L14" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P14" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B15" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B16" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C16" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K16" t="n">
         <v>2.9701</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M16" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B17" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C17" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O17" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P17" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B18" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C18" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B19" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G19" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B20" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H20" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L20" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M20" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.2113</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.8634</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.3241</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.8971</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2057</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.7544</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8543</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.9022</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9366</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.962</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.981</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.0262</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.0388</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.0508</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.0837</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>3.1825</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>2.8474</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>2.3276</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>1.9139</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>2.2074</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>2.7345</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>2.829</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>2.8305</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2.8734</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2.9034</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>2.9248</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>2.9401</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>2.9682</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>2.9638</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>2.9573</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>2.9686</v>
       </c>
     </row>
@@ -1579,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,1100 +1725,1155 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C2" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D2" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E2" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F2" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G2" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H2" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I2" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J2" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K2" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L2" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M2" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N2" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O2" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P2" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q2" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C3" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D3" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E3" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F3" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G3" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H3" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I3" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J3" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K3" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L3" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M3" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N3" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O3" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P3" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q3" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C4" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D4" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E4" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F4" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G4" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H4" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I4" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J4" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K4" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L4" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M4" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N4" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O4" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P4" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q4" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C5" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D5" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E5" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F5" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G5" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H5" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I5" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J5" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K5" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L5" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M5" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N5" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O5" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P5" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q5" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C6" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D6" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E6" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F6" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G6" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H6" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I6" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J6" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K6" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L6" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M6" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N6" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O6" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P6" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q6" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C7" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D7" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E7" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F7" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G7" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H7" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I7" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J7" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K7" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L7" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M7" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N7" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O7" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P7" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q7" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C8" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D8" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E8" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F8" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G8" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H8" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I8" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J8" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K8" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L8" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M8" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N8" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O8" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P8" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q8" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C9" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D9" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E9" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F9" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G9" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H9" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I9" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J9" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K9" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L9" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M9" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N9" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O9" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P9" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q9" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C10" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D10" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E10" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F10" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G10" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H10" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I10" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J10" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K10" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L10" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M10" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N10" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O10" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P10" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q10" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C11" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D11" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E11" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F11" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G11" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H11" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I11" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J11" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K11" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L11" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M11" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N11" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O11" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P11" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q11" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C12" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D12" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E12" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F12" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G12" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H12" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I12" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J12" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K12" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L12" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M12" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N12" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O12" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P12" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q12" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C13" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D13" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E13" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F13" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G13" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H13" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I13" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J13" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K13" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L13" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M13" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N13" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O13" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P13" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q13" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C14" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D14" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E14" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F14" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G14" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H14" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I14" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J14" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K14" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L14" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M14" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N14" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O14" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P14" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q14" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C15" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D15" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E15" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F15" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G15" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H15" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I15" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J15" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K15" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L15" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M15" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N15" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O15" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P15" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q15" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C16" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D16" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E16" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F16" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G16" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H16" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I16" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J16" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K16" t="n">
         <v>29701</v>
       </c>
       <c r="L16" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M16" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N16" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O16" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P16" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q16" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C17" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D17" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E17" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F17" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G17" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H17" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I17" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J17" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K17" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L17" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M17" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N17" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O17" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P17" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q17" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C18" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D18" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F18" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G18" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H18" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I18" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J18" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K18" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L18" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O18" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P18" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q18" t="n">
         <v>30659</v>
-      </c>
-      <c r="D18" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E18" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F18" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G18" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H18" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I18" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J18" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K18" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L18" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M18" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N18" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O18" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P18" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C19" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D19" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E19" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F19" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G19" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H19" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I19" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J19" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K19" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L19" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M19" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N19" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O19" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P19" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q19" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C20" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D20" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E20" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F20" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G20" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H20" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I20" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J20" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K20" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L20" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M20" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N20" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O20" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P20" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q20" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>32113</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28634</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23241</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18971</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22057</v>
+      </c>
+      <c r="G21" t="n">
+        <v>27544</v>
+      </c>
+      <c r="H21" t="n">
+        <v>285</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28543</v>
+      </c>
+      <c r="J21" t="n">
+        <v>29022</v>
+      </c>
+      <c r="K21" t="n">
+        <v>29366</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29620</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29810</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30262</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30388</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30508</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>30837</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>31825</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>28474</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>23276</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>19139</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>22074</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>27345</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>28290</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>28305</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>28734</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>29034</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>29248</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>29401</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>29682</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>29638</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>29573</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>29686</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1114 +510,1167 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J3" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M3" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O3" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O5" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E6" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I7" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J7" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B10" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J10" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M10" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O10" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E11" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B12" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E12" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B13" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B14" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B15" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L15" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P15" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B16" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B17" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C17" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K17" t="n">
         <v>2.9701</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M17" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B18" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C18" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O18" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P18" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B19" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C19" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B20" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G20" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M20" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B21" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H21" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L21" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M21" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.2113</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.8634</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.3241</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.8971</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.2057</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.7544</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8543</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.9022</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.9366</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.962</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.981</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.0262</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.0388</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.0508</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.0837</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>3.1825</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>2.8474</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>2.3276</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>1.9139</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>2.2074</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>2.7345</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>2.829</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>2.8305</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2.8734</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>2.9034</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>2.9248</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>2.9401</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>2.9682</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>2.9638</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>2.9573</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>2.9686</v>
       </c>
     </row>
@@ -1632,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,1155 +1778,1210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C2" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D2" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E2" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F2" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G2" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H2" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I2" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J2" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K2" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L2" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M2" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N2" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O2" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P2" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q2" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C3" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D3" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E3" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F3" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G3" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H3" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I3" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J3" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K3" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L3" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M3" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N3" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O3" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P3" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q3" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C4" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D4" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E4" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F4" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G4" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H4" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I4" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J4" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K4" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L4" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M4" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N4" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O4" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P4" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q4" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C5" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D5" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E5" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F5" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G5" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H5" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I5" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J5" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K5" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L5" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M5" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N5" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O5" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P5" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q5" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C6" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D6" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E6" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F6" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G6" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H6" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I6" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J6" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K6" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L6" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M6" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N6" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O6" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P6" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q6" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C7" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D7" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E7" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F7" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G7" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H7" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I7" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J7" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K7" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L7" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M7" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N7" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O7" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P7" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q7" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C8" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D8" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E8" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F8" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G8" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H8" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I8" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J8" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K8" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L8" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M8" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N8" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O8" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P8" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q8" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C9" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D9" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E9" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F9" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G9" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H9" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I9" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J9" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K9" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L9" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M9" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N9" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O9" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P9" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q9" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C10" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D10" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E10" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F10" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G10" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H10" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I10" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J10" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K10" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L10" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M10" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N10" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O10" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P10" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q10" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C11" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D11" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E11" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F11" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G11" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H11" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I11" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J11" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K11" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L11" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M11" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N11" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O11" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P11" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q11" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C12" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D12" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E12" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F12" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G12" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H12" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I12" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J12" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K12" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L12" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M12" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N12" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O12" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P12" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q12" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C13" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D13" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E13" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F13" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G13" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H13" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I13" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J13" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K13" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L13" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M13" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N13" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O13" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P13" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q13" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C14" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D14" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E14" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F14" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G14" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H14" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I14" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J14" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K14" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L14" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M14" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N14" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O14" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P14" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q14" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C15" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D15" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E15" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F15" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G15" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H15" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I15" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J15" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K15" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L15" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M15" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N15" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O15" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P15" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q15" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C16" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D16" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E16" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F16" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G16" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H16" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I16" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J16" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K16" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L16" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M16" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N16" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O16" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P16" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q16" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C17" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D17" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E17" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F17" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G17" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H17" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I17" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J17" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K17" t="n">
         <v>29701</v>
       </c>
       <c r="L17" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M17" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N17" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O17" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P17" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q17" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C18" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D18" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E18" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F18" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G18" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H18" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I18" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J18" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K18" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L18" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M18" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N18" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O18" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P18" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q18" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C19" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E19" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G19" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H19" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I19" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J19" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K19" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L19" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M19" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O19" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P19" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q19" t="n">
         <v>30659</v>
-      </c>
-      <c r="D19" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E19" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G19" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H19" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I19" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J19" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K19" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L19" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M19" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N19" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O19" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P19" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C20" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D20" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E20" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F20" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G20" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H20" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I20" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J20" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K20" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L20" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M20" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N20" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O20" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P20" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q20" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C21" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D21" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E21" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F21" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G21" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H21" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I21" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J21" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K21" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L21" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M21" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N21" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O21" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P21" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q21" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>32113</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28634</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23241</v>
+      </c>
+      <c r="E22" t="n">
+        <v>18971</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22057</v>
+      </c>
+      <c r="G22" t="n">
+        <v>27544</v>
+      </c>
+      <c r="H22" t="n">
+        <v>285</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28543</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29022</v>
+      </c>
+      <c r="K22" t="n">
+        <v>29366</v>
+      </c>
+      <c r="L22" t="n">
+        <v>29620</v>
+      </c>
+      <c r="M22" t="n">
+        <v>29810</v>
+      </c>
+      <c r="N22" t="n">
+        <v>30262</v>
+      </c>
+      <c r="O22" t="n">
+        <v>30388</v>
+      </c>
+      <c r="P22" t="n">
+        <v>30508</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>30837</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>31825</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>28474</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>23276</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>19139</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>22074</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>27345</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>28290</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>28305</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>28734</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>29034</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>29248</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>29401</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>29682</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>29638</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>29573</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>29686</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1168 +510,1168 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M2" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J4" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M4" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O4" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O6" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E7" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I8" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J8" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B11" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J11" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M11" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O11" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E12" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B13" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E13" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B14" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B15" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B16" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L16" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P16" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B17" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B18" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C18" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K18" t="n">
         <v>2.9701</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M18" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B19" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C19" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O19" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P19" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B20" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C20" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B21" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C21" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G21" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M21" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0724</v>
+        <v>3.0679</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B22" t="n">
-        <v>3.2113</v>
+        <v>3.3823</v>
       </c>
       <c r="C22" t="n">
-        <v>2.8634</v>
+        <v>2.9942</v>
       </c>
       <c r="D22" t="n">
-        <v>2.3241</v>
+        <v>2.3888</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8971</v>
+        <v>1.8901</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2057</v>
+        <v>2.1949</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7544</v>
+        <v>2.767</v>
       </c>
       <c r="H22" t="n">
-        <v>2.85</v>
+        <v>2.8727</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8543</v>
+        <v>2.8754</v>
       </c>
       <c r="J22" t="n">
-        <v>2.9022</v>
+        <v>2.9233</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9366</v>
+        <v>2.9574</v>
       </c>
       <c r="L22" t="n">
-        <v>2.962</v>
+        <v>2.9822</v>
       </c>
       <c r="M22" t="n">
-        <v>2.981</v>
+        <v>3.0006</v>
       </c>
       <c r="N22" t="n">
-        <v>3.0262</v>
+        <v>3.0406</v>
       </c>
       <c r="O22" t="n">
-        <v>3.0388</v>
+        <v>3.0461</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0508</v>
+        <v>3.0495</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.0837</v>
+        <v>3.0724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B23" t="n">
-        <v>3.1825</v>
+        <v>3.2113</v>
       </c>
       <c r="C23" t="n">
-        <v>2.8474</v>
+        <v>2.8634</v>
       </c>
       <c r="D23" t="n">
-        <v>2.3276</v>
+        <v>2.3241</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9139</v>
+        <v>1.8971</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2074</v>
+        <v>2.2057</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7345</v>
+        <v>2.7544</v>
       </c>
       <c r="H23" t="n">
-        <v>2.829</v>
+        <v>2.85</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8305</v>
+        <v>2.8543</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8734</v>
+        <v>2.9022</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9034</v>
+        <v>2.9366</v>
       </c>
       <c r="L23" t="n">
-        <v>2.9248</v>
+        <v>2.962</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9401</v>
+        <v>2.981</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9682</v>
+        <v>3.0262</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9638</v>
+        <v>3.0388</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9573</v>
+        <v>3.0508</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9686</v>
+        <v>3.0837</v>
       </c>
     </row>
   </sheetData>
@@ -1778,1211 +1778,1211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C2" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D2" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E2" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F2" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G2" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H2" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I2" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J2" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K2" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L2" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M2" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N2" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O2" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P2" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q2" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C3" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D3" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E3" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F3" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G3" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H3" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I3" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J3" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K3" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L3" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M3" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N3" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O3" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P3" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q3" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C4" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D4" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E4" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F4" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G4" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H4" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I4" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J4" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K4" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L4" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M4" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N4" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O4" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P4" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q4" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C5" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D5" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E5" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F5" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G5" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H5" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I5" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J5" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K5" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L5" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M5" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N5" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O5" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P5" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q5" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C6" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D6" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E6" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F6" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G6" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H6" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I6" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J6" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K6" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L6" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M6" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N6" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O6" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P6" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q6" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C7" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D7" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E7" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F7" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G7" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H7" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I7" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J7" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K7" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L7" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M7" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N7" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O7" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P7" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q7" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C8" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D8" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E8" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F8" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G8" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H8" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I8" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J8" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K8" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L8" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M8" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N8" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O8" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P8" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q8" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C9" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D9" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E9" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F9" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G9" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H9" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I9" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J9" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K9" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L9" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M9" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N9" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O9" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P9" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q9" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C10" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D10" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E10" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F10" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G10" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H10" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I10" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J10" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K10" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L10" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M10" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N10" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O10" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P10" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q10" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C11" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D11" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E11" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F11" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G11" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H11" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I11" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J11" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K11" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L11" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M11" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N11" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O11" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P11" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q11" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C12" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D12" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E12" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F12" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G12" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H12" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I12" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J12" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K12" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L12" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M12" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N12" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O12" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P12" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q12" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C13" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D13" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E13" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F13" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G13" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H13" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I13" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J13" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K13" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L13" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M13" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N13" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O13" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P13" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q13" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C14" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D14" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E14" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F14" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G14" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H14" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I14" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J14" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K14" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L14" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M14" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N14" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O14" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P14" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q14" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C15" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D15" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E15" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F15" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G15" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H15" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I15" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J15" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K15" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L15" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M15" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N15" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O15" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P15" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q15" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C16" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D16" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E16" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F16" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G16" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H16" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I16" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J16" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K16" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L16" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M16" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N16" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O16" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P16" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q16" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C17" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D17" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E17" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F17" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G17" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H17" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I17" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J17" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K17" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L17" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M17" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N17" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O17" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P17" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q17" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C18" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D18" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E18" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F18" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G18" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H18" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I18" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J18" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K18" t="n">
         <v>29701</v>
       </c>
       <c r="L18" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M18" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N18" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O18" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P18" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q18" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C19" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D19" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E19" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F19" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G19" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H19" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I19" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J19" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K19" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L19" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M19" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N19" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O19" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P19" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q19" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C20" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G20" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H20" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J20" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K20" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N20" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O20" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P20" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q20" t="n">
         <v>30659</v>
-      </c>
-      <c r="D20" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E20" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F20" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G20" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H20" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I20" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J20" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K20" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L20" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M20" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N20" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O20" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P20" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C21" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D21" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E21" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F21" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G21" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H21" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I21" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J21" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K21" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L21" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M21" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N21" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O21" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P21" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q21" t="n">
-        <v>30724</v>
+        <v>30679</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32113</v>
+        <v>33823</v>
       </c>
       <c r="C22" t="n">
-        <v>28634</v>
+        <v>29942</v>
       </c>
       <c r="D22" t="n">
-        <v>23241</v>
+        <v>23888</v>
       </c>
       <c r="E22" t="n">
-        <v>18971</v>
+        <v>18901</v>
       </c>
       <c r="F22" t="n">
-        <v>22057</v>
+        <v>21949</v>
       </c>
       <c r="G22" t="n">
-        <v>27544</v>
+        <v>27670</v>
       </c>
       <c r="H22" t="n">
-        <v>285</v>
+        <v>28727</v>
       </c>
       <c r="I22" t="n">
-        <v>28543</v>
+        <v>28754</v>
       </c>
       <c r="J22" t="n">
-        <v>29022</v>
+        <v>29233</v>
       </c>
       <c r="K22" t="n">
-        <v>29366</v>
+        <v>29574</v>
       </c>
       <c r="L22" t="n">
-        <v>29620</v>
+        <v>29822</v>
       </c>
       <c r="M22" t="n">
-        <v>29810</v>
+        <v>30006</v>
       </c>
       <c r="N22" t="n">
-        <v>30262</v>
+        <v>30406</v>
       </c>
       <c r="O22" t="n">
-        <v>30388</v>
+        <v>30461</v>
       </c>
       <c r="P22" t="n">
-        <v>30508</v>
+        <v>30495</v>
       </c>
       <c r="Q22" t="n">
-        <v>30837</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31825</v>
+        <v>32113</v>
       </c>
       <c r="C23" t="n">
-        <v>28474</v>
+        <v>28634</v>
       </c>
       <c r="D23" t="n">
-        <v>23276</v>
+        <v>23241</v>
       </c>
       <c r="E23" t="n">
-        <v>19139</v>
+        <v>18971</v>
       </c>
       <c r="F23" t="n">
-        <v>22074</v>
+        <v>22057</v>
       </c>
       <c r="G23" t="n">
-        <v>27345</v>
+        <v>27544</v>
       </c>
       <c r="H23" t="n">
-        <v>28290</v>
+        <v>285</v>
       </c>
       <c r="I23" t="n">
-        <v>28305</v>
+        <v>28543</v>
       </c>
       <c r="J23" t="n">
-        <v>28734</v>
+        <v>29022</v>
       </c>
       <c r="K23" t="n">
-        <v>29034</v>
+        <v>29366</v>
       </c>
       <c r="L23" t="n">
-        <v>29248</v>
+        <v>29620</v>
       </c>
       <c r="M23" t="n">
-        <v>29401</v>
+        <v>29810</v>
       </c>
       <c r="N23" t="n">
-        <v>29682</v>
+        <v>30262</v>
       </c>
       <c r="O23" t="n">
-        <v>29638</v>
+        <v>30388</v>
       </c>
       <c r="P23" t="n">
-        <v>29573</v>
+        <v>30508</v>
       </c>
       <c r="Q23" t="n">
-        <v>29686</v>
+        <v>30837</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1168 +510,1115 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M2" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B3" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M3" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J5" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M5" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O5" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O7" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E8" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I9" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J9" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B12" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J12" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M12" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O12" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E13" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B14" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E14" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B15" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B16" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B17" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L17" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P17" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B18" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B19" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C19" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K19" t="n">
         <v>2.9701</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M19" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B20" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C20" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M20" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O20" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P20" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B21" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C21" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.0679</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B22" t="n">
-        <v>3.3823</v>
+        <v>3.474</v>
       </c>
       <c r="C22" t="n">
-        <v>2.9942</v>
+        <v>3.0659</v>
       </c>
       <c r="D22" t="n">
-        <v>2.3888</v>
+        <v>2.4273</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8901</v>
+        <v>1.8916</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1949</v>
+        <v>2.1924</v>
       </c>
       <c r="G22" t="n">
-        <v>2.767</v>
+        <v>2.7736</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8727</v>
+        <v>2.8828</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8754</v>
+        <v>2.8842</v>
       </c>
       <c r="J22" t="n">
-        <v>2.9233</v>
+        <v>2.9317</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9574</v>
+        <v>2.9653</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9822</v>
+        <v>2.9898</v>
       </c>
       <c r="M22" t="n">
-        <v>3.0006</v>
+        <v>3.0077</v>
       </c>
       <c r="N22" t="n">
-        <v>3.0406</v>
+        <v>3.0454</v>
       </c>
       <c r="O22" t="n">
-        <v>3.0461</v>
+        <v>3.0482</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0495</v>
+        <v>3.0485</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.0724</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3.2113</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.8634</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.3241</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.8971</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.2057</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.7544</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.8543</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.9022</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.9366</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.962</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.981</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.0262</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.0388</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.0508</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.0837</v>
+        <v>3.0679</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,1211 +1725,1156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C2" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D2" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E2" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F2" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G2" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H2" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I2" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J2" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K2" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L2" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M2" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N2" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O2" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P2" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q2" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C3" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D3" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E3" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F3" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G3" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H3" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I3" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J3" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K3" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L3" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M3" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N3" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O3" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P3" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q3" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C4" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D4" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E4" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F4" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G4" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H4" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I4" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J4" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K4" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L4" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M4" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N4" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O4" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P4" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q4" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C5" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D5" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E5" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F5" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G5" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H5" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I5" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J5" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K5" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L5" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M5" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N5" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O5" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P5" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q5" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C6" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D6" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E6" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F6" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G6" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H6" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I6" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J6" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K6" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L6" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M6" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N6" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O6" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P6" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q6" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C7" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D7" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E7" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F7" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G7" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H7" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I7" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J7" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K7" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L7" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M7" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N7" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O7" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P7" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q7" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C8" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D8" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E8" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F8" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G8" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H8" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I8" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J8" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K8" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L8" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M8" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N8" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O8" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P8" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q8" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C9" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D9" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E9" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F9" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G9" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H9" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I9" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J9" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K9" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L9" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M9" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N9" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O9" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P9" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q9" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C10" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D10" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E10" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F10" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G10" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H10" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I10" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J10" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K10" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L10" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M10" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N10" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O10" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P10" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q10" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C11" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D11" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E11" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F11" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G11" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H11" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I11" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J11" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K11" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L11" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M11" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N11" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O11" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P11" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q11" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C12" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D12" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E12" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F12" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G12" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H12" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I12" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J12" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K12" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L12" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M12" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N12" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O12" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P12" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q12" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C13" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D13" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E13" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F13" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G13" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H13" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I13" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J13" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K13" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L13" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M13" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N13" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O13" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P13" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q13" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C14" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D14" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E14" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F14" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G14" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H14" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I14" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J14" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K14" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L14" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M14" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N14" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O14" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P14" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q14" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C15" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D15" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E15" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F15" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G15" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H15" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I15" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J15" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K15" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L15" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M15" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N15" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O15" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P15" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q15" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C16" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D16" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E16" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F16" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G16" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H16" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I16" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J16" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K16" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L16" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M16" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N16" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O16" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P16" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q16" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C17" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D17" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E17" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F17" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G17" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H17" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I17" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J17" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K17" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L17" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M17" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N17" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O17" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P17" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q17" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C18" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D18" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E18" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F18" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G18" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H18" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I18" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J18" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K18" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L18" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M18" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N18" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O18" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P18" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q18" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C19" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D19" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E19" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F19" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G19" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H19" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I19" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J19" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K19" t="n">
         <v>29701</v>
       </c>
       <c r="L19" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M19" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N19" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O19" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P19" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q19" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C20" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D20" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E20" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F20" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G20" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H20" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I20" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J20" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K20" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L20" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M20" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N20" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O20" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P20" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q20" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C21" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F21" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G21" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H21" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J21" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K21" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M21" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q21" t="n">
         <v>30659</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E21" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F21" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G21" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H21" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I21" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K21" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L21" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M21" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N21" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O21" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P21" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>30679</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33823</v>
+        <v>34740</v>
       </c>
       <c r="C22" t="n">
-        <v>29942</v>
+        <v>30659</v>
       </c>
       <c r="D22" t="n">
-        <v>23888</v>
+        <v>24273</v>
       </c>
       <c r="E22" t="n">
-        <v>18901</v>
+        <v>18916</v>
       </c>
       <c r="F22" t="n">
-        <v>21949</v>
+        <v>21924</v>
       </c>
       <c r="G22" t="n">
-        <v>27670</v>
+        <v>27736</v>
       </c>
       <c r="H22" t="n">
-        <v>28727</v>
+        <v>28828</v>
       </c>
       <c r="I22" t="n">
-        <v>28754</v>
+        <v>28842</v>
       </c>
       <c r="J22" t="n">
-        <v>29233</v>
+        <v>29317</v>
       </c>
       <c r="K22" t="n">
-        <v>29574</v>
+        <v>29653</v>
       </c>
       <c r="L22" t="n">
-        <v>29822</v>
+        <v>29898</v>
       </c>
       <c r="M22" t="n">
-        <v>30006</v>
+        <v>30077</v>
       </c>
       <c r="N22" t="n">
-        <v>30406</v>
+        <v>30454</v>
       </c>
       <c r="O22" t="n">
-        <v>30461</v>
+        <v>30482</v>
       </c>
       <c r="P22" t="n">
-        <v>30495</v>
+        <v>30485</v>
       </c>
       <c r="Q22" t="n">
-        <v>30724</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>26/08/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>32113</v>
-      </c>
-      <c r="C23" t="n">
-        <v>28634</v>
-      </c>
-      <c r="D23" t="n">
-        <v>23241</v>
-      </c>
-      <c r="E23" t="n">
-        <v>18971</v>
-      </c>
-      <c r="F23" t="n">
-        <v>22057</v>
-      </c>
-      <c r="G23" t="n">
-        <v>27544</v>
-      </c>
-      <c r="H23" t="n">
-        <v>285</v>
-      </c>
-      <c r="I23" t="n">
-        <v>28543</v>
-      </c>
-      <c r="J23" t="n">
-        <v>29022</v>
-      </c>
-      <c r="K23" t="n">
-        <v>29366</v>
-      </c>
-      <c r="L23" t="n">
-        <v>29620</v>
-      </c>
-      <c r="M23" t="n">
-        <v>29810</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30262</v>
-      </c>
-      <c r="O23" t="n">
-        <v>30388</v>
-      </c>
-      <c r="P23" t="n">
-        <v>30508</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>30837</v>
+        <v>30679</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1115 +510,1115 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O2" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M3" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B4" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M4" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J6" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M6" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O6" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O8" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E9" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I10" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J10" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B13" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J13" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M13" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O13" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E14" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B15" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E15" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B16" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B17" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B18" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L18" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P18" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B19" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B20" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C20" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K20" t="n">
         <v>2.9701</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M20" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B21" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C21" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M21" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O21" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P21" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B22" t="n">
-        <v>3.474</v>
+        <v>3.5012</v>
       </c>
       <c r="C22" t="n">
+        <v>3.0863</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.4368</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.1929</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.7796</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.8874</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8876</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.9349</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.9685</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.9928</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.0105</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.0473</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.0659</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.4273</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.8916</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.1924</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.7736</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.8828</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8842</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.9317</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.9653</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.9898</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.0454</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.0482</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.0485</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.0679</v>
       </c>
     </row>
   </sheetData>
@@ -1725,1156 +1725,1156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C2" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D2" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E2" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F2" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G2" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H2" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I2" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J2" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K2" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L2" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M2" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N2" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O2" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P2" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q2" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C3" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D3" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E3" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F3" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G3" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H3" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I3" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J3" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K3" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L3" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M3" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N3" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O3" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P3" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q3" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C4" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D4" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E4" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F4" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G4" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H4" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I4" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J4" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K4" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L4" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M4" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N4" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O4" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P4" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q4" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C5" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D5" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E5" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F5" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G5" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H5" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I5" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J5" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K5" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L5" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M5" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N5" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O5" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P5" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q5" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C6" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D6" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E6" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F6" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G6" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H6" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I6" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J6" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K6" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L6" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M6" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N6" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O6" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P6" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q6" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C7" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D7" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E7" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F7" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G7" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H7" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I7" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J7" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K7" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L7" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M7" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N7" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O7" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P7" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q7" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C8" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D8" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E8" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F8" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G8" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H8" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I8" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J8" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K8" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L8" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M8" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N8" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O8" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P8" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q8" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C9" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D9" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E9" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F9" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G9" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H9" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I9" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J9" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K9" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L9" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M9" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N9" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O9" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P9" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q9" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C10" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D10" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E10" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F10" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G10" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H10" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I10" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J10" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K10" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L10" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M10" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N10" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O10" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P10" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q10" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C11" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D11" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E11" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F11" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G11" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H11" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I11" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J11" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K11" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L11" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M11" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N11" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O11" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P11" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q11" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C12" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D12" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E12" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F12" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G12" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H12" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I12" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J12" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K12" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L12" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M12" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N12" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O12" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P12" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q12" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C13" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D13" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E13" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F13" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G13" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H13" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I13" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J13" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K13" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L13" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M13" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N13" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O13" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P13" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q13" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C14" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D14" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E14" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F14" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G14" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H14" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I14" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J14" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K14" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L14" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M14" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N14" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O14" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P14" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q14" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C15" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D15" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E15" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F15" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G15" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H15" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I15" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J15" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K15" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L15" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M15" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N15" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O15" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P15" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q15" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C16" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D16" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E16" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F16" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G16" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H16" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I16" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J16" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K16" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L16" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M16" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N16" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O16" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P16" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q16" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C17" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D17" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E17" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F17" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G17" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H17" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I17" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J17" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K17" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L17" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M17" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N17" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O17" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P17" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q17" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C18" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D18" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E18" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F18" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G18" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H18" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I18" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J18" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K18" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L18" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M18" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N18" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O18" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P18" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q18" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C19" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D19" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E19" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F19" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G19" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H19" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I19" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J19" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K19" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L19" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M19" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N19" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O19" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P19" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q19" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C20" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D20" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E20" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F20" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G20" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H20" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I20" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J20" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K20" t="n">
         <v>29701</v>
       </c>
       <c r="L20" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M20" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N20" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O20" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P20" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q20" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C21" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D21" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E21" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F21" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G21" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H21" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I21" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J21" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K21" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L21" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M21" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N21" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O21" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P21" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q21" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34740</v>
+        <v>35012</v>
       </c>
       <c r="C22" t="n">
+        <v>30863</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24368</v>
+      </c>
+      <c r="E22" t="n">
+        <v>18904</v>
+      </c>
+      <c r="F22" t="n">
+        <v>21929</v>
+      </c>
+      <c r="G22" t="n">
+        <v>27796</v>
+      </c>
+      <c r="H22" t="n">
+        <v>28874</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28876</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29349</v>
+      </c>
+      <c r="K22" t="n">
+        <v>29685</v>
+      </c>
+      <c r="L22" t="n">
+        <v>29928</v>
+      </c>
+      <c r="M22" t="n">
+        <v>30105</v>
+      </c>
+      <c r="N22" t="n">
+        <v>30473</v>
+      </c>
+      <c r="O22" t="n">
+        <v>30490</v>
+      </c>
+      <c r="P22" t="n">
+        <v>30480</v>
+      </c>
+      <c r="Q22" t="n">
         <v>30659</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24273</v>
-      </c>
-      <c r="E22" t="n">
-        <v>18916</v>
-      </c>
-      <c r="F22" t="n">
-        <v>21924</v>
-      </c>
-      <c r="G22" t="n">
-        <v>27736</v>
-      </c>
-      <c r="H22" t="n">
-        <v>28828</v>
-      </c>
-      <c r="I22" t="n">
-        <v>28842</v>
-      </c>
-      <c r="J22" t="n">
-        <v>29317</v>
-      </c>
-      <c r="K22" t="n">
-        <v>29653</v>
-      </c>
-      <c r="L22" t="n">
-        <v>29898</v>
-      </c>
-      <c r="M22" t="n">
-        <v>30077</v>
-      </c>
-      <c r="N22" t="n">
-        <v>30454</v>
-      </c>
-      <c r="O22" t="n">
-        <v>30482</v>
-      </c>
-      <c r="P22" t="n">
-        <v>30485</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>30679</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1114 +510,1167 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B2" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O3" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M4" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B5" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M5" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J7" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M7" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O7" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O9" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E10" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I11" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J11" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B14" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J14" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M14" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O14" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E15" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B16" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E16" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B17" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B18" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B19" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L19" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P19" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B20" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M20" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B21" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C21" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K21" t="n">
         <v>2.9701</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M21" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.0452</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.4729</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.9851</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.2407</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.7546</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.8791</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8913</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.9374</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.9701</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.9937</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.011</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.0469</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.0488</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.0486</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.0676</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
         <v>46265</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>3.5012</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>3.0863</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>2.4368</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>1.8904</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>2.1929</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>2.7796</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>2.8874</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>2.8876</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2.9349</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>2.9685</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>2.9928</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>3.0105</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>3.0473</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>3.049</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>3.048</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>3.0659</v>
       </c>
     </row>
@@ -1632,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,1155 +1778,1210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C2" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D2" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E2" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F2" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G2" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H2" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I2" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J2" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K2" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L2" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M2" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N2" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O2" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P2" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q2" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C3" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D3" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E3" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F3" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G3" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H3" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I3" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J3" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K3" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L3" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M3" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N3" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O3" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P3" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q3" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C4" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D4" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E4" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F4" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G4" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H4" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I4" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J4" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K4" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L4" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M4" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N4" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O4" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P4" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q4" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C5" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D5" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E5" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F5" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G5" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H5" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I5" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J5" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K5" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L5" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M5" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N5" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O5" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P5" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q5" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C6" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D6" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E6" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F6" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G6" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H6" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I6" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J6" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K6" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L6" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M6" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N6" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O6" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P6" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q6" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C7" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D7" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E7" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F7" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G7" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H7" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I7" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J7" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K7" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L7" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M7" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N7" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O7" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P7" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q7" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C8" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D8" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E8" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F8" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G8" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H8" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I8" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J8" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K8" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L8" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M8" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N8" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O8" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P8" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q8" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C9" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D9" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E9" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F9" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G9" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H9" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I9" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J9" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K9" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L9" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M9" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N9" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O9" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P9" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q9" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C10" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D10" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E10" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F10" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G10" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H10" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I10" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J10" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K10" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L10" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M10" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N10" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O10" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P10" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q10" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C11" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D11" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E11" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F11" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G11" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H11" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I11" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J11" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K11" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L11" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M11" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N11" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O11" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P11" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q11" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C12" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D12" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E12" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F12" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G12" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H12" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I12" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J12" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K12" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L12" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M12" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N12" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O12" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P12" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q12" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C13" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D13" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E13" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F13" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G13" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H13" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I13" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J13" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K13" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L13" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M13" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N13" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O13" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P13" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q13" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C14" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D14" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E14" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F14" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G14" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H14" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I14" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J14" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K14" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L14" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M14" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N14" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O14" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P14" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q14" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C15" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D15" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E15" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F15" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G15" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H15" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I15" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J15" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K15" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L15" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M15" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N15" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O15" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P15" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q15" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C16" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D16" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E16" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F16" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G16" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H16" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I16" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J16" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K16" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L16" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M16" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N16" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O16" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P16" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q16" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C17" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D17" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E17" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F17" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G17" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H17" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I17" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J17" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K17" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L17" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M17" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N17" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O17" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P17" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q17" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C18" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D18" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E18" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F18" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G18" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H18" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I18" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J18" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K18" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L18" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M18" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N18" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O18" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P18" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q18" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C19" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D19" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E19" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F19" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G19" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H19" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I19" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J19" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K19" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L19" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M19" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N19" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O19" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P19" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q19" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C20" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D20" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E20" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F20" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G20" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H20" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I20" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J20" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K20" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L20" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M20" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N20" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O20" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P20" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q20" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C21" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D21" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E21" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F21" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G21" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H21" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I21" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J21" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K21" t="n">
         <v>29701</v>
       </c>
       <c r="L21" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M21" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N21" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O21" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P21" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q21" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>341</v>
+      </c>
+      <c r="C22" t="n">
+        <v>30452</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24729</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19851</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22407</v>
+      </c>
+      <c r="G22" t="n">
+        <v>27546</v>
+      </c>
+      <c r="H22" t="n">
+        <v>28791</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28913</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29374</v>
+      </c>
+      <c r="K22" t="n">
+        <v>29701</v>
+      </c>
+      <c r="L22" t="n">
+        <v>29937</v>
+      </c>
+      <c r="M22" t="n">
+        <v>30110</v>
+      </c>
+      <c r="N22" t="n">
+        <v>30469</v>
+      </c>
+      <c r="O22" t="n">
+        <v>30488</v>
+      </c>
+      <c r="P22" t="n">
+        <v>30486</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>30676</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>31/08/2026</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>35012</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>30863</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>24368</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>18904</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>21929</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>27796</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>28874</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>28876</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>29349</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>29685</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>29928</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>30105</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>30473</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>30490</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>30480</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>30659</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1168 +510,1168 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B3" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O4" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M5" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B6" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M6" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J8" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M8" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O8" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O10" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E11" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I12" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J12" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B15" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J15" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M15" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O15" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E16" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B17" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E17" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B18" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B19" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B20" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L20" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M20" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P20" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B21" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C21" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M21" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B22" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C22" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J22" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K22" t="n">
         <v>2.9701</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M22" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N22" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O22" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B23" t="n">
-        <v>3.5012</v>
+        <v>3.41</v>
       </c>
       <c r="C23" t="n">
-        <v>3.0863</v>
+        <v>3.0452</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4368</v>
+        <v>2.4729</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8904</v>
+        <v>1.9851</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1929</v>
+        <v>2.2407</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7796</v>
+        <v>2.7546</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8874</v>
+        <v>2.8791</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8876</v>
+        <v>2.8913</v>
       </c>
       <c r="J23" t="n">
-        <v>2.9349</v>
+        <v>2.9374</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9685</v>
+        <v>2.9701</v>
       </c>
       <c r="L23" t="n">
-        <v>2.9928</v>
+        <v>2.9937</v>
       </c>
       <c r="M23" t="n">
-        <v>3.0105</v>
+        <v>3.011</v>
       </c>
       <c r="N23" t="n">
-        <v>3.0473</v>
+        <v>3.0469</v>
       </c>
       <c r="O23" t="n">
-        <v>3.049</v>
+        <v>3.0488</v>
       </c>
       <c r="P23" t="n">
-        <v>3.048</v>
+        <v>3.0486</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.0659</v>
+        <v>3.0676</v>
       </c>
     </row>
   </sheetData>
@@ -1778,1211 +1778,1211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C2" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D2" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E2" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F2" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G2" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H2" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I2" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J2" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K2" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L2" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M2" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N2" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O2" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P2" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q2" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C3" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D3" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E3" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F3" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G3" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H3" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I3" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J3" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K3" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L3" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M3" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N3" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O3" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P3" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q3" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C4" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D4" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E4" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F4" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G4" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H4" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I4" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J4" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K4" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L4" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M4" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N4" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O4" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P4" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q4" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C5" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D5" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E5" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F5" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G5" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H5" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I5" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J5" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K5" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L5" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M5" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N5" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O5" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P5" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q5" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C6" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D6" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E6" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F6" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G6" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H6" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I6" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J6" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K6" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L6" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M6" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N6" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O6" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P6" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q6" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C7" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D7" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E7" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F7" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G7" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H7" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I7" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J7" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K7" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L7" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M7" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N7" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O7" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P7" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q7" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C8" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D8" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E8" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F8" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G8" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H8" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I8" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J8" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K8" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L8" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M8" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N8" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O8" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P8" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q8" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C9" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D9" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E9" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F9" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G9" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H9" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I9" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J9" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K9" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L9" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M9" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N9" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O9" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P9" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q9" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C10" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D10" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E10" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F10" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G10" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H10" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I10" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J10" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K10" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L10" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M10" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N10" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O10" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P10" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q10" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C11" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D11" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E11" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F11" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G11" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H11" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I11" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J11" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K11" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L11" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M11" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N11" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O11" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P11" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q11" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C12" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D12" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E12" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F12" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G12" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H12" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I12" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J12" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K12" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L12" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M12" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N12" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O12" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P12" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q12" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C13" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D13" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E13" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F13" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G13" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H13" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I13" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J13" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K13" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L13" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M13" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N13" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O13" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P13" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q13" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C14" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D14" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E14" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F14" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G14" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H14" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I14" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J14" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K14" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L14" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M14" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N14" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O14" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P14" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q14" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C15" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D15" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E15" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F15" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G15" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H15" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I15" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J15" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K15" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L15" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M15" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N15" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O15" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P15" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q15" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C16" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D16" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E16" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F16" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G16" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H16" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I16" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J16" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K16" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L16" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M16" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N16" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O16" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P16" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q16" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C17" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D17" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E17" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F17" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G17" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H17" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I17" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J17" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K17" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L17" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M17" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N17" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O17" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P17" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q17" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C18" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D18" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E18" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F18" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G18" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H18" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I18" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J18" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K18" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L18" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M18" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N18" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O18" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P18" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q18" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C19" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D19" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E19" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F19" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G19" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H19" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I19" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J19" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K19" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L19" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M19" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N19" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O19" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P19" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q19" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C20" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D20" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E20" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F20" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G20" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H20" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I20" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J20" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K20" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L20" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M20" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N20" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O20" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P20" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q20" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C21" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D21" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E21" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F21" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G21" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H21" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I21" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J21" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K21" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L21" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M21" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N21" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O21" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P21" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q21" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C22" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D22" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E22" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F22" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G22" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H22" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I22" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J22" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K22" t="n">
         <v>29701</v>
       </c>
       <c r="L22" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M22" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N22" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O22" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P22" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q22" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35012</v>
+        <v>341</v>
       </c>
       <c r="C23" t="n">
-        <v>30863</v>
+        <v>30452</v>
       </c>
       <c r="D23" t="n">
-        <v>24368</v>
+        <v>24729</v>
       </c>
       <c r="E23" t="n">
-        <v>18904</v>
+        <v>19851</v>
       </c>
       <c r="F23" t="n">
-        <v>21929</v>
+        <v>22407</v>
       </c>
       <c r="G23" t="n">
-        <v>27796</v>
+        <v>27546</v>
       </c>
       <c r="H23" t="n">
-        <v>28874</v>
+        <v>28791</v>
       </c>
       <c r="I23" t="n">
-        <v>28876</v>
+        <v>28913</v>
       </c>
       <c r="J23" t="n">
-        <v>29349</v>
+        <v>29374</v>
       </c>
       <c r="K23" t="n">
-        <v>29685</v>
+        <v>29701</v>
       </c>
       <c r="L23" t="n">
-        <v>29928</v>
+        <v>29937</v>
       </c>
       <c r="M23" t="n">
-        <v>30105</v>
+        <v>30110</v>
       </c>
       <c r="N23" t="n">
-        <v>30473</v>
+        <v>30469</v>
       </c>
       <c r="O23" t="n">
-        <v>30490</v>
+        <v>30488</v>
       </c>
       <c r="P23" t="n">
-        <v>30480</v>
+        <v>30486</v>
       </c>
       <c r="Q23" t="n">
-        <v>30659</v>
+        <v>30676</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1168 +510,1168 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C2" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F2" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O2" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B4" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O5" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M6" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B7" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M7" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P7" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J9" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M9" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O9" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O11" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E12" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I13" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J13" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B16" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J16" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M16" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O16" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E17" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B18" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E18" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B19" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B20" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M20" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0333</v>
+        <v>3.0263</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B21" t="n">
-        <v>3.2609</v>
+        <v>3.2492</v>
       </c>
       <c r="C21" t="n">
-        <v>2.9522</v>
+        <v>2.9463</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4684</v>
+        <v>2.4714</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0588</v>
+        <v>2.0686</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2825</v>
+        <v>2.2873</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7338</v>
+        <v>2.7304</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8695</v>
+        <v>2.8669</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8913</v>
+        <v>2.8894</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9359</v>
+        <v>2.9336</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9674</v>
+        <v>2.9646</v>
       </c>
       <c r="L21" t="n">
-        <v>2.99</v>
+        <v>2.9867</v>
       </c>
       <c r="M21" t="n">
-        <v>3.0063</v>
+        <v>3.0026</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0378</v>
+        <v>3.0323</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0356</v>
+        <v>3.0283</v>
       </c>
       <c r="P21" t="n">
-        <v>3.031</v>
+        <v>3.0216</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.045</v>
+        <v>3.0333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B22" t="n">
-        <v>3.3104</v>
+        <v>3.2609</v>
       </c>
       <c r="C22" t="n">
-        <v>2.9865</v>
+        <v>2.9522</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4783</v>
+        <v>2.4684</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0453</v>
+        <v>2.0588</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2741</v>
+        <v>2.2825</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7388</v>
+        <v>2.7338</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8723</v>
+        <v>2.8695</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8925</v>
+        <v>2.8913</v>
       </c>
       <c r="J22" t="n">
-        <v>2.9379</v>
+        <v>2.9359</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9701</v>
+        <v>2.9674</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9934</v>
+        <v>2.99</v>
       </c>
       <c r="M22" t="n">
-        <v>3.0104</v>
+        <v>3.0063</v>
       </c>
       <c r="N22" t="n">
-        <v>3.0458</v>
+        <v>3.0378</v>
       </c>
       <c r="O22" t="n">
-        <v>3.0479</v>
+        <v>3.0356</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0483</v>
+        <v>3.031</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.0681</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B23" t="n">
-        <v>3.41</v>
+        <v>3.3104</v>
       </c>
       <c r="C23" t="n">
-        <v>3.0452</v>
+        <v>2.9865</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4729</v>
+        <v>2.4783</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9851</v>
+        <v>2.0453</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2407</v>
+        <v>2.2741</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7546</v>
+        <v>2.7388</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8791</v>
+        <v>2.8723</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8913</v>
+        <v>2.8925</v>
       </c>
       <c r="J23" t="n">
-        <v>2.9374</v>
+        <v>2.9379</v>
       </c>
       <c r="K23" t="n">
         <v>2.9701</v>
       </c>
       <c r="L23" t="n">
-        <v>2.9937</v>
+        <v>2.9934</v>
       </c>
       <c r="M23" t="n">
-        <v>3.011</v>
+        <v>3.0104</v>
       </c>
       <c r="N23" t="n">
-        <v>3.0469</v>
+        <v>3.0458</v>
       </c>
       <c r="O23" t="n">
-        <v>3.0488</v>
+        <v>3.0479</v>
       </c>
       <c r="P23" t="n">
-        <v>3.0486</v>
+        <v>3.0483</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.0676</v>
+        <v>3.0681</v>
       </c>
     </row>
   </sheetData>
@@ -1778,1211 +1778,1211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C2" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D2" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E2" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F2" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G2" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H2" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I2" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J2" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K2" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L2" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M2" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N2" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O2" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P2" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q2" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C3" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D3" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E3" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F3" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G3" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H3" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I3" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J3" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K3" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L3" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M3" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N3" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O3" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P3" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q3" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C4" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D4" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E4" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F4" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G4" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H4" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I4" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J4" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K4" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L4" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M4" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N4" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O4" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P4" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q4" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C5" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D5" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E5" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F5" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G5" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H5" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I5" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J5" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K5" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L5" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M5" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N5" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O5" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P5" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q5" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C6" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D6" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E6" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F6" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G6" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H6" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I6" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J6" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K6" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L6" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M6" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N6" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O6" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P6" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q6" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C7" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D7" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E7" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F7" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G7" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H7" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I7" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J7" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K7" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L7" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M7" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N7" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O7" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P7" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q7" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C8" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D8" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E8" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F8" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G8" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H8" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I8" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J8" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K8" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L8" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M8" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N8" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O8" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P8" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q8" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C9" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D9" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E9" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F9" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G9" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H9" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I9" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J9" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K9" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L9" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M9" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N9" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O9" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P9" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q9" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C10" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D10" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E10" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F10" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G10" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H10" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I10" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J10" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K10" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L10" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M10" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N10" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O10" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P10" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q10" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C11" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D11" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E11" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F11" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G11" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H11" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I11" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J11" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K11" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L11" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M11" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N11" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O11" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P11" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q11" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C12" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D12" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E12" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F12" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G12" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H12" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I12" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J12" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K12" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L12" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M12" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N12" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O12" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P12" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q12" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C13" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D13" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E13" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F13" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G13" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H13" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I13" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J13" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K13" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L13" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M13" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N13" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O13" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P13" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q13" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C14" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D14" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E14" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F14" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G14" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H14" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I14" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J14" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K14" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L14" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M14" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N14" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O14" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P14" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q14" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C15" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D15" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E15" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F15" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G15" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H15" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I15" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J15" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K15" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L15" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M15" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N15" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O15" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P15" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q15" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C16" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D16" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E16" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F16" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G16" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H16" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I16" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J16" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K16" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L16" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M16" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N16" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O16" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P16" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q16" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C17" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D17" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E17" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F17" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G17" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H17" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I17" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J17" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K17" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L17" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M17" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N17" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O17" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P17" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q17" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C18" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D18" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E18" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F18" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G18" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H18" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I18" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J18" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K18" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L18" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M18" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N18" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O18" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P18" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q18" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C19" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D19" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E19" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F19" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G19" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H19" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I19" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J19" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K19" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L19" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M19" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N19" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O19" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P19" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q19" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C20" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D20" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E20" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F20" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G20" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H20" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I20" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J20" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K20" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L20" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M20" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N20" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O20" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P20" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q20" t="n">
-        <v>30333</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32609</v>
+        <v>32492</v>
       </c>
       <c r="C21" t="n">
-        <v>29522</v>
+        <v>29463</v>
       </c>
       <c r="D21" t="n">
-        <v>24684</v>
+        <v>24714</v>
       </c>
       <c r="E21" t="n">
-        <v>20588</v>
+        <v>20686</v>
       </c>
       <c r="F21" t="n">
-        <v>22825</v>
+        <v>22873</v>
       </c>
       <c r="G21" t="n">
-        <v>27338</v>
+        <v>27304</v>
       </c>
       <c r="H21" t="n">
-        <v>28695</v>
+        <v>28669</v>
       </c>
       <c r="I21" t="n">
-        <v>28913</v>
+        <v>28894</v>
       </c>
       <c r="J21" t="n">
-        <v>29359</v>
+        <v>29336</v>
       </c>
       <c r="K21" t="n">
-        <v>29674</v>
+        <v>29646</v>
       </c>
       <c r="L21" t="n">
-        <v>299</v>
+        <v>29867</v>
       </c>
       <c r="M21" t="n">
-        <v>30063</v>
+        <v>30026</v>
       </c>
       <c r="N21" t="n">
-        <v>30378</v>
+        <v>30323</v>
       </c>
       <c r="O21" t="n">
-        <v>30356</v>
+        <v>30283</v>
       </c>
       <c r="P21" t="n">
-        <v>30310</v>
+        <v>30216</v>
       </c>
       <c r="Q21" t="n">
-        <v>30450</v>
+        <v>30333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33104</v>
+        <v>32609</v>
       </c>
       <c r="C22" t="n">
-        <v>29865</v>
+        <v>29522</v>
       </c>
       <c r="D22" t="n">
-        <v>24783</v>
+        <v>24684</v>
       </c>
       <c r="E22" t="n">
-        <v>20453</v>
+        <v>20588</v>
       </c>
       <c r="F22" t="n">
-        <v>22741</v>
+        <v>22825</v>
       </c>
       <c r="G22" t="n">
-        <v>27388</v>
+        <v>27338</v>
       </c>
       <c r="H22" t="n">
-        <v>28723</v>
+        <v>28695</v>
       </c>
       <c r="I22" t="n">
-        <v>28925</v>
+        <v>28913</v>
       </c>
       <c r="J22" t="n">
-        <v>29379</v>
+        <v>29359</v>
       </c>
       <c r="K22" t="n">
-        <v>29701</v>
+        <v>29674</v>
       </c>
       <c r="L22" t="n">
-        <v>29934</v>
+        <v>299</v>
       </c>
       <c r="M22" t="n">
-        <v>30104</v>
+        <v>30063</v>
       </c>
       <c r="N22" t="n">
-        <v>30458</v>
+        <v>30378</v>
       </c>
       <c r="O22" t="n">
-        <v>30479</v>
+        <v>30356</v>
       </c>
       <c r="P22" t="n">
-        <v>30483</v>
+        <v>30310</v>
       </c>
       <c r="Q22" t="n">
-        <v>30681</v>
+        <v>30450</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>341</v>
+        <v>33104</v>
       </c>
       <c r="C23" t="n">
-        <v>30452</v>
+        <v>29865</v>
       </c>
       <c r="D23" t="n">
-        <v>24729</v>
+        <v>24783</v>
       </c>
       <c r="E23" t="n">
-        <v>19851</v>
+        <v>20453</v>
       </c>
       <c r="F23" t="n">
-        <v>22407</v>
+        <v>22741</v>
       </c>
       <c r="G23" t="n">
-        <v>27546</v>
+        <v>27388</v>
       </c>
       <c r="H23" t="n">
-        <v>28791</v>
+        <v>28723</v>
       </c>
       <c r="I23" t="n">
-        <v>28913</v>
+        <v>28925</v>
       </c>
       <c r="J23" t="n">
-        <v>29374</v>
+        <v>29379</v>
       </c>
       <c r="K23" t="n">
         <v>29701</v>
       </c>
       <c r="L23" t="n">
-        <v>29937</v>
+        <v>29934</v>
       </c>
       <c r="M23" t="n">
-        <v>30110</v>
+        <v>30104</v>
       </c>
       <c r="N23" t="n">
-        <v>30469</v>
+        <v>30458</v>
       </c>
       <c r="O23" t="n">
-        <v>30488</v>
+        <v>30479</v>
       </c>
       <c r="P23" t="n">
-        <v>30486</v>
+        <v>30483</v>
       </c>
       <c r="Q23" t="n">
-        <v>30676</v>
+        <v>30681</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1168 +510,1062 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L2" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O2" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C3" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F3" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O3" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B4" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B5" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O6" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M7" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B8" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M8" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P8" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J10" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M10" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O10" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P11" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O12" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E13" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I14" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J14" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B17" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J17" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M17" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O17" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E18" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B19" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E19" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B20" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B21" t="n">
-        <v>3.2492</v>
+        <v>3.2292</v>
       </c>
       <c r="C21" t="n">
-        <v>2.9463</v>
+        <v>2.9296</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4714</v>
+        <v>2.4604</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0686</v>
+        <v>2.0651</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2873</v>
+        <v>2.2868</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7304</v>
+        <v>2.7301</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8669</v>
+        <v>2.8639</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8894</v>
+        <v>2.8858</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9336</v>
+        <v>2.9299</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9646</v>
+        <v>2.9607</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9867</v>
+        <v>2.9827</v>
       </c>
       <c r="M21" t="n">
-        <v>3.0026</v>
+        <v>2.9985</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0323</v>
+        <v>3.0276</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0283</v>
+        <v>3.0229</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0216</v>
+        <v>3.0155</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0333</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3.2609</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.9522</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.4684</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.0588</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.2825</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.7338</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.8695</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8913</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.9359</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.9674</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.0063</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.0378</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.0356</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.031</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.045</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3.3104</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.9865</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.4783</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.0453</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.2741</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.7388</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.8723</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.8925</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.9379</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.9701</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.9934</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.0104</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.0458</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.0479</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.0483</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.0681</v>
+        <v>3.0263</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,1211 +1672,1101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C2" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D2" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E2" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F2" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G2" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H2" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I2" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J2" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K2" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L2" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M2" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N2" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O2" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P2" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q2" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C3" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D3" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E3" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F3" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G3" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H3" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I3" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J3" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K3" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L3" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M3" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N3" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O3" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P3" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q3" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C4" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D4" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E4" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F4" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G4" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H4" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I4" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J4" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K4" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L4" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M4" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N4" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O4" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P4" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q4" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C5" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D5" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E5" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F5" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G5" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H5" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I5" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J5" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K5" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L5" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M5" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N5" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O5" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P5" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q5" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C6" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D6" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E6" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F6" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G6" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H6" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I6" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J6" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K6" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L6" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M6" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N6" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O6" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P6" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q6" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C7" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D7" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E7" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F7" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G7" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H7" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I7" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J7" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K7" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L7" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M7" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N7" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O7" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P7" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q7" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C8" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D8" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E8" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F8" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G8" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H8" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I8" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J8" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K8" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L8" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M8" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N8" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O8" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P8" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q8" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C9" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D9" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E9" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F9" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G9" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H9" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I9" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J9" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K9" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L9" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M9" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N9" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O9" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P9" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q9" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C10" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D10" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E10" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F10" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G10" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H10" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I10" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J10" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K10" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L10" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M10" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N10" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O10" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P10" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q10" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C11" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D11" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E11" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F11" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G11" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H11" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I11" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J11" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K11" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L11" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M11" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N11" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O11" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P11" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q11" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C12" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D12" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E12" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F12" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G12" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H12" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I12" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J12" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K12" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L12" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M12" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N12" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O12" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P12" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q12" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C13" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D13" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E13" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F13" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G13" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H13" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I13" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J13" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K13" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L13" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M13" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N13" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O13" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P13" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q13" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C14" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D14" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E14" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F14" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G14" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H14" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I14" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J14" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K14" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L14" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M14" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N14" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O14" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P14" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q14" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C15" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D15" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E15" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F15" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G15" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H15" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I15" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J15" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K15" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L15" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M15" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N15" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O15" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P15" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q15" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C16" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D16" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E16" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F16" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G16" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H16" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I16" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J16" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K16" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L16" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M16" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N16" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O16" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P16" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q16" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C17" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D17" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E17" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F17" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G17" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H17" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I17" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J17" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K17" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L17" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M17" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N17" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O17" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P17" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q17" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C18" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D18" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E18" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F18" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G18" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H18" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I18" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J18" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K18" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L18" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M18" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N18" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O18" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P18" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q18" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C19" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D19" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E19" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F19" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G19" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H19" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I19" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J19" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K19" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L19" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M19" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N19" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O19" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P19" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q19" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C20" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D20" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E20" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F20" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G20" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H20" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I20" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J20" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K20" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L20" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M20" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N20" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O20" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P20" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q20" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32492</v>
+        <v>32292</v>
       </c>
       <c r="C21" t="n">
-        <v>29463</v>
+        <v>29296</v>
       </c>
       <c r="D21" t="n">
-        <v>24714</v>
+        <v>24604</v>
       </c>
       <c r="E21" t="n">
-        <v>20686</v>
+        <v>20651</v>
       </c>
       <c r="F21" t="n">
-        <v>22873</v>
+        <v>22868</v>
       </c>
       <c r="G21" t="n">
-        <v>27304</v>
+        <v>27301</v>
       </c>
       <c r="H21" t="n">
-        <v>28669</v>
+        <v>28639</v>
       </c>
       <c r="I21" t="n">
-        <v>28894</v>
+        <v>28858</v>
       </c>
       <c r="J21" t="n">
-        <v>29336</v>
+        <v>29299</v>
       </c>
       <c r="K21" t="n">
-        <v>29646</v>
+        <v>29607</v>
       </c>
       <c r="L21" t="n">
-        <v>29867</v>
+        <v>29827</v>
       </c>
       <c r="M21" t="n">
-        <v>30026</v>
+        <v>29985</v>
       </c>
       <c r="N21" t="n">
-        <v>30323</v>
+        <v>30276</v>
       </c>
       <c r="O21" t="n">
-        <v>30283</v>
+        <v>30229</v>
       </c>
       <c r="P21" t="n">
-        <v>30216</v>
+        <v>30155</v>
       </c>
       <c r="Q21" t="n">
-        <v>30333</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>03/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>32609</v>
-      </c>
-      <c r="C22" t="n">
-        <v>29522</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24684</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20588</v>
-      </c>
-      <c r="F22" t="n">
-        <v>22825</v>
-      </c>
-      <c r="G22" t="n">
-        <v>27338</v>
-      </c>
-      <c r="H22" t="n">
-        <v>28695</v>
-      </c>
-      <c r="I22" t="n">
-        <v>28913</v>
-      </c>
-      <c r="J22" t="n">
-        <v>29359</v>
-      </c>
-      <c r="K22" t="n">
-        <v>29674</v>
-      </c>
-      <c r="L22" t="n">
-        <v>299</v>
-      </c>
-      <c r="M22" t="n">
-        <v>30063</v>
-      </c>
-      <c r="N22" t="n">
-        <v>30378</v>
-      </c>
-      <c r="O22" t="n">
-        <v>30356</v>
-      </c>
-      <c r="P22" t="n">
-        <v>30310</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>30450</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>33104</v>
-      </c>
-      <c r="C23" t="n">
-        <v>29865</v>
-      </c>
-      <c r="D23" t="n">
-        <v>24783</v>
-      </c>
-      <c r="E23" t="n">
-        <v>20453</v>
-      </c>
-      <c r="F23" t="n">
-        <v>22741</v>
-      </c>
-      <c r="G23" t="n">
-        <v>27388</v>
-      </c>
-      <c r="H23" t="n">
-        <v>28723</v>
-      </c>
-      <c r="I23" t="n">
-        <v>28925</v>
-      </c>
-      <c r="J23" t="n">
-        <v>29379</v>
-      </c>
-      <c r="K23" t="n">
-        <v>29701</v>
-      </c>
-      <c r="L23" t="n">
-        <v>29934</v>
-      </c>
-      <c r="M23" t="n">
-        <v>30104</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30458</v>
-      </c>
-      <c r="O23" t="n">
-        <v>30479</v>
-      </c>
-      <c r="P23" t="n">
-        <v>30483</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>30681</v>
+        <v>30263</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1061 +510,1114 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M2" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L3" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O3" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C4" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F4" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O4" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B5" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B6" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B7" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O7" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M8" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B9" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M9" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J11" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M11" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O11" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P11" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O13" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E14" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I15" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J15" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B18" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J18" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M18" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O18" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E19" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B20" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E20" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.212</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.9217</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.4659</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2759</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.6969</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.8479</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8777</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.9229</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9547</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.9773</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.9936</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.0239</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.0193</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.0115</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.0216</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>46272</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>3.2292</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>2.9296</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>2.4604</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>2.0651</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>2.2868</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>2.7301</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>2.8639</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>2.8858</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2.9299</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2.9607</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>2.9827</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>2.9985</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>3.0276</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>3.0229</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>3.0155</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>3.0263</v>
       </c>
     </row>
@@ -1579,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,1100 +1725,1155 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C2" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D2" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E2" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F2" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G2" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H2" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I2" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J2" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K2" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L2" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M2" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N2" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O2" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P2" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q2" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C3" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D3" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E3" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F3" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G3" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H3" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I3" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J3" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K3" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L3" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M3" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N3" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O3" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P3" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q3" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C4" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D4" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E4" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F4" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G4" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H4" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I4" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J4" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K4" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L4" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M4" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N4" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O4" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P4" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q4" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C5" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D5" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E5" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F5" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G5" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H5" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I5" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J5" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K5" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L5" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M5" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N5" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O5" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P5" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q5" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C6" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D6" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E6" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F6" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G6" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H6" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I6" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J6" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K6" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L6" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M6" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N6" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O6" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P6" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q6" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C7" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D7" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E7" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F7" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G7" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H7" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I7" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J7" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K7" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L7" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M7" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N7" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O7" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P7" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q7" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C8" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D8" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E8" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F8" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G8" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H8" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I8" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J8" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K8" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L8" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M8" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N8" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O8" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P8" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q8" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C9" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D9" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E9" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F9" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G9" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H9" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I9" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J9" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K9" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L9" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M9" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N9" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O9" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P9" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q9" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C10" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D10" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E10" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F10" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G10" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H10" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I10" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J10" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K10" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L10" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M10" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N10" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O10" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P10" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q10" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C11" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D11" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E11" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F11" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G11" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H11" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I11" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J11" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K11" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L11" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M11" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N11" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O11" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P11" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q11" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C12" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D12" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E12" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F12" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G12" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H12" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I12" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J12" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K12" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L12" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M12" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N12" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O12" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P12" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q12" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C13" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D13" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E13" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F13" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G13" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H13" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I13" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J13" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K13" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L13" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M13" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N13" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O13" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P13" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q13" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C14" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D14" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E14" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F14" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G14" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H14" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I14" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J14" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K14" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L14" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M14" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N14" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O14" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P14" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q14" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C15" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D15" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E15" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F15" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G15" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H15" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I15" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J15" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K15" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L15" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M15" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N15" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O15" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P15" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q15" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C16" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D16" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E16" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F16" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G16" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H16" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I16" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J16" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K16" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L16" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M16" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N16" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O16" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P16" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q16" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C17" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D17" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E17" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F17" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G17" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H17" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I17" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J17" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K17" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L17" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M17" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N17" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O17" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P17" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q17" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C18" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D18" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E18" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F18" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G18" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H18" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I18" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J18" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K18" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L18" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M18" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N18" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O18" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P18" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q18" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C19" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D19" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E19" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F19" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G19" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H19" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I19" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J19" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K19" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L19" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M19" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N19" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O19" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P19" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q19" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C20" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D20" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E20" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F20" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G20" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H20" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I20" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J20" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K20" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L20" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M20" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N20" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O20" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P20" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q20" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>32120</v>
+      </c>
+      <c r="C21" t="n">
+        <v>29217</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24659</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20750</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22759</v>
+      </c>
+      <c r="G21" t="n">
+        <v>26969</v>
+      </c>
+      <c r="H21" t="n">
+        <v>28479</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28777</v>
+      </c>
+      <c r="J21" t="n">
+        <v>29229</v>
+      </c>
+      <c r="K21" t="n">
+        <v>29547</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29773</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29936</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30239</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30193</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30115</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>30216</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>32292</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>29296</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>24604</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>20651</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>22868</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>27301</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>28639</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>28858</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>29299</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>29607</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>29827</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>29985</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>30276</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>30229</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>30155</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>30263</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1114 +510,1167 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N2" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P2" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M3" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L4" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O4" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C5" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F5" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O5" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B6" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B7" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O8" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M9" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B10" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M10" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P11" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J12" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M12" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O12" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O14" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E15" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I16" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J16" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B19" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J19" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M19" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O19" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E20" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B21" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C21" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E21" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.212</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.9217</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.4659</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.2759</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.6969</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.8479</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8777</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.9229</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.9547</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.9773</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.9936</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.0239</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.0193</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.0115</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.0216</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
         <v>46272</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>3.2292</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>2.9296</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>2.4604</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>2.0651</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>2.2868</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>2.7301</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>2.8639</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>2.8858</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2.9299</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>2.9607</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>2.9827</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>2.9985</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>3.0276</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>3.0229</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>3.0155</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>3.0263</v>
       </c>
     </row>
@@ -1632,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,1155 +1778,1210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C2" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D2" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E2" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F2" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G2" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H2" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I2" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J2" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K2" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L2" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M2" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N2" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O2" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P2" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q2" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C3" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D3" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E3" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F3" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G3" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H3" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I3" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J3" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K3" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L3" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M3" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N3" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O3" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P3" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q3" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C4" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D4" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E4" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F4" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G4" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H4" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I4" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J4" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K4" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L4" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M4" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N4" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O4" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P4" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q4" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C5" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D5" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E5" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F5" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G5" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H5" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I5" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J5" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K5" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L5" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M5" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N5" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O5" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P5" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q5" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C6" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D6" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E6" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F6" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G6" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H6" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I6" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J6" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K6" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L6" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M6" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N6" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O6" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P6" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q6" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C7" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D7" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E7" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F7" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G7" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H7" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I7" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J7" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K7" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L7" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M7" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N7" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O7" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P7" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q7" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C8" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D8" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E8" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F8" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G8" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H8" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I8" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J8" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K8" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L8" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M8" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N8" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O8" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P8" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q8" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C9" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D9" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E9" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F9" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G9" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H9" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I9" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J9" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K9" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L9" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M9" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N9" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O9" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P9" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q9" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C10" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D10" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E10" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F10" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G10" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H10" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I10" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J10" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K10" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L10" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M10" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N10" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O10" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P10" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q10" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C11" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D11" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E11" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F11" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G11" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H11" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I11" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J11" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K11" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L11" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M11" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N11" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O11" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P11" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q11" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C12" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D12" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E12" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F12" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G12" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H12" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I12" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J12" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K12" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L12" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M12" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N12" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O12" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P12" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q12" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C13" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D13" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E13" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F13" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G13" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H13" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I13" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J13" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K13" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L13" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M13" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N13" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O13" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P13" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q13" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C14" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D14" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E14" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F14" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G14" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H14" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I14" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J14" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K14" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L14" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M14" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N14" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O14" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P14" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q14" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C15" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D15" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E15" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F15" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G15" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H15" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I15" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J15" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K15" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L15" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M15" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N15" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O15" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P15" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q15" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C16" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D16" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E16" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F16" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G16" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H16" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I16" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J16" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K16" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L16" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M16" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N16" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O16" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P16" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q16" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C17" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D17" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E17" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F17" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G17" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H17" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I17" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J17" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K17" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L17" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M17" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N17" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O17" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P17" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q17" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C18" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D18" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E18" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F18" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G18" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H18" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I18" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J18" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K18" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L18" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M18" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N18" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O18" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P18" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q18" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C19" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D19" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E19" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F19" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G19" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H19" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I19" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J19" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K19" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L19" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M19" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N19" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O19" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P19" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q19" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C20" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D20" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E20" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F20" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G20" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H20" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I20" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J20" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K20" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L20" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M20" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N20" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O20" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P20" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q20" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C21" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D21" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E21" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F21" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G21" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H21" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I21" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J21" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K21" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L21" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M21" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N21" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O21" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P21" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q21" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>32120</v>
+      </c>
+      <c r="C22" t="n">
+        <v>29217</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24659</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20750</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22759</v>
+      </c>
+      <c r="G22" t="n">
+        <v>26969</v>
+      </c>
+      <c r="H22" t="n">
+        <v>28479</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28777</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29229</v>
+      </c>
+      <c r="K22" t="n">
+        <v>29547</v>
+      </c>
+      <c r="L22" t="n">
+        <v>29773</v>
+      </c>
+      <c r="M22" t="n">
+        <v>29936</v>
+      </c>
+      <c r="N22" t="n">
+        <v>30239</v>
+      </c>
+      <c r="O22" t="n">
+        <v>30193</v>
+      </c>
+      <c r="P22" t="n">
+        <v>30115</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>30216</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/09/2026</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
         <v>32292</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C23" t="n">
         <v>29296</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>24604</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>20651</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>22868</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>27301</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>28639</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>28858</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>29299</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>29607</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>29827</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>29985</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>30276</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>30229</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>30155</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>30263</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1168 +510,1168 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B2" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E2" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I2" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P2" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N3" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P3" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M4" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L5" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O5" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C6" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F6" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O6" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B7" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B8" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B9" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O9" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M10" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B11" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M11" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P11" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O12" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J13" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M13" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O13" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O15" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E16" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I17" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J17" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B20" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J20" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M20" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O20" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B21" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C21" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E21" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B22" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C22" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E22" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J22" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N22" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O22" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B23" t="n">
-        <v>3.2292</v>
+        <v>3.212</v>
       </c>
       <c r="C23" t="n">
-        <v>2.9296</v>
+        <v>2.9217</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4604</v>
+        <v>2.4659</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0651</v>
+        <v>2.075</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2868</v>
+        <v>2.2759</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7301</v>
+        <v>2.6969</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8639</v>
+        <v>2.8479</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8858</v>
+        <v>2.8777</v>
       </c>
       <c r="J23" t="n">
-        <v>2.9299</v>
+        <v>2.9229</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9607</v>
+        <v>2.9547</v>
       </c>
       <c r="L23" t="n">
-        <v>2.9827</v>
+        <v>2.9773</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9985</v>
+        <v>2.9936</v>
       </c>
       <c r="N23" t="n">
-        <v>3.0276</v>
+        <v>3.0239</v>
       </c>
       <c r="O23" t="n">
-        <v>3.0229</v>
+        <v>3.0193</v>
       </c>
       <c r="P23" t="n">
-        <v>3.0155</v>
+        <v>3.0115</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.0263</v>
+        <v>3.0216</v>
       </c>
     </row>
   </sheetData>
@@ -1778,1211 +1778,1211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C2" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D2" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E2" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F2" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G2" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H2" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I2" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J2" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K2" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L2" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M2" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N2" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O2" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P2" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q2" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C3" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D3" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E3" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F3" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G3" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H3" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I3" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J3" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K3" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L3" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M3" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N3" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O3" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P3" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q3" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C4" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D4" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E4" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F4" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G4" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H4" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I4" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J4" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K4" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L4" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M4" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N4" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O4" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P4" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q4" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C5" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D5" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E5" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F5" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G5" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H5" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I5" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J5" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K5" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L5" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M5" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N5" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O5" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P5" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q5" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C6" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D6" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E6" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F6" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G6" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H6" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I6" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J6" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K6" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L6" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M6" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N6" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O6" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P6" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q6" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C7" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D7" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E7" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F7" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G7" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H7" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I7" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J7" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K7" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L7" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M7" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N7" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O7" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P7" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q7" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C8" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D8" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E8" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F8" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G8" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H8" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I8" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J8" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K8" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L8" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M8" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N8" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O8" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P8" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q8" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C9" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D9" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E9" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F9" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G9" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H9" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I9" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J9" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K9" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L9" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M9" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N9" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O9" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P9" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q9" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C10" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D10" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E10" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F10" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G10" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H10" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I10" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J10" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K10" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L10" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M10" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N10" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O10" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P10" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q10" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C11" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D11" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E11" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F11" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G11" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H11" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I11" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J11" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K11" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L11" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M11" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N11" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O11" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P11" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q11" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C12" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D12" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E12" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F12" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G12" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H12" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I12" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J12" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K12" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L12" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M12" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N12" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O12" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P12" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q12" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C13" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D13" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E13" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F13" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G13" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H13" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I13" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J13" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K13" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L13" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M13" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N13" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O13" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P13" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q13" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C14" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D14" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E14" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F14" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G14" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H14" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I14" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J14" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K14" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L14" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M14" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N14" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O14" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P14" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q14" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C15" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D15" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E15" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F15" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G15" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H15" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I15" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J15" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K15" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L15" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M15" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N15" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O15" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P15" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q15" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C16" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D16" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E16" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F16" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G16" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H16" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I16" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J16" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K16" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L16" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M16" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N16" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O16" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P16" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q16" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C17" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D17" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E17" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F17" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G17" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H17" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I17" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J17" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K17" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L17" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M17" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N17" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O17" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P17" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q17" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C18" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D18" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E18" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F18" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G18" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H18" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I18" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J18" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K18" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L18" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M18" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N18" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O18" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P18" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q18" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C19" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D19" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E19" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F19" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G19" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H19" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I19" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J19" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K19" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L19" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M19" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N19" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O19" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P19" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q19" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C20" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D20" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E20" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F20" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G20" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H20" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I20" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J20" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K20" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L20" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M20" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N20" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O20" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P20" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q20" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C21" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D21" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E21" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F21" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G21" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H21" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I21" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J21" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K21" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L21" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M21" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N21" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O21" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P21" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q21" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C22" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D22" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E22" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F22" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G22" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H22" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I22" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J22" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K22" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L22" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M22" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N22" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O22" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P22" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q22" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32292</v>
+        <v>32120</v>
       </c>
       <c r="C23" t="n">
-        <v>29296</v>
+        <v>29217</v>
       </c>
       <c r="D23" t="n">
-        <v>24604</v>
+        <v>24659</v>
       </c>
       <c r="E23" t="n">
-        <v>20651</v>
+        <v>20750</v>
       </c>
       <c r="F23" t="n">
-        <v>22868</v>
+        <v>22759</v>
       </c>
       <c r="G23" t="n">
-        <v>27301</v>
+        <v>26969</v>
       </c>
       <c r="H23" t="n">
-        <v>28639</v>
+        <v>28479</v>
       </c>
       <c r="I23" t="n">
-        <v>28858</v>
+        <v>28777</v>
       </c>
       <c r="J23" t="n">
-        <v>29299</v>
+        <v>29229</v>
       </c>
       <c r="K23" t="n">
-        <v>29607</v>
+        <v>29547</v>
       </c>
       <c r="L23" t="n">
-        <v>29827</v>
+        <v>29773</v>
       </c>
       <c r="M23" t="n">
-        <v>29985</v>
+        <v>29936</v>
       </c>
       <c r="N23" t="n">
-        <v>30276</v>
+        <v>30239</v>
       </c>
       <c r="O23" t="n">
-        <v>30229</v>
+        <v>30193</v>
       </c>
       <c r="P23" t="n">
-        <v>30155</v>
+        <v>30115</v>
       </c>
       <c r="Q23" t="n">
-        <v>30263</v>
+        <v>30216</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1168 +510,1168 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C2" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G2" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B3" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E3" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I3" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P3" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N4" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P4" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M5" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L6" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O6" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C7" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F7" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O7" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B8" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B9" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C9" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B10" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O10" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M11" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B12" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M12" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O12" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J14" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M14" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O14" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O16" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E17" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I18" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J18" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1865</v>
+        <v>3.1676</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9053</v>
+        <v>2.8911</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4611</v>
+        <v>2.4537</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0671</v>
+        <v>2.0628</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2352</v>
+        <v>2.2221</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6255</v>
+        <v>2.6031</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8096</v>
+        <v>2.7977</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8545</v>
+        <v>2.8478</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9034</v>
+        <v>2.8982</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9379</v>
+        <v>2.9338</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9628</v>
+        <v>2.9595</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9808</v>
+        <v>2.9782</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0166</v>
+        <v>3.0161</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0152</v>
+        <v>3.0156</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0098</v>
+        <v>3.0106</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0218</v>
+        <v>3.023</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B21" t="n">
-        <v>3.193</v>
+        <v>3.1865</v>
       </c>
       <c r="C21" t="n">
-        <v>2.9037</v>
+        <v>2.9053</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4493</v>
+        <v>2.4611</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0586</v>
+        <v>2.0671</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2566</v>
+        <v>2.2352</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6752</v>
+        <v>2.6255</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8318</v>
+        <v>2.8096</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8645</v>
+        <v>2.8545</v>
       </c>
       <c r="J21" t="n">
-        <v>2.911</v>
+        <v>2.9034</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9436</v>
+        <v>2.9379</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9671</v>
+        <v>2.9628</v>
       </c>
       <c r="M21" t="n">
-        <v>2.984</v>
+        <v>2.9808</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0167</v>
+        <v>3.0166</v>
       </c>
       <c r="O21" t="n">
-        <v>3.014</v>
+        <v>3.0152</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0081</v>
+        <v>3.0098</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0199</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B22" t="n">
-        <v>3.1936</v>
+        <v>3.193</v>
       </c>
       <c r="C22" t="n">
-        <v>2.9089</v>
+        <v>2.9037</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4615</v>
+        <v>2.4493</v>
       </c>
       <c r="E22" t="n">
-        <v>2.076</v>
+        <v>2.0586</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2695</v>
+        <v>2.2566</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6811</v>
+        <v>2.6752</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8379</v>
+        <v>2.8318</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8709</v>
+        <v>2.8645</v>
       </c>
       <c r="J22" t="n">
-        <v>2.9166</v>
+        <v>2.911</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9487</v>
+        <v>2.9436</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9717</v>
+        <v>2.9671</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9882</v>
+        <v>2.984</v>
       </c>
       <c r="N22" t="n">
-        <v>3.0192</v>
+        <v>3.0167</v>
       </c>
       <c r="O22" t="n">
-        <v>3.0151</v>
+        <v>3.014</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0077</v>
+        <v>3.0081</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.018</v>
+        <v>3.0199</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B23" t="n">
-        <v>3.212</v>
+        <v>3.1936</v>
       </c>
       <c r="C23" t="n">
-        <v>2.9217</v>
+        <v>2.9089</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4659</v>
+        <v>2.4615</v>
       </c>
       <c r="E23" t="n">
-        <v>2.075</v>
+        <v>2.076</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2759</v>
+        <v>2.2695</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6969</v>
+        <v>2.6811</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8479</v>
+        <v>2.8379</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8777</v>
+        <v>2.8709</v>
       </c>
       <c r="J23" t="n">
-        <v>2.9229</v>
+        <v>2.9166</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9547</v>
+        <v>2.9487</v>
       </c>
       <c r="L23" t="n">
-        <v>2.9773</v>
+        <v>2.9717</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9936</v>
+        <v>2.9882</v>
       </c>
       <c r="N23" t="n">
-        <v>3.0239</v>
+        <v>3.0192</v>
       </c>
       <c r="O23" t="n">
-        <v>3.0193</v>
+        <v>3.0151</v>
       </c>
       <c r="P23" t="n">
-        <v>3.0115</v>
+        <v>3.0077</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.0216</v>
+        <v>3.018</v>
       </c>
     </row>
   </sheetData>
@@ -1778,1211 +1778,1211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C2" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D2" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E2" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F2" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G2" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H2" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I2" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J2" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K2" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L2" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M2" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N2" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O2" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P2" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q2" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C3" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D3" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E3" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F3" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G3" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H3" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I3" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J3" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K3" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L3" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M3" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N3" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O3" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P3" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q3" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C4" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D4" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E4" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F4" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G4" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H4" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I4" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J4" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K4" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L4" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M4" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N4" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O4" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P4" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q4" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C5" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D5" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E5" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F5" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G5" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H5" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I5" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J5" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K5" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L5" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M5" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N5" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O5" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P5" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q5" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C6" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D6" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E6" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F6" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G6" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H6" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I6" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J6" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K6" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L6" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M6" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N6" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O6" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P6" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q6" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C7" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D7" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E7" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F7" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G7" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H7" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I7" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J7" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K7" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L7" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M7" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N7" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O7" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P7" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q7" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C8" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D8" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E8" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F8" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G8" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H8" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I8" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J8" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K8" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L8" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M8" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N8" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O8" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P8" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q8" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C9" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D9" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E9" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F9" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G9" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H9" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I9" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J9" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K9" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L9" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M9" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N9" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O9" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P9" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q9" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C10" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D10" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E10" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F10" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G10" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H10" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I10" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J10" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K10" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L10" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M10" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N10" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O10" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P10" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q10" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C11" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D11" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E11" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F11" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G11" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H11" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I11" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J11" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K11" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L11" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M11" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N11" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O11" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P11" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q11" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C12" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D12" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E12" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F12" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G12" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H12" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I12" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J12" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K12" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L12" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M12" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N12" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O12" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P12" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q12" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C13" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D13" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E13" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F13" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G13" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H13" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I13" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J13" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K13" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L13" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M13" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N13" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O13" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P13" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q13" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C14" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D14" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E14" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F14" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G14" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H14" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I14" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J14" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K14" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L14" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M14" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N14" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O14" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P14" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q14" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C15" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D15" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E15" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F15" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G15" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H15" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I15" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J15" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K15" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L15" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M15" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N15" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O15" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P15" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q15" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C16" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D16" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E16" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F16" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G16" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H16" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I16" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J16" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K16" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L16" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M16" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N16" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O16" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P16" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q16" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C17" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D17" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E17" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F17" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G17" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H17" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I17" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J17" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K17" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L17" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M17" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N17" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O17" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P17" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q17" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C18" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D18" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E18" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F18" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G18" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H18" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I18" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J18" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K18" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L18" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M18" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N18" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O18" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P18" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q18" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C19" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D19" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E19" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F19" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G19" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H19" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I19" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J19" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K19" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L19" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M19" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N19" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O19" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P19" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q19" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31865</v>
+        <v>31676</v>
       </c>
       <c r="C20" t="n">
-        <v>29053</v>
+        <v>28911</v>
       </c>
       <c r="D20" t="n">
-        <v>24611</v>
+        <v>24537</v>
       </c>
       <c r="E20" t="n">
-        <v>20671</v>
+        <v>20628</v>
       </c>
       <c r="F20" t="n">
-        <v>22352</v>
+        <v>22221</v>
       </c>
       <c r="G20" t="n">
-        <v>26255</v>
+        <v>26031</v>
       </c>
       <c r="H20" t="n">
-        <v>28096</v>
+        <v>27977</v>
       </c>
       <c r="I20" t="n">
-        <v>28545</v>
+        <v>28478</v>
       </c>
       <c r="J20" t="n">
-        <v>29034</v>
+        <v>28982</v>
       </c>
       <c r="K20" t="n">
-        <v>29379</v>
+        <v>29338</v>
       </c>
       <c r="L20" t="n">
-        <v>29628</v>
+        <v>29595</v>
       </c>
       <c r="M20" t="n">
-        <v>29808</v>
+        <v>29782</v>
       </c>
       <c r="N20" t="n">
-        <v>30166</v>
+        <v>30161</v>
       </c>
       <c r="O20" t="n">
-        <v>30152</v>
+        <v>30156</v>
       </c>
       <c r="P20" t="n">
-        <v>30098</v>
+        <v>30106</v>
       </c>
       <c r="Q20" t="n">
-        <v>30218</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31930</v>
+        <v>31865</v>
       </c>
       <c r="C21" t="n">
-        <v>29037</v>
+        <v>29053</v>
       </c>
       <c r="D21" t="n">
-        <v>24493</v>
+        <v>24611</v>
       </c>
       <c r="E21" t="n">
-        <v>20586</v>
+        <v>20671</v>
       </c>
       <c r="F21" t="n">
-        <v>22566</v>
+        <v>22352</v>
       </c>
       <c r="G21" t="n">
-        <v>26752</v>
+        <v>26255</v>
       </c>
       <c r="H21" t="n">
-        <v>28318</v>
+        <v>28096</v>
       </c>
       <c r="I21" t="n">
-        <v>28645</v>
+        <v>28545</v>
       </c>
       <c r="J21" t="n">
-        <v>29110</v>
+        <v>29034</v>
       </c>
       <c r="K21" t="n">
-        <v>29436</v>
+        <v>29379</v>
       </c>
       <c r="L21" t="n">
-        <v>29671</v>
+        <v>29628</v>
       </c>
       <c r="M21" t="n">
-        <v>29840</v>
+        <v>29808</v>
       </c>
       <c r="N21" t="n">
-        <v>30167</v>
+        <v>30166</v>
       </c>
       <c r="O21" t="n">
-        <v>30140</v>
+        <v>30152</v>
       </c>
       <c r="P21" t="n">
-        <v>30081</v>
+        <v>30098</v>
       </c>
       <c r="Q21" t="n">
-        <v>30199</v>
+        <v>30218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31936</v>
+        <v>31930</v>
       </c>
       <c r="C22" t="n">
-        <v>29089</v>
+        <v>29037</v>
       </c>
       <c r="D22" t="n">
-        <v>24615</v>
+        <v>24493</v>
       </c>
       <c r="E22" t="n">
-        <v>20760</v>
+        <v>20586</v>
       </c>
       <c r="F22" t="n">
-        <v>22695</v>
+        <v>22566</v>
       </c>
       <c r="G22" t="n">
-        <v>26811</v>
+        <v>26752</v>
       </c>
       <c r="H22" t="n">
-        <v>28379</v>
+        <v>28318</v>
       </c>
       <c r="I22" t="n">
-        <v>28709</v>
+        <v>28645</v>
       </c>
       <c r="J22" t="n">
-        <v>29166</v>
+        <v>29110</v>
       </c>
       <c r="K22" t="n">
-        <v>29487</v>
+        <v>29436</v>
       </c>
       <c r="L22" t="n">
-        <v>29717</v>
+        <v>29671</v>
       </c>
       <c r="M22" t="n">
-        <v>29882</v>
+        <v>29840</v>
       </c>
       <c r="N22" t="n">
-        <v>30192</v>
+        <v>30167</v>
       </c>
       <c r="O22" t="n">
-        <v>30151</v>
+        <v>30140</v>
       </c>
       <c r="P22" t="n">
-        <v>30077</v>
+        <v>30081</v>
       </c>
       <c r="Q22" t="n">
-        <v>30180</v>
+        <v>30199</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32120</v>
+        <v>31936</v>
       </c>
       <c r="C23" t="n">
-        <v>29217</v>
+        <v>29089</v>
       </c>
       <c r="D23" t="n">
-        <v>24659</v>
+        <v>24615</v>
       </c>
       <c r="E23" t="n">
-        <v>20750</v>
+        <v>20760</v>
       </c>
       <c r="F23" t="n">
-        <v>22759</v>
+        <v>22695</v>
       </c>
       <c r="G23" t="n">
-        <v>26969</v>
+        <v>26811</v>
       </c>
       <c r="H23" t="n">
-        <v>28479</v>
+        <v>28379</v>
       </c>
       <c r="I23" t="n">
-        <v>28777</v>
+        <v>28709</v>
       </c>
       <c r="J23" t="n">
-        <v>29229</v>
+        <v>29166</v>
       </c>
       <c r="K23" t="n">
-        <v>29547</v>
+        <v>29487</v>
       </c>
       <c r="L23" t="n">
-        <v>29773</v>
+        <v>29717</v>
       </c>
       <c r="M23" t="n">
-        <v>29936</v>
+        <v>29882</v>
       </c>
       <c r="N23" t="n">
-        <v>30239</v>
+        <v>30192</v>
       </c>
       <c r="O23" t="n">
-        <v>30193</v>
+        <v>30151</v>
       </c>
       <c r="P23" t="n">
-        <v>30115</v>
+        <v>30077</v>
       </c>
       <c r="Q23" t="n">
-        <v>30216</v>
+        <v>30180</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,165 +1513,6 @@
       </c>
       <c r="Q20" t="n">
         <v>3.023</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B21" t="n">
-        <v>3.1865</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2.9053</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.4611</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.0671</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.2352</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.6255</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.8096</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.8545</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.9034</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.9379</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.9628</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.9808</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.0166</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.0152</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3.0098</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.0218</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3.193</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.9037</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.4493</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.0586</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.2566</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.6752</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.8318</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8645</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.9436</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.9671</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.984</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.0167</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.014</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.0081</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.0199</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3.1936</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.9089</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.4615</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.076</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2.2695</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.6811</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.8379</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.8709</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.9166</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.9487</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.9717</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.9882</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.0192</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.0151</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.0077</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.018</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2820,171 +2661,6 @@
         <v>30230</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>31865</v>
-      </c>
-      <c r="C21" t="n">
-        <v>29053</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24611</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20671</v>
-      </c>
-      <c r="F21" t="n">
-        <v>22352</v>
-      </c>
-      <c r="G21" t="n">
-        <v>26255</v>
-      </c>
-      <c r="H21" t="n">
-        <v>28096</v>
-      </c>
-      <c r="I21" t="n">
-        <v>28545</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29034</v>
-      </c>
-      <c r="K21" t="n">
-        <v>29379</v>
-      </c>
-      <c r="L21" t="n">
-        <v>29628</v>
-      </c>
-      <c r="M21" t="n">
-        <v>29808</v>
-      </c>
-      <c r="N21" t="n">
-        <v>30166</v>
-      </c>
-      <c r="O21" t="n">
-        <v>30152</v>
-      </c>
-      <c r="P21" t="n">
-        <v>30098</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>30218</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>31930</v>
-      </c>
-      <c r="C22" t="n">
-        <v>29037</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24493</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20586</v>
-      </c>
-      <c r="F22" t="n">
-        <v>22566</v>
-      </c>
-      <c r="G22" t="n">
-        <v>26752</v>
-      </c>
-      <c r="H22" t="n">
-        <v>28318</v>
-      </c>
-      <c r="I22" t="n">
-        <v>28645</v>
-      </c>
-      <c r="J22" t="n">
-        <v>29110</v>
-      </c>
-      <c r="K22" t="n">
-        <v>29436</v>
-      </c>
-      <c r="L22" t="n">
-        <v>29671</v>
-      </c>
-      <c r="M22" t="n">
-        <v>29840</v>
-      </c>
-      <c r="N22" t="n">
-        <v>30167</v>
-      </c>
-      <c r="O22" t="n">
-        <v>30140</v>
-      </c>
-      <c r="P22" t="n">
-        <v>30081</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>30199</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>31936</v>
-      </c>
-      <c r="C23" t="n">
-        <v>29089</v>
-      </c>
-      <c r="D23" t="n">
-        <v>24615</v>
-      </c>
-      <c r="E23" t="n">
-        <v>20760</v>
-      </c>
-      <c r="F23" t="n">
-        <v>22695</v>
-      </c>
-      <c r="G23" t="n">
-        <v>26811</v>
-      </c>
-      <c r="H23" t="n">
-        <v>28379</v>
-      </c>
-      <c r="I23" t="n">
-        <v>28709</v>
-      </c>
-      <c r="J23" t="n">
-        <v>29166</v>
-      </c>
-      <c r="K23" t="n">
-        <v>29487</v>
-      </c>
-      <c r="L23" t="n">
-        <v>29717</v>
-      </c>
-      <c r="M23" t="n">
-        <v>29882</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30192</v>
-      </c>
-      <c r="O23" t="n">
-        <v>30151</v>
-      </c>
-      <c r="P23" t="n">
-        <v>30077</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>30180</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1008 +510,1061 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L2" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B3" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C3" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G3" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B4" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E4" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I4" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P4" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N5" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P5" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M6" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L7" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O7" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C8" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F8" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O8" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B9" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B10" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B11" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O11" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M12" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B13" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M13" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J15" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M15" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O15" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O17" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E18" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I19" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J19" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.1502</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.8784</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.4484</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.0627</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.2168</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.5906</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.7893</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.842</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.893</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.9291</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.9553</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.9744</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.0139</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.0148</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.0113</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.0251</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>3.1676</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>2.8911</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>2.4537</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>2.0628</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>2.2221</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>2.6031</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>2.7977</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>2.8478</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>2.8982</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>2.9338</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2.9595</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>2.9782</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>3.0161</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>3.0156</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>3.0106</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>3.023</v>
       </c>
     </row>
@@ -1526,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1619,1045 +1672,1100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C2" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D2" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E2" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F2" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G2" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H2" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I2" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J2" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K2" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L2" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M2" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N2" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O2" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P2" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q2" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C3" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D3" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E3" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F3" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G3" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H3" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I3" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J3" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K3" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L3" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M3" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N3" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O3" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P3" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q3" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C4" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D4" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E4" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F4" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G4" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H4" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I4" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J4" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K4" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L4" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M4" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N4" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O4" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P4" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q4" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C5" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D5" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E5" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F5" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G5" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H5" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I5" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J5" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K5" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L5" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M5" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N5" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O5" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P5" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q5" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C6" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D6" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E6" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F6" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G6" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H6" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I6" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J6" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K6" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L6" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M6" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N6" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O6" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P6" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q6" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C7" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D7" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E7" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F7" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G7" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H7" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I7" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J7" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K7" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L7" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M7" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N7" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O7" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P7" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q7" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C8" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D8" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E8" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F8" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G8" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H8" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I8" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J8" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K8" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L8" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M8" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N8" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O8" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P8" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q8" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C9" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E9" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F9" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G9" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H9" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I9" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J9" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K9" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L9" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M9" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N9" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O9" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P9" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q9" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C10" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D10" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E10" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F10" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G10" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H10" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I10" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J10" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K10" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L10" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M10" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N10" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O10" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P10" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q10" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C11" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D11" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E11" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F11" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G11" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H11" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I11" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J11" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K11" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L11" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M11" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N11" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O11" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P11" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q11" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C12" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D12" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E12" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F12" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G12" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H12" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I12" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J12" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K12" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L12" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M12" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N12" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O12" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P12" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q12" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C13" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D13" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E13" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F13" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G13" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H13" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I13" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J13" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K13" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L13" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M13" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N13" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O13" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P13" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q13" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C14" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D14" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E14" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F14" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G14" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H14" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I14" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J14" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K14" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L14" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M14" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N14" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O14" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P14" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q14" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C15" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D15" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E15" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F15" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G15" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H15" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I15" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J15" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K15" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L15" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M15" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N15" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O15" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P15" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q15" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C16" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D16" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E16" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F16" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G16" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H16" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I16" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J16" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K16" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L16" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M16" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N16" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O16" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P16" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q16" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C17" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D17" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E17" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F17" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G17" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H17" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I17" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J17" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K17" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L17" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M17" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N17" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O17" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P17" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q17" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C18" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D18" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E18" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F18" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G18" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H18" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I18" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J18" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K18" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L18" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M18" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N18" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O18" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P18" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q18" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C19" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D19" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E19" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F19" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G19" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H19" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I19" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J19" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K19" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L19" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M19" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N19" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O19" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P19" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q19" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>31502</v>
+      </c>
+      <c r="C20" t="n">
+        <v>28784</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24484</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20627</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22168</v>
+      </c>
+      <c r="G20" t="n">
+        <v>25906</v>
+      </c>
+      <c r="H20" t="n">
+        <v>27893</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28420</v>
+      </c>
+      <c r="J20" t="n">
+        <v>28930</v>
+      </c>
+      <c r="K20" t="n">
+        <v>29291</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29553</v>
+      </c>
+      <c r="M20" t="n">
+        <v>29744</v>
+      </c>
+      <c r="N20" t="n">
+        <v>30139</v>
+      </c>
+      <c r="O20" t="n">
+        <v>30148</v>
+      </c>
+      <c r="P20" t="n">
+        <v>30113</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>30251</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>14/09/2026</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>31676</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>28911</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>24537</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>20628</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>22221</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>26031</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>27977</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>28478</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>28982</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>29338</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>29595</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>29782</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>30161</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>30156</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>30106</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>30230</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1061 +510,1114 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B2" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G2" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B3" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L3" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B4" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C4" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G4" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B5" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E5" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I5" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P5" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N6" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P6" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M7" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L8" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O8" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C9" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F9" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O9" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B10" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B11" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B12" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C12" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O12" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M13" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B14" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M14" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J16" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M16" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O16" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O18" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E19" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I20" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J20" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.1502</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.8784</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.4484</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.0627</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2168</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.5906</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.7893</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.842</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.893</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9291</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.9553</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.9744</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.0139</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.0148</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.0113</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.0251</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>3.1676</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>2.8911</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>2.4537</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>2.0628</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>2.2221</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>2.6031</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>2.7977</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>2.8478</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2.8982</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2.9338</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>2.9595</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>2.9782</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>3.0161</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>3.0156</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>3.0106</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>3.023</v>
       </c>
     </row>
@@ -1579,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,1100 +1725,1155 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C2" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D2" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E2" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F2" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G2" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H2" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I2" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J2" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K2" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L2" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M2" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N2" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O2" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P2" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q2" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C3" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D3" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E3" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F3" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G3" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H3" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I3" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J3" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K3" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L3" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M3" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N3" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O3" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P3" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q3" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C4" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D4" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E4" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F4" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G4" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H4" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I4" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J4" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K4" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L4" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M4" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N4" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O4" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P4" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q4" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C5" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D5" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E5" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F5" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G5" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H5" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I5" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J5" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K5" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L5" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M5" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N5" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O5" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P5" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q5" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C6" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D6" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E6" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F6" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G6" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H6" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I6" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J6" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K6" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L6" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M6" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N6" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O6" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P6" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q6" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C7" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D7" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E7" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F7" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G7" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H7" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I7" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J7" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K7" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L7" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M7" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N7" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O7" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P7" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q7" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C8" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D8" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E8" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F8" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G8" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H8" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I8" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J8" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K8" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L8" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M8" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N8" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O8" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P8" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q8" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D9" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E9" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F9" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G9" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H9" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I9" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J9" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K9" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L9" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M9" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N9" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O9" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P9" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q9" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C10" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D10" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E10" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F10" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G10" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H10" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I10" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J10" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K10" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L10" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M10" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N10" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O10" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P10" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q10" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C11" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D11" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E11" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F11" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G11" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H11" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I11" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J11" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K11" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L11" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M11" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N11" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O11" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P11" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q11" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C12" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D12" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E12" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F12" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G12" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H12" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I12" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J12" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K12" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L12" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M12" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N12" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O12" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P12" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q12" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C13" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D13" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E13" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F13" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G13" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H13" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I13" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J13" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K13" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L13" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M13" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N13" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O13" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P13" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q13" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C14" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D14" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E14" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F14" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G14" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H14" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I14" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J14" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K14" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L14" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M14" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N14" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O14" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P14" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q14" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C15" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D15" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E15" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F15" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G15" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H15" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I15" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J15" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K15" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L15" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M15" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N15" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O15" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P15" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q15" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C16" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D16" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E16" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F16" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G16" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H16" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I16" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J16" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K16" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L16" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M16" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N16" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O16" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P16" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q16" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C17" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D17" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E17" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F17" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G17" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H17" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I17" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J17" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K17" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L17" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M17" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N17" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O17" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P17" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q17" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C18" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D18" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E18" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F18" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G18" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H18" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I18" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J18" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K18" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L18" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M18" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N18" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O18" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P18" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q18" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C19" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D19" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E19" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F19" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G19" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H19" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I19" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J19" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K19" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L19" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M19" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N19" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O19" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P19" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q19" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C20" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D20" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E20" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F20" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G20" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H20" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I20" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J20" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K20" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L20" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M20" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N20" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O20" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P20" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q20" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>31502</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28784</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24484</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20627</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22168</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25906</v>
+      </c>
+      <c r="H21" t="n">
+        <v>27893</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28420</v>
+      </c>
+      <c r="J21" t="n">
+        <v>28930</v>
+      </c>
+      <c r="K21" t="n">
+        <v>29291</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29553</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29744</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30139</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30148</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30113</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>30251</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>14/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>31676</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>28911</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>24537</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>20628</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>22221</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>26031</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>27977</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>28478</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>28982</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>29338</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>29595</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>29782</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>30161</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>30156</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>30106</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>30230</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1115 +510,1115 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D2" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H2" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L2" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B3" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G3" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B4" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L4" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B5" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C5" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G5" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B6" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E6" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I6" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P6" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N7" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P7" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M8" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L9" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O9" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C10" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F10" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O10" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B11" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B12" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B13" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O13" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M14" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B15" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M15" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J17" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M17" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O17" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O19" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E20" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B21" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I21" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J21" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B22" t="n">
-        <v>3.1676</v>
+        <v>3.1502</v>
       </c>
       <c r="C22" t="n">
-        <v>2.8911</v>
+        <v>2.8784</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4537</v>
+        <v>2.4484</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0628</v>
+        <v>2.0627</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2221</v>
+        <v>2.2168</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6031</v>
+        <v>2.5906</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7977</v>
+        <v>2.7893</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8478</v>
+        <v>2.842</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8982</v>
+        <v>2.893</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9338</v>
+        <v>2.9291</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9595</v>
+        <v>2.9553</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9782</v>
+        <v>2.9744</v>
       </c>
       <c r="N22" t="n">
-        <v>3.0161</v>
+        <v>3.0139</v>
       </c>
       <c r="O22" t="n">
-        <v>3.0156</v>
+        <v>3.0148</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0106</v>
+        <v>3.0113</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.023</v>
+        <v>3.0251</v>
       </c>
     </row>
   </sheetData>
@@ -1725,1156 +1725,1156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C2" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D2" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E2" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F2" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G2" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H2" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I2" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J2" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K2" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L2" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M2" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N2" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O2" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P2" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q2" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C3" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D3" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E3" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F3" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G3" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H3" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I3" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J3" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K3" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L3" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M3" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N3" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O3" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P3" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q3" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C4" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D4" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E4" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F4" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G4" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H4" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I4" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J4" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K4" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L4" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M4" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N4" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O4" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P4" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q4" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C5" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D5" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E5" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F5" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G5" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H5" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I5" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J5" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K5" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L5" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M5" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N5" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O5" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P5" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q5" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C6" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D6" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E6" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F6" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G6" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H6" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I6" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J6" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K6" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L6" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M6" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N6" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O6" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P6" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q6" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C7" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D7" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E7" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F7" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G7" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H7" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I7" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J7" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K7" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L7" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M7" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N7" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O7" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P7" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q7" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C8" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D8" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E8" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F8" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G8" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H8" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I8" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J8" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K8" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L8" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M8" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N8" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O8" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P8" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q8" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C9" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D9" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E9" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F9" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G9" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H9" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I9" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J9" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K9" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L9" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M9" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N9" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O9" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P9" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q9" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C10" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D10" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E10" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F10" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G10" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H10" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I10" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J10" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K10" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L10" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M10" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N10" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O10" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P10" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q10" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C11" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D11" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E11" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F11" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G11" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H11" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I11" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J11" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K11" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L11" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M11" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N11" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O11" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P11" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q11" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C12" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D12" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E12" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F12" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G12" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H12" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I12" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J12" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K12" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L12" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M12" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N12" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O12" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P12" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q12" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C13" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D13" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E13" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F13" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G13" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H13" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I13" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J13" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K13" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L13" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M13" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N13" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O13" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P13" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q13" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C14" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D14" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E14" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F14" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G14" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H14" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I14" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J14" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K14" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L14" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M14" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N14" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O14" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P14" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q14" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C15" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D15" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E15" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F15" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G15" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H15" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I15" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J15" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K15" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L15" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M15" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N15" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O15" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P15" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q15" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C16" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D16" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E16" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F16" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G16" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H16" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I16" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J16" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K16" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L16" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M16" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N16" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O16" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P16" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q16" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C17" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D17" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E17" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F17" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G17" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H17" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I17" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J17" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K17" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L17" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M17" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N17" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O17" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P17" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q17" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C18" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D18" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E18" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F18" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G18" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H18" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I18" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J18" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K18" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L18" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M18" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N18" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O18" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P18" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q18" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C19" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D19" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E19" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F19" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G19" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H19" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I19" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J19" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K19" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L19" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M19" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N19" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O19" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P19" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q19" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C20" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D20" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E20" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F20" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G20" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H20" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I20" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J20" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K20" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L20" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M20" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N20" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O20" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P20" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q20" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C21" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D21" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E21" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F21" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G21" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H21" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I21" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J21" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K21" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L21" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M21" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N21" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O21" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P21" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q21" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31676</v>
+        <v>31502</v>
       </c>
       <c r="C22" t="n">
-        <v>28911</v>
+        <v>28784</v>
       </c>
       <c r="D22" t="n">
-        <v>24537</v>
+        <v>24484</v>
       </c>
       <c r="E22" t="n">
-        <v>20628</v>
+        <v>20627</v>
       </c>
       <c r="F22" t="n">
-        <v>22221</v>
+        <v>22168</v>
       </c>
       <c r="G22" t="n">
-        <v>26031</v>
+        <v>25906</v>
       </c>
       <c r="H22" t="n">
-        <v>27977</v>
+        <v>27893</v>
       </c>
       <c r="I22" t="n">
-        <v>28478</v>
+        <v>28420</v>
       </c>
       <c r="J22" t="n">
-        <v>28982</v>
+        <v>28930</v>
       </c>
       <c r="K22" t="n">
-        <v>29338</v>
+        <v>29291</v>
       </c>
       <c r="L22" t="n">
-        <v>29595</v>
+        <v>29553</v>
       </c>
       <c r="M22" t="n">
-        <v>29782</v>
+        <v>29744</v>
       </c>
       <c r="N22" t="n">
-        <v>30161</v>
+        <v>30139</v>
       </c>
       <c r="O22" t="n">
-        <v>30156</v>
+        <v>30148</v>
       </c>
       <c r="P22" t="n">
-        <v>30106</v>
+        <v>30113</v>
       </c>
       <c r="Q22" t="n">
-        <v>30230</v>
+        <v>30251</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,1115 +510,1115 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L2" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D3" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H3" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L3" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B4" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G4" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B5" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L5" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B6" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C6" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G6" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B7" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E7" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I7" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P7" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N8" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P8" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M9" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L10" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O10" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B11" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C11" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F11" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O11" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B12" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B13" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B14" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C14" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O14" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M15" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B16" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M16" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J18" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M18" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O18" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0121</v>
+        <v>3.0009</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1191</v>
+        <v>3.1212</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8544</v>
+        <v>2.8561</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4357</v>
+        <v>2.4366</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0611</v>
+        <v>2.0608</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2132</v>
+        <v>2.2121</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5813</v>
+        <v>2.5795</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7837</v>
+        <v>2.7802</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8388</v>
+        <v>2.8342</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8906</v>
+        <v>2.8852</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9273</v>
+        <v>2.9213</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9539</v>
+        <v>2.9473</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9733</v>
+        <v>2.9663</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0137</v>
+        <v>3.0049</v>
       </c>
       <c r="O20" t="n">
-        <v>3.015</v>
+        <v>3.0048</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0116</v>
+        <v>2.9999</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0256</v>
+        <v>3.0121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B21" t="n">
-        <v>3.1341</v>
+        <v>3.1191</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8661</v>
+        <v>2.8544</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4421</v>
+        <v>2.4357</v>
       </c>
       <c r="E21" t="n">
-        <v>2.062</v>
+        <v>2.0611</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2142</v>
+        <v>2.2132</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5843</v>
+        <v>2.5813</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7856</v>
+        <v>2.7837</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8398</v>
+        <v>2.8388</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8913</v>
+        <v>2.8906</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9278</v>
+        <v>2.9273</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9542</v>
+        <v>2.9539</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9736</v>
+        <v>2.9733</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0136</v>
+        <v>3.0137</v>
       </c>
       <c r="O21" t="n">
-        <v>3.0149</v>
+        <v>3.015</v>
       </c>
       <c r="P21" t="n">
-        <v>3.0115</v>
+        <v>3.0116</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.0255</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B22" t="n">
-        <v>3.1502</v>
+        <v>3.1341</v>
       </c>
       <c r="C22" t="n">
-        <v>2.8784</v>
+        <v>2.8661</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4484</v>
+        <v>2.4421</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0627</v>
+        <v>2.062</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2168</v>
+        <v>2.2142</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5906</v>
+        <v>2.5843</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7893</v>
+        <v>2.7856</v>
       </c>
       <c r="I22" t="n">
-        <v>2.842</v>
+        <v>2.8398</v>
       </c>
       <c r="J22" t="n">
-        <v>2.893</v>
+        <v>2.8913</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9291</v>
+        <v>2.9278</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9553</v>
+        <v>2.9542</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9744</v>
+        <v>2.9736</v>
       </c>
       <c r="N22" t="n">
-        <v>3.0139</v>
+        <v>3.0136</v>
       </c>
       <c r="O22" t="n">
-        <v>3.0148</v>
+        <v>3.0149</v>
       </c>
       <c r="P22" t="n">
-        <v>3.0113</v>
+        <v>3.0115</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.0251</v>
+        <v>3.0255</v>
       </c>
     </row>
   </sheetData>
@@ -1725,1156 +1725,1156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C2" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D2" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E2" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F2" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G2" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H2" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I2" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J2" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K2" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L2" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M2" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N2" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O2" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P2" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q2" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C3" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D3" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E3" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F3" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G3" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H3" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I3" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J3" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K3" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L3" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M3" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N3" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O3" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P3" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q3" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C4" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D4" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E4" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F4" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G4" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H4" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I4" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J4" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K4" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L4" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M4" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N4" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O4" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P4" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q4" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C5" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D5" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E5" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F5" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G5" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H5" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I5" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J5" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K5" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L5" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M5" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N5" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O5" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P5" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q5" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C6" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D6" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E6" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F6" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G6" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H6" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I6" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J6" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K6" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L6" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M6" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N6" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O6" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P6" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q6" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C7" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D7" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E7" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F7" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G7" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H7" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I7" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J7" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K7" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L7" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M7" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N7" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O7" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P7" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q7" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C8" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D8" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E8" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F8" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G8" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H8" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I8" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J8" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K8" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L8" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M8" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N8" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O8" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P8" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q8" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C9" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D9" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E9" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F9" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G9" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H9" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I9" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J9" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K9" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L9" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M9" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N9" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O9" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P9" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q9" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C10" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D10" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E10" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F10" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G10" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H10" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I10" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J10" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K10" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L10" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M10" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N10" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O10" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P10" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q10" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C11" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D11" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E11" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F11" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G11" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H11" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I11" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J11" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K11" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L11" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M11" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N11" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O11" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P11" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q11" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C12" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D12" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E12" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F12" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G12" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H12" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I12" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J12" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K12" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L12" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M12" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N12" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O12" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P12" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q12" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C13" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D13" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E13" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F13" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G13" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H13" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I13" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J13" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K13" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L13" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M13" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N13" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O13" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P13" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q13" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C14" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D14" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E14" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F14" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G14" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H14" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I14" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J14" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K14" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L14" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M14" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N14" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O14" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P14" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q14" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C15" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D15" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E15" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F15" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G15" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H15" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I15" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J15" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K15" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L15" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M15" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N15" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O15" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P15" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q15" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C16" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D16" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E16" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F16" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G16" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H16" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I16" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J16" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K16" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L16" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M16" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N16" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O16" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P16" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q16" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C17" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D17" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E17" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F17" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G17" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H17" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I17" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J17" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K17" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L17" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M17" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N17" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O17" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P17" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q17" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C18" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D18" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E18" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F18" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G18" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H18" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I18" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J18" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K18" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L18" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M18" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N18" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O18" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P18" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q18" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C19" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D19" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E19" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F19" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G19" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H19" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I19" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J19" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K19" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L19" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M19" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N19" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O19" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P19" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q19" t="n">
-        <v>30121</v>
+        <v>30009</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31191</v>
+        <v>31212</v>
       </c>
       <c r="C20" t="n">
-        <v>28544</v>
+        <v>28561</v>
       </c>
       <c r="D20" t="n">
-        <v>24357</v>
+        <v>24366</v>
       </c>
       <c r="E20" t="n">
-        <v>20611</v>
+        <v>20608</v>
       </c>
       <c r="F20" t="n">
-        <v>22132</v>
+        <v>22121</v>
       </c>
       <c r="G20" t="n">
-        <v>25813</v>
+        <v>25795</v>
       </c>
       <c r="H20" t="n">
-        <v>27837</v>
+        <v>27802</v>
       </c>
       <c r="I20" t="n">
-        <v>28388</v>
+        <v>28342</v>
       </c>
       <c r="J20" t="n">
-        <v>28906</v>
+        <v>28852</v>
       </c>
       <c r="K20" t="n">
-        <v>29273</v>
+        <v>29213</v>
       </c>
       <c r="L20" t="n">
-        <v>29539</v>
+        <v>29473</v>
       </c>
       <c r="M20" t="n">
-        <v>29733</v>
+        <v>29663</v>
       </c>
       <c r="N20" t="n">
-        <v>30137</v>
+        <v>30049</v>
       </c>
       <c r="O20" t="n">
-        <v>30150</v>
+        <v>30048</v>
       </c>
       <c r="P20" t="n">
-        <v>30116</v>
+        <v>29999</v>
       </c>
       <c r="Q20" t="n">
-        <v>30256</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31341</v>
+        <v>31191</v>
       </c>
       <c r="C21" t="n">
-        <v>28661</v>
+        <v>28544</v>
       </c>
       <c r="D21" t="n">
-        <v>24421</v>
+        <v>24357</v>
       </c>
       <c r="E21" t="n">
-        <v>20620</v>
+        <v>20611</v>
       </c>
       <c r="F21" t="n">
-        <v>22142</v>
+        <v>22132</v>
       </c>
       <c r="G21" t="n">
-        <v>25843</v>
+        <v>25813</v>
       </c>
       <c r="H21" t="n">
-        <v>27856</v>
+        <v>27837</v>
       </c>
       <c r="I21" t="n">
-        <v>28398</v>
+        <v>28388</v>
       </c>
       <c r="J21" t="n">
-        <v>28913</v>
+        <v>28906</v>
       </c>
       <c r="K21" t="n">
-        <v>29278</v>
+        <v>29273</v>
       </c>
       <c r="L21" t="n">
-        <v>29542</v>
+        <v>29539</v>
       </c>
       <c r="M21" t="n">
-        <v>29736</v>
+        <v>29733</v>
       </c>
       <c r="N21" t="n">
-        <v>30136</v>
+        <v>30137</v>
       </c>
       <c r="O21" t="n">
-        <v>30149</v>
+        <v>30150</v>
       </c>
       <c r="P21" t="n">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="Q21" t="n">
-        <v>30255</v>
+        <v>30256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31502</v>
+        <v>31341</v>
       </c>
       <c r="C22" t="n">
-        <v>28784</v>
+        <v>28661</v>
       </c>
       <c r="D22" t="n">
-        <v>24484</v>
+        <v>24421</v>
       </c>
       <c r="E22" t="n">
-        <v>20627</v>
+        <v>20620</v>
       </c>
       <c r="F22" t="n">
-        <v>22168</v>
+        <v>22142</v>
       </c>
       <c r="G22" t="n">
-        <v>25906</v>
+        <v>25843</v>
       </c>
       <c r="H22" t="n">
-        <v>27893</v>
+        <v>27856</v>
       </c>
       <c r="I22" t="n">
-        <v>28420</v>
+        <v>28398</v>
       </c>
       <c r="J22" t="n">
-        <v>28930</v>
+        <v>28913</v>
       </c>
       <c r="K22" t="n">
-        <v>29291</v>
+        <v>29278</v>
       </c>
       <c r="L22" t="n">
-        <v>29553</v>
+        <v>29542</v>
       </c>
       <c r="M22" t="n">
-        <v>29744</v>
+        <v>29736</v>
       </c>
       <c r="N22" t="n">
-        <v>30139</v>
+        <v>30136</v>
       </c>
       <c r="O22" t="n">
-        <v>30148</v>
+        <v>30149</v>
       </c>
       <c r="P22" t="n">
-        <v>30113</v>
+        <v>30115</v>
       </c>
       <c r="Q22" t="n">
-        <v>30251</v>
+        <v>30255</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1115 +510,1009 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D2" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O2" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P2" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L3" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D4" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H4" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L4" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B5" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G5" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B6" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L6" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B7" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C7" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G7" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B8" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E8" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I8" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P8" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N9" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P9" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M10" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B11" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C11" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L11" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O11" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B12" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C12" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F12" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O12" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B13" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C13" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B14" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B15" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O15" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M16" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B17" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M17" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J19" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M19" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O19" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1212</v>
+        <v>3.1153</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8561</v>
+        <v>2.8473</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4366</v>
+        <v>2.4244</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0608</v>
+        <v>2.0517</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2121</v>
+        <v>2.2169</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5795</v>
+        <v>2.5965</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7802</v>
+        <v>2.7837</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8342</v>
+        <v>2.8322</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8852</v>
+        <v>2.882</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9213</v>
+        <v>2.9172</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9473</v>
+        <v>2.9426</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9663</v>
+        <v>2.961</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0049</v>
+        <v>2.9975</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0048</v>
+        <v>2.996</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9999</v>
+        <v>2.9899</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0121</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B21" t="n">
-        <v>3.1191</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2.8544</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.4357</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.0611</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.2132</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.5813</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.7837</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.8388</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.8906</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.9273</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.9539</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.9733</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.0137</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.015</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3.0116</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.0256</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3.1341</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.8661</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.4421</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.062</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.2142</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.5843</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.7856</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8398</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.8913</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.9278</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.9542</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.9736</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.0136</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.0149</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.0115</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.0255</v>
+        <v>3.0009</v>
       </c>
     </row>
   </sheetData>
@@ -1632,7 +1526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,1156 +1619,1046 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34747</v>
+        <v>34689</v>
       </c>
       <c r="C2" t="n">
-        <v>30605</v>
+        <v>30562</v>
       </c>
       <c r="D2" t="n">
-        <v>24090</v>
+        <v>24072</v>
       </c>
       <c r="E2" t="n">
-        <v>18448</v>
+        <v>18449</v>
       </c>
       <c r="F2" t="n">
-        <v>21132</v>
+        <v>21120</v>
       </c>
       <c r="G2" t="n">
-        <v>26773</v>
+        <v>26736</v>
       </c>
       <c r="H2" t="n">
-        <v>28531</v>
+        <v>28496</v>
       </c>
       <c r="I2" t="n">
-        <v>28872</v>
+        <v>28842</v>
       </c>
       <c r="J2" t="n">
-        <v>29481</v>
+        <v>29453</v>
       </c>
       <c r="K2" t="n">
-        <v>29913</v>
+        <v>29887</v>
       </c>
       <c r="L2" t="n">
-        <v>30226</v>
+        <v>30201</v>
       </c>
       <c r="M2" t="n">
-        <v>30454</v>
+        <v>30432</v>
       </c>
       <c r="N2" t="n">
-        <v>30916</v>
+        <v>30905</v>
       </c>
       <c r="O2" t="n">
-        <v>30890</v>
+        <v>30893</v>
       </c>
       <c r="P2" t="n">
-        <v>30770</v>
+        <v>30789</v>
       </c>
       <c r="Q2" t="n">
-        <v>30799</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C3" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D3" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E3" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F3" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G3" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H3" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I3" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J3" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K3" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L3" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M3" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N3" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O3" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P3" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q3" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C4" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D4" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E4" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F4" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G4" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H4" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I4" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J4" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K4" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L4" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M4" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N4" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O4" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P4" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q4" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C5" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D5" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E5" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F5" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G5" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H5" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I5" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J5" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K5" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L5" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M5" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N5" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O5" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P5" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q5" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C6" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D6" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E6" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F6" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G6" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H6" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I6" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J6" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K6" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L6" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M6" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N6" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O6" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P6" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q6" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C7" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D7" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E7" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F7" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G7" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H7" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I7" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J7" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K7" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L7" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M7" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N7" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O7" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P7" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q7" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C8" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D8" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E8" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F8" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G8" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H8" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I8" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J8" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K8" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L8" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M8" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N8" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O8" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P8" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q8" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C9" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D9" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E9" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F9" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G9" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H9" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I9" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J9" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K9" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L9" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M9" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N9" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O9" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P9" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q9" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C10" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D10" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E10" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F10" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G10" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H10" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I10" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J10" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K10" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L10" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M10" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N10" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O10" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P10" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q10" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C11" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D11" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E11" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F11" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G11" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H11" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I11" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J11" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K11" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L11" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M11" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N11" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O11" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P11" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q11" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C12" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D12" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E12" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F12" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G12" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H12" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I12" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J12" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K12" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L12" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M12" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N12" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O12" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P12" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q12" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C13" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D13" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E13" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F13" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G13" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H13" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I13" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J13" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K13" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L13" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M13" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N13" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O13" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P13" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q13" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C14" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D14" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E14" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F14" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G14" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H14" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I14" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J14" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K14" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L14" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M14" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N14" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O14" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P14" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q14" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C15" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D15" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E15" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F15" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G15" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H15" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I15" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J15" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K15" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L15" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M15" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N15" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O15" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P15" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q15" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C16" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D16" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E16" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F16" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G16" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H16" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I16" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J16" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K16" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L16" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M16" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N16" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O16" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P16" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q16" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C17" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D17" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E17" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F17" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G17" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H17" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I17" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J17" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K17" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L17" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M17" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N17" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O17" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P17" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q17" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C18" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D18" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E18" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F18" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G18" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H18" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I18" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J18" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K18" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L18" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M18" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N18" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O18" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P18" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q18" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C19" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D19" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E19" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F19" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G19" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H19" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I19" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J19" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K19" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L19" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M19" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N19" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O19" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P19" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q19" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31212</v>
+        <v>31153</v>
       </c>
       <c r="C20" t="n">
-        <v>28561</v>
+        <v>28473</v>
       </c>
       <c r="D20" t="n">
-        <v>24366</v>
+        <v>24244</v>
       </c>
       <c r="E20" t="n">
-        <v>20608</v>
+        <v>20517</v>
       </c>
       <c r="F20" t="n">
-        <v>22121</v>
+        <v>22169</v>
       </c>
       <c r="G20" t="n">
-        <v>25795</v>
+        <v>25965</v>
       </c>
       <c r="H20" t="n">
-        <v>27802</v>
+        <v>27837</v>
       </c>
       <c r="I20" t="n">
-        <v>28342</v>
+        <v>28322</v>
       </c>
       <c r="J20" t="n">
-        <v>28852</v>
+        <v>28820</v>
       </c>
       <c r="K20" t="n">
-        <v>29213</v>
+        <v>29172</v>
       </c>
       <c r="L20" t="n">
-        <v>29473</v>
+        <v>29426</v>
       </c>
       <c r="M20" t="n">
-        <v>29663</v>
+        <v>29610</v>
       </c>
       <c r="N20" t="n">
-        <v>30049</v>
+        <v>29975</v>
       </c>
       <c r="O20" t="n">
-        <v>30048</v>
+        <v>29960</v>
       </c>
       <c r="P20" t="n">
-        <v>29999</v>
+        <v>29899</v>
       </c>
       <c r="Q20" t="n">
-        <v>30121</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>31191</v>
-      </c>
-      <c r="C21" t="n">
-        <v>28544</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24357</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20611</v>
-      </c>
-      <c r="F21" t="n">
-        <v>22132</v>
-      </c>
-      <c r="G21" t="n">
-        <v>25813</v>
-      </c>
-      <c r="H21" t="n">
-        <v>27837</v>
-      </c>
-      <c r="I21" t="n">
-        <v>28388</v>
-      </c>
-      <c r="J21" t="n">
-        <v>28906</v>
-      </c>
-      <c r="K21" t="n">
-        <v>29273</v>
-      </c>
-      <c r="L21" t="n">
-        <v>29539</v>
-      </c>
-      <c r="M21" t="n">
-        <v>29733</v>
-      </c>
-      <c r="N21" t="n">
-        <v>30137</v>
-      </c>
-      <c r="O21" t="n">
-        <v>30150</v>
-      </c>
-      <c r="P21" t="n">
-        <v>30116</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>30256</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>16/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>31341</v>
-      </c>
-      <c r="C22" t="n">
-        <v>28661</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24421</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20620</v>
-      </c>
-      <c r="F22" t="n">
-        <v>22142</v>
-      </c>
-      <c r="G22" t="n">
-        <v>25843</v>
-      </c>
-      <c r="H22" t="n">
-        <v>27856</v>
-      </c>
-      <c r="I22" t="n">
-        <v>28398</v>
-      </c>
-      <c r="J22" t="n">
-        <v>28913</v>
-      </c>
-      <c r="K22" t="n">
-        <v>29278</v>
-      </c>
-      <c r="L22" t="n">
-        <v>29542</v>
-      </c>
-      <c r="M22" t="n">
-        <v>29736</v>
-      </c>
-      <c r="N22" t="n">
-        <v>30136</v>
-      </c>
-      <c r="O22" t="n">
-        <v>30149</v>
-      </c>
-      <c r="P22" t="n">
-        <v>30115</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>30255</v>
+        <v>30009</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,1008 +510,1061 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4689</v>
+        <v>3.4975</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0562</v>
+        <v>3.1024</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4072</v>
+        <v>2.4778</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8449</v>
+        <v>1.9206</v>
       </c>
       <c r="F2" t="n">
-        <v>2.112</v>
+        <v>2.1453</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6736</v>
+        <v>2.6571</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8496</v>
+        <v>2.8448</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8842</v>
+        <v>2.886</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9453</v>
+        <v>2.9454</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9887</v>
+        <v>2.9875</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0201</v>
+        <v>3.0181</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0432</v>
+        <v>3.0405</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0905</v>
+        <v>3.0868</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0893</v>
+        <v>3.0866</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0789</v>
+        <v>3.0781</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0837</v>
+        <v>3.0855</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D3" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O3" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P3" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L4" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D5" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H5" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L5" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B6" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G6" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B7" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L7" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B8" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C8" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G8" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B9" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E9" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I9" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P9" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N10" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P10" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B11" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C11" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M11" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B12" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C12" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L12" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O12" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B13" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C13" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F13" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O13" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B14" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C14" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B15" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B16" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O16" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M17" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B18" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M18" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.1299</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.8523</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.4152</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.0342</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.2138</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.6109</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.7874</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.8305</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.8797</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.9143</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.9392</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.9572</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.9922</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.9894</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.9821</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.9917</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
         <v>46286</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>3.1153</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>2.8473</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>2.4244</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>2.0517</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>2.2169</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>2.5965</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>2.7837</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>2.8322</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>2.882</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>2.9172</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2.9426</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>2.961</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>2.9975</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>2.996</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>2.9899</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>3.0009</v>
       </c>
     </row>
@@ -1526,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1619,1045 +1672,1100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34689</v>
+        <v>34975</v>
       </c>
       <c r="C2" t="n">
-        <v>30562</v>
+        <v>31024</v>
       </c>
       <c r="D2" t="n">
-        <v>24072</v>
+        <v>24778</v>
       </c>
       <c r="E2" t="n">
-        <v>18449</v>
+        <v>19206</v>
       </c>
       <c r="F2" t="n">
-        <v>21120</v>
+        <v>21453</v>
       </c>
       <c r="G2" t="n">
-        <v>26736</v>
+        <v>26571</v>
       </c>
       <c r="H2" t="n">
-        <v>28496</v>
+        <v>28448</v>
       </c>
       <c r="I2" t="n">
-        <v>28842</v>
+        <v>28860</v>
       </c>
       <c r="J2" t="n">
-        <v>29453</v>
+        <v>29454</v>
       </c>
       <c r="K2" t="n">
-        <v>29887</v>
+        <v>29875</v>
       </c>
       <c r="L2" t="n">
-        <v>30201</v>
+        <v>30181</v>
       </c>
       <c r="M2" t="n">
-        <v>30432</v>
+        <v>30405</v>
       </c>
       <c r="N2" t="n">
-        <v>30905</v>
+        <v>30868</v>
       </c>
       <c r="O2" t="n">
-        <v>30893</v>
+        <v>30866</v>
       </c>
       <c r="P2" t="n">
-        <v>30789</v>
+        <v>30781</v>
       </c>
       <c r="Q2" t="n">
-        <v>30837</v>
+        <v>30855</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34747</v>
+        <v>34689</v>
       </c>
       <c r="C3" t="n">
-        <v>30605</v>
+        <v>30562</v>
       </c>
       <c r="D3" t="n">
-        <v>24090</v>
+        <v>24072</v>
       </c>
       <c r="E3" t="n">
-        <v>18448</v>
+        <v>18449</v>
       </c>
       <c r="F3" t="n">
-        <v>21132</v>
+        <v>21120</v>
       </c>
       <c r="G3" t="n">
-        <v>26773</v>
+        <v>26736</v>
       </c>
       <c r="H3" t="n">
-        <v>28531</v>
+        <v>28496</v>
       </c>
       <c r="I3" t="n">
-        <v>28872</v>
+        <v>28842</v>
       </c>
       <c r="J3" t="n">
-        <v>29481</v>
+        <v>29453</v>
       </c>
       <c r="K3" t="n">
-        <v>29913</v>
+        <v>29887</v>
       </c>
       <c r="L3" t="n">
-        <v>30226</v>
+        <v>30201</v>
       </c>
       <c r="M3" t="n">
-        <v>30454</v>
+        <v>30432</v>
       </c>
       <c r="N3" t="n">
-        <v>30916</v>
+        <v>30905</v>
       </c>
       <c r="O3" t="n">
-        <v>30890</v>
+        <v>30893</v>
       </c>
       <c r="P3" t="n">
-        <v>30770</v>
+        <v>30789</v>
       </c>
       <c r="Q3" t="n">
-        <v>30799</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C4" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D4" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E4" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F4" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G4" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H4" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I4" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J4" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K4" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L4" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M4" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N4" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O4" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P4" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q4" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C5" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D5" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E5" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F5" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G5" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H5" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I5" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J5" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K5" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L5" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M5" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N5" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O5" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P5" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q5" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C6" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D6" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E6" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F6" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G6" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H6" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I6" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J6" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K6" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L6" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M6" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N6" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O6" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P6" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q6" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C7" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D7" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E7" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F7" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G7" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H7" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I7" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J7" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K7" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L7" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M7" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N7" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O7" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P7" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q7" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C8" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D8" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E8" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F8" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G8" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H8" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I8" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J8" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K8" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L8" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M8" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N8" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O8" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P8" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q8" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C9" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D9" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E9" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F9" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G9" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H9" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I9" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J9" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K9" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L9" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M9" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N9" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O9" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P9" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q9" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C10" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D10" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E10" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F10" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G10" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H10" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I10" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J10" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K10" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L10" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M10" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N10" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O10" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P10" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q10" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C11" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D11" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E11" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F11" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G11" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H11" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I11" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J11" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K11" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L11" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M11" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N11" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O11" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P11" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q11" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C12" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D12" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E12" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F12" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G12" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H12" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I12" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J12" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K12" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L12" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M12" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N12" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O12" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P12" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q12" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C13" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D13" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E13" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F13" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G13" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H13" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I13" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J13" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K13" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L13" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M13" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N13" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O13" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P13" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q13" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C14" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D14" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E14" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F14" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G14" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H14" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I14" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J14" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K14" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L14" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M14" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N14" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O14" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P14" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q14" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C15" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D15" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E15" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F15" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G15" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H15" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I15" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J15" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K15" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L15" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M15" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N15" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O15" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P15" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q15" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C16" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D16" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E16" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F16" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G16" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H16" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I16" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J16" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K16" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L16" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M16" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N16" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O16" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P16" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q16" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C17" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D17" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E17" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F17" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G17" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H17" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I17" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J17" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K17" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L17" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M17" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N17" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O17" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P17" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q17" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C18" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D18" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E18" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F18" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G18" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H18" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I18" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J18" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K18" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L18" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M18" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N18" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O18" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P18" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q18" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C19" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D19" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E19" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F19" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G19" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H19" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I19" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J19" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K19" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L19" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M19" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N19" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O19" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P19" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q19" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>31299</v>
+      </c>
+      <c r="C20" t="n">
+        <v>28523</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24152</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20342</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22138</v>
+      </c>
+      <c r="G20" t="n">
+        <v>26109</v>
+      </c>
+      <c r="H20" t="n">
+        <v>27874</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28305</v>
+      </c>
+      <c r="J20" t="n">
+        <v>28797</v>
+      </c>
+      <c r="K20" t="n">
+        <v>29143</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29392</v>
+      </c>
+      <c r="M20" t="n">
+        <v>29572</v>
+      </c>
+      <c r="N20" t="n">
+        <v>29922</v>
+      </c>
+      <c r="O20" t="n">
+        <v>29894</v>
+      </c>
+      <c r="P20" t="n">
+        <v>29821</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>29917</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>21/09/2026</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>31153</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>28473</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>24244</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>20517</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>22169</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>25965</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>27837</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>28322</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>28820</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>29172</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>29426</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>29610</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>29975</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>29960</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>29899</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>30009</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,52 +510,52 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B2" t="n">
-        <v>3.4975</v>
+        <v>3.5465</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1024</v>
+        <v>3.1449</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4778</v>
+        <v>2.5086</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9206</v>
+        <v>1.9347</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1453</v>
+        <v>2.1504</v>
       </c>
       <c r="G2" t="n">
         <v>2.6571</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8448</v>
+        <v>2.8454</v>
       </c>
       <c r="I2" t="n">
-        <v>2.886</v>
+        <v>2.8865</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9454</v>
+        <v>2.9452</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9875</v>
+        <v>2.987</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0181</v>
+        <v>3.0172</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0405</v>
+        <v>3.0394</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0868</v>
+        <v>3.0854</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0866</v>
+        <v>3.0854</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0781</v>
+        <v>3.0775</v>
       </c>
       <c r="Q2" t="n">
         <v>3.0855</v>
@@ -563,1008 +563,1061 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4689</v>
+        <v>3.4975</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0562</v>
+        <v>3.1024</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4072</v>
+        <v>2.4778</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8449</v>
+        <v>1.9206</v>
       </c>
       <c r="F3" t="n">
-        <v>2.112</v>
+        <v>2.1453</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6736</v>
+        <v>2.6571</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8496</v>
+        <v>2.8448</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8842</v>
+        <v>2.886</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9453</v>
+        <v>2.9454</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9887</v>
+        <v>2.9875</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0201</v>
+        <v>3.0181</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0432</v>
+        <v>3.0405</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0905</v>
+        <v>3.0868</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0893</v>
+        <v>3.0866</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0789</v>
+        <v>3.0781</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0837</v>
+        <v>3.0855</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D4" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O4" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P4" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L5" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D6" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H6" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L6" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B7" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G7" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B8" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L8" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B9" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C9" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G9" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B10" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E10" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I10" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L10" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P10" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B11" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C11" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D11" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N11" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P11" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B12" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C12" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M12" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B13" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C13" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L13" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O13" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B14" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C14" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F14" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O14" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B15" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C15" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B16" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B17" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O17" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M18" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B19" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M19" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.1299</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.8523</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.4152</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.0342</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2138</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.6109</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.7874</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8305</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.8797</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9143</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.9392</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.9572</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.9922</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.9894</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.9821</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.9917</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>46286</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>3.1153</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>2.8473</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>2.4244</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>2.0517</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>2.2169</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>2.5965</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>2.7837</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>2.8322</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2.882</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2.9172</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>2.9426</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>2.961</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>2.9975</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>2.996</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>2.9899</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>3.0009</v>
       </c>
     </row>
@@ -1579,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,53 +1725,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34975</v>
+        <v>35465</v>
       </c>
       <c r="C2" t="n">
-        <v>31024</v>
+        <v>31449</v>
       </c>
       <c r="D2" t="n">
-        <v>24778</v>
+        <v>25086</v>
       </c>
       <c r="E2" t="n">
-        <v>19206</v>
+        <v>19347</v>
       </c>
       <c r="F2" t="n">
-        <v>21453</v>
+        <v>21504</v>
       </c>
       <c r="G2" t="n">
         <v>26571</v>
       </c>
       <c r="H2" t="n">
-        <v>28448</v>
+        <v>28454</v>
       </c>
       <c r="I2" t="n">
-        <v>28860</v>
+        <v>28865</v>
       </c>
       <c r="J2" t="n">
-        <v>29454</v>
+        <v>29452</v>
       </c>
       <c r="K2" t="n">
-        <v>29875</v>
+        <v>29870</v>
       </c>
       <c r="L2" t="n">
-        <v>30181</v>
+        <v>30172</v>
       </c>
       <c r="M2" t="n">
-        <v>30405</v>
+        <v>30394</v>
       </c>
       <c r="N2" t="n">
-        <v>30868</v>
+        <v>30854</v>
       </c>
       <c r="O2" t="n">
-        <v>30866</v>
+        <v>30854</v>
       </c>
       <c r="P2" t="n">
-        <v>30781</v>
+        <v>30775</v>
       </c>
       <c r="Q2" t="n">
         <v>30855</v>
@@ -1727,1045 +1780,1100 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34689</v>
+        <v>34975</v>
       </c>
       <c r="C3" t="n">
-        <v>30562</v>
+        <v>31024</v>
       </c>
       <c r="D3" t="n">
-        <v>24072</v>
+        <v>24778</v>
       </c>
       <c r="E3" t="n">
-        <v>18449</v>
+        <v>19206</v>
       </c>
       <c r="F3" t="n">
-        <v>21120</v>
+        <v>21453</v>
       </c>
       <c r="G3" t="n">
-        <v>26736</v>
+        <v>26571</v>
       </c>
       <c r="H3" t="n">
-        <v>28496</v>
+        <v>28448</v>
       </c>
       <c r="I3" t="n">
-        <v>28842</v>
+        <v>28860</v>
       </c>
       <c r="J3" t="n">
-        <v>29453</v>
+        <v>29454</v>
       </c>
       <c r="K3" t="n">
-        <v>29887</v>
+        <v>29875</v>
       </c>
       <c r="L3" t="n">
-        <v>30201</v>
+        <v>30181</v>
       </c>
       <c r="M3" t="n">
-        <v>30432</v>
+        <v>30405</v>
       </c>
       <c r="N3" t="n">
-        <v>30905</v>
+        <v>30868</v>
       </c>
       <c r="O3" t="n">
-        <v>30893</v>
+        <v>30866</v>
       </c>
       <c r="P3" t="n">
-        <v>30789</v>
+        <v>30781</v>
       </c>
       <c r="Q3" t="n">
-        <v>30837</v>
+        <v>30855</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34747</v>
+        <v>34689</v>
       </c>
       <c r="C4" t="n">
-        <v>30605</v>
+        <v>30562</v>
       </c>
       <c r="D4" t="n">
-        <v>24090</v>
+        <v>24072</v>
       </c>
       <c r="E4" t="n">
-        <v>18448</v>
+        <v>18449</v>
       </c>
       <c r="F4" t="n">
-        <v>21132</v>
+        <v>21120</v>
       </c>
       <c r="G4" t="n">
-        <v>26773</v>
+        <v>26736</v>
       </c>
       <c r="H4" t="n">
-        <v>28531</v>
+        <v>28496</v>
       </c>
       <c r="I4" t="n">
-        <v>28872</v>
+        <v>28842</v>
       </c>
       <c r="J4" t="n">
-        <v>29481</v>
+        <v>29453</v>
       </c>
       <c r="K4" t="n">
-        <v>29913</v>
+        <v>29887</v>
       </c>
       <c r="L4" t="n">
-        <v>30226</v>
+        <v>30201</v>
       </c>
       <c r="M4" t="n">
-        <v>30454</v>
+        <v>30432</v>
       </c>
       <c r="N4" t="n">
-        <v>30916</v>
+        <v>30905</v>
       </c>
       <c r="O4" t="n">
-        <v>30890</v>
+        <v>30893</v>
       </c>
       <c r="P4" t="n">
-        <v>30770</v>
+        <v>30789</v>
       </c>
       <c r="Q4" t="n">
-        <v>30799</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C5" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D5" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E5" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F5" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G5" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H5" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I5" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J5" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K5" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L5" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M5" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N5" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O5" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P5" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q5" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C6" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D6" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E6" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F6" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G6" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H6" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I6" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J6" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K6" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L6" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M6" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N6" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O6" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P6" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q6" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C7" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D7" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E7" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F7" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G7" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H7" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I7" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J7" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K7" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L7" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M7" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N7" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O7" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P7" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q7" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C8" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D8" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E8" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F8" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G8" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H8" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I8" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J8" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K8" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L8" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M8" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N8" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O8" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P8" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q8" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C9" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D9" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E9" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F9" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G9" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H9" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I9" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J9" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K9" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L9" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M9" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N9" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O9" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P9" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q9" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C10" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D10" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E10" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F10" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G10" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H10" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I10" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J10" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K10" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L10" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M10" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N10" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O10" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P10" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q10" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C11" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D11" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E11" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F11" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G11" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H11" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I11" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J11" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K11" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L11" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M11" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N11" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O11" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P11" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q11" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C12" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D12" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E12" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F12" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G12" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H12" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I12" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J12" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K12" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L12" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M12" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N12" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O12" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P12" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q12" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C13" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D13" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E13" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F13" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G13" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H13" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I13" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J13" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K13" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L13" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M13" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N13" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O13" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P13" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q13" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C14" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D14" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E14" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F14" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G14" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H14" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I14" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J14" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K14" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L14" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M14" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N14" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O14" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P14" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q14" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C15" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D15" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E15" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F15" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G15" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H15" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I15" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J15" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K15" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L15" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M15" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N15" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O15" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P15" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q15" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C16" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D16" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E16" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F16" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G16" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H16" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I16" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J16" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K16" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L16" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M16" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N16" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O16" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P16" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q16" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C17" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D17" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E17" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F17" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G17" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H17" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I17" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J17" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K17" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L17" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M17" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N17" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O17" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P17" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q17" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C18" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D18" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E18" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F18" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G18" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H18" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I18" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J18" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K18" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L18" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M18" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N18" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O18" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P18" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q18" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C19" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D19" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E19" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F19" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G19" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H19" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I19" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J19" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K19" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L19" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M19" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N19" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O19" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P19" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q19" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C20" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D20" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E20" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F20" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G20" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H20" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I20" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J20" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K20" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L20" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M20" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N20" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O20" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P20" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q20" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>31299</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28523</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24152</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20342</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22138</v>
+      </c>
+      <c r="G21" t="n">
+        <v>26109</v>
+      </c>
+      <c r="H21" t="n">
+        <v>27874</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28305</v>
+      </c>
+      <c r="J21" t="n">
+        <v>28797</v>
+      </c>
+      <c r="K21" t="n">
+        <v>29143</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29392</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29572</v>
+      </c>
+      <c r="N21" t="n">
+        <v>29922</v>
+      </c>
+      <c r="O21" t="n">
+        <v>29894</v>
+      </c>
+      <c r="P21" t="n">
+        <v>29821</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>29917</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>21/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>31153</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>28473</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>24244</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>20517</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>22169</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>25965</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>27837</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>28322</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>28820</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>29172</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>29426</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>29610</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>29975</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>29960</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>29899</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>30009</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,105 +510,105 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B2" t="n">
-        <v>3.5465</v>
+        <v>3.601</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1449</v>
+        <v>3.1872</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5086</v>
+        <v>2.5308</v>
       </c>
       <c r="E2" t="n">
         <v>1.9347</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1504</v>
+        <v>2.1488</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6571</v>
+        <v>2.6608</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8454</v>
+        <v>2.8483</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8865</v>
+        <v>2.8884</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9452</v>
+        <v>2.9472</v>
       </c>
       <c r="K2" t="n">
-        <v>2.987</v>
+        <v>2.989</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0172</v>
+        <v>3.0194</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0394</v>
+        <v>3.0417</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0854</v>
+        <v>3.0881</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0854</v>
+        <v>3.0886</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0775</v>
+        <v>3.0812</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0855</v>
+        <v>3.0899</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4975</v>
+        <v>3.5465</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1024</v>
+        <v>3.1449</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4778</v>
+        <v>2.5086</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9206</v>
+        <v>1.9347</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1453</v>
+        <v>2.1504</v>
       </c>
       <c r="G3" t="n">
         <v>2.6571</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8448</v>
+        <v>2.8454</v>
       </c>
       <c r="I3" t="n">
-        <v>2.886</v>
+        <v>2.8865</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9454</v>
+        <v>2.9452</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9875</v>
+        <v>2.987</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0181</v>
+        <v>3.0172</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0405</v>
+        <v>3.0394</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0868</v>
+        <v>3.0854</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0866</v>
+        <v>3.0854</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0781</v>
+        <v>3.0775</v>
       </c>
       <c r="Q3" t="n">
         <v>3.0855</v>
@@ -616,1009 +616,1009 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4689</v>
+        <v>3.4975</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0562</v>
+        <v>3.1024</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4072</v>
+        <v>2.4778</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8449</v>
+        <v>1.9206</v>
       </c>
       <c r="F4" t="n">
-        <v>2.112</v>
+        <v>2.1453</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6736</v>
+        <v>2.6571</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8496</v>
+        <v>2.8448</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8842</v>
+        <v>2.886</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9453</v>
+        <v>2.9454</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9887</v>
+        <v>2.9875</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0201</v>
+        <v>3.0181</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0432</v>
+        <v>3.0405</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0905</v>
+        <v>3.0868</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0893</v>
+        <v>3.0866</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0789</v>
+        <v>3.0781</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0837</v>
+        <v>3.0855</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D5" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O5" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P5" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L6" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D7" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L7" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B8" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G8" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B9" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L9" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B10" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C10" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G10" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L10" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B11" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E11" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I11" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L11" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P11" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B12" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C12" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N12" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P12" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B13" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C13" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M13" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B14" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C14" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L14" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O14" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B15" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C15" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F15" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O15" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B16" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C16" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B17" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B18" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C18" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O18" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M19" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B20" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M20" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B21" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B22" t="n">
-        <v>3.1153</v>
+        <v>3.1299</v>
       </c>
       <c r="C22" t="n">
-        <v>2.8473</v>
+        <v>2.8523</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4244</v>
+        <v>2.4152</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0517</v>
+        <v>2.0342</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2169</v>
+        <v>2.2138</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5965</v>
+        <v>2.6109</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7837</v>
+        <v>2.7874</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8322</v>
+        <v>2.8305</v>
       </c>
       <c r="J22" t="n">
-        <v>2.882</v>
+        <v>2.8797</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9172</v>
+        <v>2.9143</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9426</v>
+        <v>2.9392</v>
       </c>
       <c r="M22" t="n">
-        <v>2.961</v>
+        <v>2.9572</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9975</v>
+        <v>2.9922</v>
       </c>
       <c r="O22" t="n">
-        <v>2.996</v>
+        <v>2.9894</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9899</v>
+        <v>2.9821</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.0009</v>
+        <v>2.9917</v>
       </c>
     </row>
   </sheetData>
@@ -1725,108 +1725,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35465</v>
+        <v>36010</v>
       </c>
       <c r="C2" t="n">
-        <v>31449</v>
+        <v>31872</v>
       </c>
       <c r="D2" t="n">
-        <v>25086</v>
+        <v>25308</v>
       </c>
       <c r="E2" t="n">
         <v>19347</v>
       </c>
       <c r="F2" t="n">
-        <v>21504</v>
+        <v>21488</v>
       </c>
       <c r="G2" t="n">
-        <v>26571</v>
+        <v>26608</v>
       </c>
       <c r="H2" t="n">
-        <v>28454</v>
+        <v>28483</v>
       </c>
       <c r="I2" t="n">
-        <v>28865</v>
+        <v>28884</v>
       </c>
       <c r="J2" t="n">
-        <v>29452</v>
+        <v>29472</v>
       </c>
       <c r="K2" t="n">
-        <v>29870</v>
+        <v>29890</v>
       </c>
       <c r="L2" t="n">
-        <v>30172</v>
+        <v>30194</v>
       </c>
       <c r="M2" t="n">
-        <v>30394</v>
+        <v>30417</v>
       </c>
       <c r="N2" t="n">
-        <v>30854</v>
+        <v>30881</v>
       </c>
       <c r="O2" t="n">
-        <v>30854</v>
+        <v>30886</v>
       </c>
       <c r="P2" t="n">
-        <v>30775</v>
+        <v>30812</v>
       </c>
       <c r="Q2" t="n">
-        <v>30855</v>
+        <v>30899</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34975</v>
+        <v>35465</v>
       </c>
       <c r="C3" t="n">
-        <v>31024</v>
+        <v>31449</v>
       </c>
       <c r="D3" t="n">
-        <v>24778</v>
+        <v>25086</v>
       </c>
       <c r="E3" t="n">
-        <v>19206</v>
+        <v>19347</v>
       </c>
       <c r="F3" t="n">
-        <v>21453</v>
+        <v>21504</v>
       </c>
       <c r="G3" t="n">
         <v>26571</v>
       </c>
       <c r="H3" t="n">
-        <v>28448</v>
+        <v>28454</v>
       </c>
       <c r="I3" t="n">
-        <v>28860</v>
+        <v>28865</v>
       </c>
       <c r="J3" t="n">
-        <v>29454</v>
+        <v>29452</v>
       </c>
       <c r="K3" t="n">
-        <v>29875</v>
+        <v>29870</v>
       </c>
       <c r="L3" t="n">
-        <v>30181</v>
+        <v>30172</v>
       </c>
       <c r="M3" t="n">
-        <v>30405</v>
+        <v>30394</v>
       </c>
       <c r="N3" t="n">
-        <v>30868</v>
+        <v>30854</v>
       </c>
       <c r="O3" t="n">
-        <v>30866</v>
+        <v>30854</v>
       </c>
       <c r="P3" t="n">
-        <v>30781</v>
+        <v>30775</v>
       </c>
       <c r="Q3" t="n">
         <v>30855</v>
@@ -1835,1046 +1835,1046 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34689</v>
+        <v>34975</v>
       </c>
       <c r="C4" t="n">
-        <v>30562</v>
+        <v>31024</v>
       </c>
       <c r="D4" t="n">
-        <v>24072</v>
+        <v>24778</v>
       </c>
       <c r="E4" t="n">
-        <v>18449</v>
+        <v>19206</v>
       </c>
       <c r="F4" t="n">
-        <v>21120</v>
+        <v>21453</v>
       </c>
       <c r="G4" t="n">
-        <v>26736</v>
+        <v>26571</v>
       </c>
       <c r="H4" t="n">
-        <v>28496</v>
+        <v>28448</v>
       </c>
       <c r="I4" t="n">
-        <v>28842</v>
+        <v>28860</v>
       </c>
       <c r="J4" t="n">
-        <v>29453</v>
+        <v>29454</v>
       </c>
       <c r="K4" t="n">
-        <v>29887</v>
+        <v>29875</v>
       </c>
       <c r="L4" t="n">
-        <v>30201</v>
+        <v>30181</v>
       </c>
       <c r="M4" t="n">
-        <v>30432</v>
+        <v>30405</v>
       </c>
       <c r="N4" t="n">
-        <v>30905</v>
+        <v>30868</v>
       </c>
       <c r="O4" t="n">
-        <v>30893</v>
+        <v>30866</v>
       </c>
       <c r="P4" t="n">
-        <v>30789</v>
+        <v>30781</v>
       </c>
       <c r="Q4" t="n">
-        <v>30837</v>
+        <v>30855</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34747</v>
+        <v>34689</v>
       </c>
       <c r="C5" t="n">
-        <v>30605</v>
+        <v>30562</v>
       </c>
       <c r="D5" t="n">
-        <v>24090</v>
+        <v>24072</v>
       </c>
       <c r="E5" t="n">
-        <v>18448</v>
+        <v>18449</v>
       </c>
       <c r="F5" t="n">
-        <v>21132</v>
+        <v>21120</v>
       </c>
       <c r="G5" t="n">
-        <v>26773</v>
+        <v>26736</v>
       </c>
       <c r="H5" t="n">
-        <v>28531</v>
+        <v>28496</v>
       </c>
       <c r="I5" t="n">
-        <v>28872</v>
+        <v>28842</v>
       </c>
       <c r="J5" t="n">
-        <v>29481</v>
+        <v>29453</v>
       </c>
       <c r="K5" t="n">
-        <v>29913</v>
+        <v>29887</v>
       </c>
       <c r="L5" t="n">
-        <v>30226</v>
+        <v>30201</v>
       </c>
       <c r="M5" t="n">
-        <v>30454</v>
+        <v>30432</v>
       </c>
       <c r="N5" t="n">
-        <v>30916</v>
+        <v>30905</v>
       </c>
       <c r="O5" t="n">
-        <v>30890</v>
+        <v>30893</v>
       </c>
       <c r="P5" t="n">
-        <v>30770</v>
+        <v>30789</v>
       </c>
       <c r="Q5" t="n">
-        <v>30799</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C6" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D6" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E6" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F6" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G6" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H6" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I6" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J6" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K6" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L6" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M6" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N6" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O6" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P6" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q6" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C7" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D7" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E7" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F7" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G7" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H7" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I7" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J7" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K7" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L7" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M7" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N7" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O7" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P7" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q7" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C8" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D8" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E8" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F8" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G8" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H8" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I8" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J8" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K8" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L8" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M8" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N8" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O8" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P8" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q8" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C9" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D9" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E9" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F9" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G9" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H9" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I9" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J9" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K9" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L9" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M9" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N9" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O9" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P9" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q9" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C10" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D10" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E10" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F10" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G10" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H10" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I10" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J10" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K10" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L10" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M10" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N10" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O10" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P10" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q10" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C11" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D11" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E11" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F11" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G11" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H11" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I11" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J11" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K11" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L11" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M11" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N11" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O11" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P11" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q11" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C12" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D12" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E12" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F12" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G12" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H12" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I12" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J12" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K12" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L12" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M12" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N12" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O12" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P12" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q12" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C13" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D13" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E13" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F13" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G13" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H13" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I13" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J13" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K13" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L13" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M13" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N13" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O13" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P13" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q13" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C14" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D14" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E14" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F14" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G14" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H14" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I14" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J14" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K14" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L14" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M14" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N14" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O14" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P14" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q14" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C15" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D15" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E15" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F15" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G15" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H15" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I15" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J15" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K15" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L15" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M15" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N15" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O15" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P15" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q15" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C16" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D16" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E16" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F16" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G16" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H16" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I16" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J16" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K16" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L16" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M16" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N16" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O16" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P16" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q16" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C17" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D17" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E17" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F17" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G17" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H17" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I17" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J17" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K17" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L17" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M17" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N17" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O17" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P17" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q17" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C18" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D18" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E18" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F18" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G18" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H18" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I18" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J18" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K18" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L18" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M18" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N18" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O18" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P18" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q18" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C19" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D19" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E19" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F19" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G19" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H19" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I19" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J19" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K19" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L19" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M19" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N19" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O19" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P19" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q19" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C20" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D20" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E20" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F20" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G20" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H20" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I20" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J20" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K20" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L20" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M20" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N20" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O20" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P20" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q20" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C21" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D21" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E21" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F21" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G21" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H21" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I21" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J21" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K21" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L21" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M21" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N21" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O21" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P21" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q21" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31153</v>
+        <v>31299</v>
       </c>
       <c r="C22" t="n">
-        <v>28473</v>
+        <v>28523</v>
       </c>
       <c r="D22" t="n">
-        <v>24244</v>
+        <v>24152</v>
       </c>
       <c r="E22" t="n">
-        <v>20517</v>
+        <v>20342</v>
       </c>
       <c r="F22" t="n">
-        <v>22169</v>
+        <v>22138</v>
       </c>
       <c r="G22" t="n">
-        <v>25965</v>
+        <v>26109</v>
       </c>
       <c r="H22" t="n">
-        <v>27837</v>
+        <v>27874</v>
       </c>
       <c r="I22" t="n">
-        <v>28322</v>
+        <v>28305</v>
       </c>
       <c r="J22" t="n">
-        <v>28820</v>
+        <v>28797</v>
       </c>
       <c r="K22" t="n">
-        <v>29172</v>
+        <v>29143</v>
       </c>
       <c r="L22" t="n">
-        <v>29426</v>
+        <v>29392</v>
       </c>
       <c r="M22" t="n">
-        <v>29610</v>
+        <v>29572</v>
       </c>
       <c r="N22" t="n">
-        <v>29975</v>
+        <v>29922</v>
       </c>
       <c r="O22" t="n">
-        <v>29960</v>
+        <v>29894</v>
       </c>
       <c r="P22" t="n">
-        <v>29899</v>
+        <v>29821</v>
       </c>
       <c r="Q22" t="n">
-        <v>30009</v>
+        <v>29917</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,158 +510,158 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B2" t="n">
-        <v>3.601</v>
+        <v>3.6486</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1872</v>
+        <v>3.2232</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5308</v>
+        <v>2.5479</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9347</v>
+        <v>1.932</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1488</v>
+        <v>2.1462</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6608</v>
+        <v>2.6646</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8483</v>
+        <v>2.8506</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8884</v>
+        <v>2.8892</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9472</v>
+        <v>2.9479</v>
       </c>
       <c r="K2" t="n">
-        <v>2.989</v>
+        <v>2.9897</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0194</v>
+        <v>3.02</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0417</v>
+        <v>3.0422</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0881</v>
+        <v>3.0884</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0886</v>
+        <v>3.0887</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0812</v>
+        <v>3.0811</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0899</v>
+        <v>3.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B3" t="n">
-        <v>3.5465</v>
+        <v>3.601</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1449</v>
+        <v>3.1872</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5086</v>
+        <v>2.5308</v>
       </c>
       <c r="E3" t="n">
         <v>1.9347</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1504</v>
+        <v>2.1488</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6571</v>
+        <v>2.6608</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8454</v>
+        <v>2.8483</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8865</v>
+        <v>2.8884</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9452</v>
+        <v>2.9472</v>
       </c>
       <c r="K3" t="n">
-        <v>2.987</v>
+        <v>2.989</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0172</v>
+        <v>3.0194</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0394</v>
+        <v>3.0417</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0854</v>
+        <v>3.0881</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0854</v>
+        <v>3.0886</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0775</v>
+        <v>3.0812</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0855</v>
+        <v>3.0899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B4" t="n">
-        <v>3.4975</v>
+        <v>3.5465</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1024</v>
+        <v>3.1449</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4778</v>
+        <v>2.5086</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9206</v>
+        <v>1.9347</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1453</v>
+        <v>2.1504</v>
       </c>
       <c r="G4" t="n">
         <v>2.6571</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8448</v>
+        <v>2.8454</v>
       </c>
       <c r="I4" t="n">
-        <v>2.886</v>
+        <v>2.8865</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9454</v>
+        <v>2.9452</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9875</v>
+        <v>2.987</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0181</v>
+        <v>3.0172</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0405</v>
+        <v>3.0394</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0868</v>
+        <v>3.0854</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0866</v>
+        <v>3.0854</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0781</v>
+        <v>3.0775</v>
       </c>
       <c r="Q4" t="n">
         <v>3.0855</v>
@@ -669,956 +669,956 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4689</v>
+        <v>3.4975</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0562</v>
+        <v>3.1024</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4072</v>
+        <v>2.4778</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8449</v>
+        <v>1.9206</v>
       </c>
       <c r="F5" t="n">
-        <v>2.112</v>
+        <v>2.1453</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6736</v>
+        <v>2.6571</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8496</v>
+        <v>2.8448</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8842</v>
+        <v>2.886</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9453</v>
+        <v>2.9454</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9887</v>
+        <v>2.9875</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0201</v>
+        <v>3.0181</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0432</v>
+        <v>3.0405</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0905</v>
+        <v>3.0868</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0893</v>
+        <v>3.0866</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0789</v>
+        <v>3.0781</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0837</v>
+        <v>3.0855</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D6" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O6" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P6" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L7" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D8" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L8" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B9" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G9" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B10" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L10" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B11" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C11" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G11" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L11" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B12" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E12" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I12" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L12" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P12" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B13" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C13" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N13" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P13" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B14" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C14" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M14" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B15" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C15" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L15" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O15" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B16" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C16" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F16" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O16" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B17" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C17" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B18" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B19" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C19" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O19" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0236</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1313</v>
+        <v>3.1287</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8485</v>
+        <v>2.8452</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4044</v>
+        <v>2.4002</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0227</v>
+        <v>2.0199</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2163</v>
+        <v>2.2182</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6278</v>
+        <v>2.6352</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7974</v>
+        <v>2.8057</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8394</v>
+        <v>2.8472</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8904</v>
+        <v>2.8982</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9265</v>
+        <v>2.9342</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9528</v>
+        <v>2.9602</v>
       </c>
       <c r="M20" t="n">
-        <v>2.972</v>
+        <v>2.9792</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0124</v>
+        <v>3.0175</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0145</v>
+        <v>3.017</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0126</v>
+        <v>3.0117</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0282</v>
+        <v>3.0236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B21" t="n">
-        <v>3.133</v>
+        <v>3.1313</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8516</v>
+        <v>2.8485</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4092</v>
+        <v>2.4044</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0266</v>
+        <v>2.0227</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2146</v>
+        <v>2.2163</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6201</v>
+        <v>2.6278</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7878</v>
+        <v>2.7974</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8272</v>
+        <v>2.8394</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8757</v>
+        <v>2.8904</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9098</v>
+        <v>2.9265</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9343</v>
+        <v>2.9528</v>
       </c>
       <c r="M21" t="n">
-        <v>2.952</v>
+        <v>2.972</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9863</v>
+        <v>3.0124</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9834</v>
+        <v>3.0145</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9763</v>
+        <v>3.0126</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9862</v>
+        <v>3.0282</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B22" t="n">
-        <v>3.1299</v>
+        <v>3.133</v>
       </c>
       <c r="C22" t="n">
-        <v>2.8523</v>
+        <v>2.8516</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4152</v>
+        <v>2.4092</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0342</v>
+        <v>2.0266</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2138</v>
+        <v>2.2146</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6109</v>
+        <v>2.6201</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7874</v>
+        <v>2.7878</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8305</v>
+        <v>2.8272</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8797</v>
+        <v>2.8757</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9143</v>
+        <v>2.9098</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9392</v>
+        <v>2.9343</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9572</v>
+        <v>2.952</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9922</v>
+        <v>2.9863</v>
       </c>
       <c r="O22" t="n">
-        <v>2.9894</v>
+        <v>2.9834</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9821</v>
+        <v>2.9763</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9917</v>
+        <v>2.9862</v>
       </c>
     </row>
   </sheetData>
@@ -1725,163 +1725,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36010</v>
+        <v>36486</v>
       </c>
       <c r="C2" t="n">
-        <v>31872</v>
+        <v>32232</v>
       </c>
       <c r="D2" t="n">
-        <v>25308</v>
+        <v>25479</v>
       </c>
       <c r="E2" t="n">
-        <v>19347</v>
+        <v>19320</v>
       </c>
       <c r="F2" t="n">
-        <v>21488</v>
+        <v>21462</v>
       </c>
       <c r="G2" t="n">
-        <v>26608</v>
+        <v>26646</v>
       </c>
       <c r="H2" t="n">
-        <v>28483</v>
+        <v>28506</v>
       </c>
       <c r="I2" t="n">
-        <v>28884</v>
+        <v>28892</v>
       </c>
       <c r="J2" t="n">
-        <v>29472</v>
+        <v>29479</v>
       </c>
       <c r="K2" t="n">
-        <v>29890</v>
+        <v>29897</v>
       </c>
       <c r="L2" t="n">
-        <v>30194</v>
+        <v>302</v>
       </c>
       <c r="M2" t="n">
-        <v>30417</v>
+        <v>30422</v>
       </c>
       <c r="N2" t="n">
-        <v>30881</v>
+        <v>30884</v>
       </c>
       <c r="O2" t="n">
-        <v>30886</v>
+        <v>30887</v>
       </c>
       <c r="P2" t="n">
-        <v>30812</v>
+        <v>30811</v>
       </c>
       <c r="Q2" t="n">
-        <v>30899</v>
+        <v>30895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35465</v>
+        <v>36010</v>
       </c>
       <c r="C3" t="n">
-        <v>31449</v>
+        <v>31872</v>
       </c>
       <c r="D3" t="n">
-        <v>25086</v>
+        <v>25308</v>
       </c>
       <c r="E3" t="n">
         <v>19347</v>
       </c>
       <c r="F3" t="n">
-        <v>21504</v>
+        <v>21488</v>
       </c>
       <c r="G3" t="n">
-        <v>26571</v>
+        <v>26608</v>
       </c>
       <c r="H3" t="n">
-        <v>28454</v>
+        <v>28483</v>
       </c>
       <c r="I3" t="n">
-        <v>28865</v>
+        <v>28884</v>
       </c>
       <c r="J3" t="n">
-        <v>29452</v>
+        <v>29472</v>
       </c>
       <c r="K3" t="n">
-        <v>29870</v>
+        <v>29890</v>
       </c>
       <c r="L3" t="n">
-        <v>30172</v>
+        <v>30194</v>
       </c>
       <c r="M3" t="n">
-        <v>30394</v>
+        <v>30417</v>
       </c>
       <c r="N3" t="n">
-        <v>30854</v>
+        <v>30881</v>
       </c>
       <c r="O3" t="n">
-        <v>30854</v>
+        <v>30886</v>
       </c>
       <c r="P3" t="n">
-        <v>30775</v>
+        <v>30812</v>
       </c>
       <c r="Q3" t="n">
-        <v>30855</v>
+        <v>30899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34975</v>
+        <v>35465</v>
       </c>
       <c r="C4" t="n">
-        <v>31024</v>
+        <v>31449</v>
       </c>
       <c r="D4" t="n">
-        <v>24778</v>
+        <v>25086</v>
       </c>
       <c r="E4" t="n">
-        <v>19206</v>
+        <v>19347</v>
       </c>
       <c r="F4" t="n">
-        <v>21453</v>
+        <v>21504</v>
       </c>
       <c r="G4" t="n">
         <v>26571</v>
       </c>
       <c r="H4" t="n">
-        <v>28448</v>
+        <v>28454</v>
       </c>
       <c r="I4" t="n">
-        <v>28860</v>
+        <v>28865</v>
       </c>
       <c r="J4" t="n">
-        <v>29454</v>
+        <v>29452</v>
       </c>
       <c r="K4" t="n">
-        <v>29875</v>
+        <v>29870</v>
       </c>
       <c r="L4" t="n">
-        <v>30181</v>
+        <v>30172</v>
       </c>
       <c r="M4" t="n">
-        <v>30405</v>
+        <v>30394</v>
       </c>
       <c r="N4" t="n">
-        <v>30868</v>
+        <v>30854</v>
       </c>
       <c r="O4" t="n">
-        <v>30866</v>
+        <v>30854</v>
       </c>
       <c r="P4" t="n">
-        <v>30781</v>
+        <v>30775</v>
       </c>
       <c r="Q4" t="n">
         <v>30855</v>
@@ -1890,991 +1890,991 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34689</v>
+        <v>34975</v>
       </c>
       <c r="C5" t="n">
-        <v>30562</v>
+        <v>31024</v>
       </c>
       <c r="D5" t="n">
-        <v>24072</v>
+        <v>24778</v>
       </c>
       <c r="E5" t="n">
-        <v>18449</v>
+        <v>19206</v>
       </c>
       <c r="F5" t="n">
-        <v>21120</v>
+        <v>21453</v>
       </c>
       <c r="G5" t="n">
-        <v>26736</v>
+        <v>26571</v>
       </c>
       <c r="H5" t="n">
-        <v>28496</v>
+        <v>28448</v>
       </c>
       <c r="I5" t="n">
-        <v>28842</v>
+        <v>28860</v>
       </c>
       <c r="J5" t="n">
-        <v>29453</v>
+        <v>29454</v>
       </c>
       <c r="K5" t="n">
-        <v>29887</v>
+        <v>29875</v>
       </c>
       <c r="L5" t="n">
-        <v>30201</v>
+        <v>30181</v>
       </c>
       <c r="M5" t="n">
-        <v>30432</v>
+        <v>30405</v>
       </c>
       <c r="N5" t="n">
-        <v>30905</v>
+        <v>30868</v>
       </c>
       <c r="O5" t="n">
-        <v>30893</v>
+        <v>30866</v>
       </c>
       <c r="P5" t="n">
-        <v>30789</v>
+        <v>30781</v>
       </c>
       <c r="Q5" t="n">
-        <v>30837</v>
+        <v>30855</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34747</v>
+        <v>34689</v>
       </c>
       <c r="C6" t="n">
-        <v>30605</v>
+        <v>30562</v>
       </c>
       <c r="D6" t="n">
-        <v>24090</v>
+        <v>24072</v>
       </c>
       <c r="E6" t="n">
-        <v>18448</v>
+        <v>18449</v>
       </c>
       <c r="F6" t="n">
-        <v>21132</v>
+        <v>21120</v>
       </c>
       <c r="G6" t="n">
-        <v>26773</v>
+        <v>26736</v>
       </c>
       <c r="H6" t="n">
-        <v>28531</v>
+        <v>28496</v>
       </c>
       <c r="I6" t="n">
-        <v>28872</v>
+        <v>28842</v>
       </c>
       <c r="J6" t="n">
-        <v>29481</v>
+        <v>29453</v>
       </c>
       <c r="K6" t="n">
-        <v>29913</v>
+        <v>29887</v>
       </c>
       <c r="L6" t="n">
-        <v>30226</v>
+        <v>30201</v>
       </c>
       <c r="M6" t="n">
-        <v>30454</v>
+        <v>30432</v>
       </c>
       <c r="N6" t="n">
-        <v>30916</v>
+        <v>30905</v>
       </c>
       <c r="O6" t="n">
-        <v>30890</v>
+        <v>30893</v>
       </c>
       <c r="P6" t="n">
-        <v>30770</v>
+        <v>30789</v>
       </c>
       <c r="Q6" t="n">
-        <v>30799</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C7" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D7" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E7" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F7" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G7" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H7" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I7" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J7" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K7" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L7" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M7" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N7" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O7" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P7" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q7" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C8" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D8" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E8" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F8" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G8" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H8" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I8" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J8" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K8" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L8" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M8" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N8" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O8" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P8" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q8" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C9" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D9" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E9" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F9" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G9" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H9" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I9" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J9" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K9" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L9" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M9" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N9" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O9" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P9" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q9" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C10" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D10" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E10" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F10" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G10" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H10" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I10" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J10" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K10" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L10" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M10" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N10" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O10" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P10" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q10" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C11" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D11" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E11" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F11" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G11" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H11" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I11" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J11" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K11" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L11" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M11" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N11" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O11" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P11" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q11" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C12" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D12" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E12" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F12" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G12" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H12" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I12" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J12" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K12" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L12" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M12" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N12" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O12" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P12" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q12" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C13" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D13" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E13" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F13" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G13" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H13" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I13" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J13" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K13" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L13" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M13" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N13" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O13" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P13" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q13" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C14" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D14" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E14" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F14" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G14" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H14" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I14" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J14" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K14" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L14" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M14" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N14" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O14" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P14" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q14" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C15" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D15" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E15" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F15" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G15" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H15" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I15" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J15" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K15" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L15" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M15" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N15" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O15" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P15" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q15" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C16" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D16" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E16" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F16" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G16" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H16" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I16" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J16" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K16" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L16" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M16" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N16" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O16" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P16" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q16" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C17" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D17" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E17" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F17" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G17" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H17" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I17" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J17" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K17" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L17" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M17" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N17" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O17" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P17" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q17" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C18" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D18" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E18" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F18" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G18" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H18" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I18" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J18" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K18" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L18" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M18" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N18" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O18" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P18" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q18" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C19" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D19" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E19" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F19" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G19" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H19" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I19" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J19" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K19" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L19" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M19" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N19" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O19" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P19" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q19" t="n">
-        <v>30236</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31313</v>
+        <v>31287</v>
       </c>
       <c r="C20" t="n">
-        <v>28485</v>
+        <v>28452</v>
       </c>
       <c r="D20" t="n">
-        <v>24044</v>
+        <v>24002</v>
       </c>
       <c r="E20" t="n">
-        <v>20227</v>
+        <v>20199</v>
       </c>
       <c r="F20" t="n">
-        <v>22163</v>
+        <v>22182</v>
       </c>
       <c r="G20" t="n">
-        <v>26278</v>
+        <v>26352</v>
       </c>
       <c r="H20" t="n">
-        <v>27974</v>
+        <v>28057</v>
       </c>
       <c r="I20" t="n">
-        <v>28394</v>
+        <v>28472</v>
       </c>
       <c r="J20" t="n">
-        <v>28904</v>
+        <v>28982</v>
       </c>
       <c r="K20" t="n">
-        <v>29265</v>
+        <v>29342</v>
       </c>
       <c r="L20" t="n">
-        <v>29528</v>
+        <v>29602</v>
       </c>
       <c r="M20" t="n">
-        <v>29720</v>
+        <v>29792</v>
       </c>
       <c r="N20" t="n">
-        <v>30124</v>
+        <v>30175</v>
       </c>
       <c r="O20" t="n">
-        <v>30145</v>
+        <v>30170</v>
       </c>
       <c r="P20" t="n">
-        <v>30126</v>
+        <v>30117</v>
       </c>
       <c r="Q20" t="n">
-        <v>30282</v>
+        <v>30236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>31330</v>
+        <v>31313</v>
       </c>
       <c r="C21" t="n">
-        <v>28516</v>
+        <v>28485</v>
       </c>
       <c r="D21" t="n">
-        <v>24092</v>
+        <v>24044</v>
       </c>
       <c r="E21" t="n">
-        <v>20266</v>
+        <v>20227</v>
       </c>
       <c r="F21" t="n">
-        <v>22146</v>
+        <v>22163</v>
       </c>
       <c r="G21" t="n">
-        <v>26201</v>
+        <v>26278</v>
       </c>
       <c r="H21" t="n">
-        <v>27878</v>
+        <v>27974</v>
       </c>
       <c r="I21" t="n">
-        <v>28272</v>
+        <v>28394</v>
       </c>
       <c r="J21" t="n">
-        <v>28757</v>
+        <v>28904</v>
       </c>
       <c r="K21" t="n">
-        <v>29098</v>
+        <v>29265</v>
       </c>
       <c r="L21" t="n">
-        <v>29343</v>
+        <v>29528</v>
       </c>
       <c r="M21" t="n">
-        <v>29520</v>
+        <v>29720</v>
       </c>
       <c r="N21" t="n">
-        <v>29863</v>
+        <v>30124</v>
       </c>
       <c r="O21" t="n">
-        <v>29834</v>
+        <v>30145</v>
       </c>
       <c r="P21" t="n">
-        <v>29763</v>
+        <v>30126</v>
       </c>
       <c r="Q21" t="n">
-        <v>29862</v>
+        <v>30282</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31299</v>
+        <v>31330</v>
       </c>
       <c r="C22" t="n">
-        <v>28523</v>
+        <v>28516</v>
       </c>
       <c r="D22" t="n">
-        <v>24152</v>
+        <v>24092</v>
       </c>
       <c r="E22" t="n">
-        <v>20342</v>
+        <v>20266</v>
       </c>
       <c r="F22" t="n">
-        <v>22138</v>
+        <v>22146</v>
       </c>
       <c r="G22" t="n">
-        <v>26109</v>
+        <v>26201</v>
       </c>
       <c r="H22" t="n">
-        <v>27874</v>
+        <v>27878</v>
       </c>
       <c r="I22" t="n">
-        <v>28305</v>
+        <v>28272</v>
       </c>
       <c r="J22" t="n">
-        <v>28797</v>
+        <v>28757</v>
       </c>
       <c r="K22" t="n">
-        <v>29143</v>
+        <v>29098</v>
       </c>
       <c r="L22" t="n">
-        <v>29392</v>
+        <v>29343</v>
       </c>
       <c r="M22" t="n">
-        <v>29572</v>
+        <v>29520</v>
       </c>
       <c r="N22" t="n">
-        <v>29922</v>
+        <v>29863</v>
       </c>
       <c r="O22" t="n">
-        <v>29894</v>
+        <v>29834</v>
       </c>
       <c r="P22" t="n">
-        <v>29821</v>
+        <v>29763</v>
       </c>
       <c r="Q22" t="n">
-        <v>29917</v>
+        <v>29862</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,211 +510,211 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B2" t="n">
-        <v>3.6486</v>
+        <v>3.6507</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2232</v>
+        <v>3.2242</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5479</v>
+        <v>2.5471</v>
       </c>
       <c r="E2" t="n">
-        <v>1.932</v>
+        <v>1.9302</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1462</v>
+        <v>2.1463</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6646</v>
+        <v>2.6663</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8506</v>
+        <v>2.8498</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8892</v>
+        <v>2.8879</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9479</v>
+        <v>2.9469</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9897</v>
+        <v>2.9889</v>
       </c>
       <c r="L2" t="n">
-        <v>3.02</v>
+        <v>3.0194</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0422</v>
+        <v>3.0419</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0884</v>
+        <v>3.0894</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0887</v>
+        <v>3.0911</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0811</v>
+        <v>3.085</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0895</v>
+        <v>3.0953</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B3" t="n">
-        <v>3.601</v>
+        <v>3.6486</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1872</v>
+        <v>3.2232</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5308</v>
+        <v>2.5479</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9347</v>
+        <v>1.932</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1488</v>
+        <v>2.1462</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6608</v>
+        <v>2.6646</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8483</v>
+        <v>2.8506</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8884</v>
+        <v>2.8892</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9472</v>
+        <v>2.9479</v>
       </c>
       <c r="K3" t="n">
-        <v>2.989</v>
+        <v>2.9897</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0194</v>
+        <v>3.02</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0417</v>
+        <v>3.0422</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0881</v>
+        <v>3.0884</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0886</v>
+        <v>3.0887</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0812</v>
+        <v>3.0811</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0899</v>
+        <v>3.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B4" t="n">
-        <v>3.5465</v>
+        <v>3.601</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1449</v>
+        <v>3.1872</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5086</v>
+        <v>2.5308</v>
       </c>
       <c r="E4" t="n">
         <v>1.9347</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1504</v>
+        <v>2.1488</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6571</v>
+        <v>2.6608</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8454</v>
+        <v>2.8483</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8865</v>
+        <v>2.8884</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9452</v>
+        <v>2.9472</v>
       </c>
       <c r="K4" t="n">
-        <v>2.987</v>
+        <v>2.989</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0172</v>
+        <v>3.0194</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0394</v>
+        <v>3.0417</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0854</v>
+        <v>3.0881</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0854</v>
+        <v>3.0886</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0775</v>
+        <v>3.0812</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0855</v>
+        <v>3.0899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B5" t="n">
-        <v>3.4975</v>
+        <v>3.5465</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1024</v>
+        <v>3.1449</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4778</v>
+        <v>2.5086</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9206</v>
+        <v>1.9347</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1453</v>
+        <v>2.1504</v>
       </c>
       <c r="G5" t="n">
         <v>2.6571</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8448</v>
+        <v>2.8454</v>
       </c>
       <c r="I5" t="n">
-        <v>2.886</v>
+        <v>2.8865</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9454</v>
+        <v>2.9452</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9875</v>
+        <v>2.987</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0181</v>
+        <v>3.0172</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0405</v>
+        <v>3.0394</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0868</v>
+        <v>3.0854</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0866</v>
+        <v>3.0854</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0781</v>
+        <v>3.0775</v>
       </c>
       <c r="Q5" t="n">
         <v>3.0855</v>
@@ -722,903 +722,797 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4689</v>
+        <v>3.4975</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0562</v>
+        <v>3.1024</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4072</v>
+        <v>2.4778</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8449</v>
+        <v>1.9206</v>
       </c>
       <c r="F6" t="n">
-        <v>2.112</v>
+        <v>2.1453</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6736</v>
+        <v>2.6571</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8496</v>
+        <v>2.8448</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8842</v>
+        <v>2.886</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9453</v>
+        <v>2.9454</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9887</v>
+        <v>2.9875</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0201</v>
+        <v>3.0181</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0432</v>
+        <v>3.0405</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0905</v>
+        <v>3.0868</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0893</v>
+        <v>3.0866</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0789</v>
+        <v>3.0781</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0837</v>
+        <v>3.0855</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D7" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O7" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P7" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L8" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D9" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H9" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L9" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B10" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G10" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L10" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B11" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C11" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L11" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B12" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C12" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G12" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L12" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B13" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C13" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E13" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I13" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L13" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P13" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B14" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C14" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N14" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P14" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B15" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C15" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M15" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B16" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C16" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L16" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O16" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B17" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C17" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F17" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O17" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B18" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C18" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O18" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B19" t="n">
-        <v>3.229</v>
+        <v>3.3649</v>
       </c>
       <c r="C19" t="n">
-        <v>2.9294</v>
+        <v>3.0251</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4569</v>
+        <v>2.4879</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0409</v>
+        <v>2.0089</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2259</v>
+        <v>2.2051</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6397</v>
+        <v>2.6533</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8116</v>
+        <v>2.8229</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8521</v>
+        <v>2.8588</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9021</v>
+        <v>2.9094</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9374</v>
+        <v>2.9451</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9628</v>
+        <v>2.9706</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9813</v>
+        <v>2.9891</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0181</v>
+        <v>3.0246</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0167</v>
+        <v>3.0205</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0109</v>
+        <v>3.0111</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0222</v>
+        <v>3.0183</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B20" t="n">
-        <v>3.1287</v>
+        <v>3.229</v>
       </c>
       <c r="C20" t="n">
-        <v>2.8452</v>
+        <v>2.9294</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4002</v>
+        <v>2.4569</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0199</v>
+        <v>2.0409</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2182</v>
+        <v>2.2259</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6352</v>
+        <v>2.6397</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8057</v>
+        <v>2.8116</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8472</v>
+        <v>2.8521</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8982</v>
+        <v>2.9021</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9342</v>
+        <v>2.9374</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9602</v>
+        <v>2.9628</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9792</v>
+        <v>2.9813</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0175</v>
+        <v>3.0181</v>
       </c>
       <c r="O20" t="n">
-        <v>3.017</v>
+        <v>3.0167</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0117</v>
+        <v>3.0109</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0236</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B21" t="n">
-        <v>3.1313</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2.8485</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.4044</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.0227</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.2163</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.6278</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.7974</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.8394</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.8904</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.9265</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.9528</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.972</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.0124</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.0145</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3.0126</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.0282</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3.133</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.8516</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.4092</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.0266</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.2146</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.6201</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.7878</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.8272</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.8757</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.9098</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.9343</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.952</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.9863</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.9834</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.9763</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.9862</v>
+        <v>3.0222</v>
       </c>
     </row>
   </sheetData>
@@ -1632,7 +1526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,218 +1619,218 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36486</v>
+        <v>36507</v>
       </c>
       <c r="C2" t="n">
-        <v>32232</v>
+        <v>32242</v>
       </c>
       <c r="D2" t="n">
-        <v>25479</v>
+        <v>25471</v>
       </c>
       <c r="E2" t="n">
-        <v>19320</v>
+        <v>19302</v>
       </c>
       <c r="F2" t="n">
-        <v>21462</v>
+        <v>21463</v>
       </c>
       <c r="G2" t="n">
-        <v>26646</v>
+        <v>26663</v>
       </c>
       <c r="H2" t="n">
-        <v>28506</v>
+        <v>28498</v>
       </c>
       <c r="I2" t="n">
-        <v>28892</v>
+        <v>28879</v>
       </c>
       <c r="J2" t="n">
-        <v>29479</v>
+        <v>29469</v>
       </c>
       <c r="K2" t="n">
-        <v>29897</v>
+        <v>29889</v>
       </c>
       <c r="L2" t="n">
-        <v>302</v>
+        <v>30194</v>
       </c>
       <c r="M2" t="n">
-        <v>30422</v>
+        <v>30419</v>
       </c>
       <c r="N2" t="n">
-        <v>30884</v>
+        <v>30894</v>
       </c>
       <c r="O2" t="n">
-        <v>30887</v>
+        <v>30911</v>
       </c>
       <c r="P2" t="n">
-        <v>30811</v>
+        <v>30850</v>
       </c>
       <c r="Q2" t="n">
-        <v>30895</v>
+        <v>30953</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36010</v>
+        <v>36486</v>
       </c>
       <c r="C3" t="n">
-        <v>31872</v>
+        <v>32232</v>
       </c>
       <c r="D3" t="n">
-        <v>25308</v>
+        <v>25479</v>
       </c>
       <c r="E3" t="n">
-        <v>19347</v>
+        <v>19320</v>
       </c>
       <c r="F3" t="n">
-        <v>21488</v>
+        <v>21462</v>
       </c>
       <c r="G3" t="n">
-        <v>26608</v>
+        <v>26646</v>
       </c>
       <c r="H3" t="n">
-        <v>28483</v>
+        <v>28506</v>
       </c>
       <c r="I3" t="n">
-        <v>28884</v>
+        <v>28892</v>
       </c>
       <c r="J3" t="n">
-        <v>29472</v>
+        <v>29479</v>
       </c>
       <c r="K3" t="n">
-        <v>29890</v>
+        <v>29897</v>
       </c>
       <c r="L3" t="n">
-        <v>30194</v>
+        <v>302</v>
       </c>
       <c r="M3" t="n">
-        <v>30417</v>
+        <v>30422</v>
       </c>
       <c r="N3" t="n">
-        <v>30881</v>
+        <v>30884</v>
       </c>
       <c r="O3" t="n">
-        <v>30886</v>
+        <v>30887</v>
       </c>
       <c r="P3" t="n">
-        <v>30812</v>
+        <v>30811</v>
       </c>
       <c r="Q3" t="n">
-        <v>30899</v>
+        <v>30895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35465</v>
+        <v>36010</v>
       </c>
       <c r="C4" t="n">
-        <v>31449</v>
+        <v>31872</v>
       </c>
       <c r="D4" t="n">
-        <v>25086</v>
+        <v>25308</v>
       </c>
       <c r="E4" t="n">
         <v>19347</v>
       </c>
       <c r="F4" t="n">
-        <v>21504</v>
+        <v>21488</v>
       </c>
       <c r="G4" t="n">
-        <v>26571</v>
+        <v>26608</v>
       </c>
       <c r="H4" t="n">
-        <v>28454</v>
+        <v>28483</v>
       </c>
       <c r="I4" t="n">
-        <v>28865</v>
+        <v>28884</v>
       </c>
       <c r="J4" t="n">
-        <v>29452</v>
+        <v>29472</v>
       </c>
       <c r="K4" t="n">
-        <v>29870</v>
+        <v>29890</v>
       </c>
       <c r="L4" t="n">
-        <v>30172</v>
+        <v>30194</v>
       </c>
       <c r="M4" t="n">
-        <v>30394</v>
+        <v>30417</v>
       </c>
       <c r="N4" t="n">
-        <v>30854</v>
+        <v>30881</v>
       </c>
       <c r="O4" t="n">
-        <v>30854</v>
+        <v>30886</v>
       </c>
       <c r="P4" t="n">
-        <v>30775</v>
+        <v>30812</v>
       </c>
       <c r="Q4" t="n">
-        <v>30855</v>
+        <v>30899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34975</v>
+        <v>35465</v>
       </c>
       <c r="C5" t="n">
-        <v>31024</v>
+        <v>31449</v>
       </c>
       <c r="D5" t="n">
-        <v>24778</v>
+        <v>25086</v>
       </c>
       <c r="E5" t="n">
-        <v>19206</v>
+        <v>19347</v>
       </c>
       <c r="F5" t="n">
-        <v>21453</v>
+        <v>21504</v>
       </c>
       <c r="G5" t="n">
         <v>26571</v>
       </c>
       <c r="H5" t="n">
-        <v>28448</v>
+        <v>28454</v>
       </c>
       <c r="I5" t="n">
-        <v>28860</v>
+        <v>28865</v>
       </c>
       <c r="J5" t="n">
-        <v>29454</v>
+        <v>29452</v>
       </c>
       <c r="K5" t="n">
-        <v>29875</v>
+        <v>29870</v>
       </c>
       <c r="L5" t="n">
-        <v>30181</v>
+        <v>30172</v>
       </c>
       <c r="M5" t="n">
-        <v>30405</v>
+        <v>30394</v>
       </c>
       <c r="N5" t="n">
-        <v>30868</v>
+        <v>30854</v>
       </c>
       <c r="O5" t="n">
-        <v>30866</v>
+        <v>30854</v>
       </c>
       <c r="P5" t="n">
-        <v>30781</v>
+        <v>30775</v>
       </c>
       <c r="Q5" t="n">
         <v>30855</v>
@@ -1945,936 +1839,826 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34689</v>
+        <v>34975</v>
       </c>
       <c r="C6" t="n">
-        <v>30562</v>
+        <v>31024</v>
       </c>
       <c r="D6" t="n">
-        <v>24072</v>
+        <v>24778</v>
       </c>
       <c r="E6" t="n">
-        <v>18449</v>
+        <v>19206</v>
       </c>
       <c r="F6" t="n">
-        <v>21120</v>
+        <v>21453</v>
       </c>
       <c r="G6" t="n">
-        <v>26736</v>
+        <v>26571</v>
       </c>
       <c r="H6" t="n">
-        <v>28496</v>
+        <v>28448</v>
       </c>
       <c r="I6" t="n">
-        <v>28842</v>
+        <v>28860</v>
       </c>
       <c r="J6" t="n">
-        <v>29453</v>
+        <v>29454</v>
       </c>
       <c r="K6" t="n">
-        <v>29887</v>
+        <v>29875</v>
       </c>
       <c r="L6" t="n">
-        <v>30201</v>
+        <v>30181</v>
       </c>
       <c r="M6" t="n">
-        <v>30432</v>
+        <v>30405</v>
       </c>
       <c r="N6" t="n">
-        <v>30905</v>
+        <v>30868</v>
       </c>
       <c r="O6" t="n">
-        <v>30893</v>
+        <v>30866</v>
       </c>
       <c r="P6" t="n">
-        <v>30789</v>
+        <v>30781</v>
       </c>
       <c r="Q6" t="n">
-        <v>30837</v>
+        <v>30855</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34747</v>
+        <v>34689</v>
       </c>
       <c r="C7" t="n">
-        <v>30605</v>
+        <v>30562</v>
       </c>
       <c r="D7" t="n">
-        <v>24090</v>
+        <v>24072</v>
       </c>
       <c r="E7" t="n">
-        <v>18448</v>
+        <v>18449</v>
       </c>
       <c r="F7" t="n">
-        <v>21132</v>
+        <v>21120</v>
       </c>
       <c r="G7" t="n">
-        <v>26773</v>
+        <v>26736</v>
       </c>
       <c r="H7" t="n">
-        <v>28531</v>
+        <v>28496</v>
       </c>
       <c r="I7" t="n">
-        <v>28872</v>
+        <v>28842</v>
       </c>
       <c r="J7" t="n">
-        <v>29481</v>
+        <v>29453</v>
       </c>
       <c r="K7" t="n">
-        <v>29913</v>
+        <v>29887</v>
       </c>
       <c r="L7" t="n">
-        <v>30226</v>
+        <v>30201</v>
       </c>
       <c r="M7" t="n">
-        <v>30454</v>
+        <v>30432</v>
       </c>
       <c r="N7" t="n">
-        <v>30916</v>
+        <v>30905</v>
       </c>
       <c r="O7" t="n">
-        <v>30890</v>
+        <v>30893</v>
       </c>
       <c r="P7" t="n">
-        <v>30770</v>
+        <v>30789</v>
       </c>
       <c r="Q7" t="n">
-        <v>30799</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C8" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D8" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E8" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F8" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G8" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H8" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I8" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J8" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K8" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L8" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M8" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N8" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O8" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P8" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q8" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C9" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D9" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E9" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F9" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G9" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H9" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I9" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J9" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K9" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L9" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M9" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N9" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O9" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P9" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q9" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C10" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D10" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E10" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F10" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G10" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H10" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I10" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J10" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K10" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L10" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M10" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N10" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O10" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P10" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q10" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C11" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D11" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E11" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F11" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G11" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H11" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I11" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J11" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K11" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L11" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M11" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N11" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O11" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P11" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q11" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C12" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D12" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E12" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F12" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G12" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H12" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I12" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J12" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K12" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L12" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M12" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N12" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O12" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P12" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q12" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C13" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D13" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E13" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F13" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G13" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H13" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I13" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J13" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K13" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L13" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M13" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N13" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O13" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P13" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q13" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C14" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D14" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E14" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F14" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G14" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H14" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I14" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J14" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K14" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L14" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M14" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N14" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O14" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P14" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q14" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C15" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D15" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E15" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F15" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G15" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H15" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I15" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J15" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K15" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L15" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M15" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N15" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O15" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P15" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q15" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C16" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D16" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E16" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F16" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G16" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H16" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I16" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J16" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K16" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L16" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M16" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N16" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O16" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P16" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q16" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C17" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D17" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E17" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F17" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G17" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H17" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I17" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J17" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K17" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L17" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M17" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N17" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O17" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P17" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q17" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C18" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D18" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E18" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F18" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G18" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H18" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I18" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J18" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K18" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L18" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M18" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N18" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O18" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P18" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q18" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32290</v>
+        <v>33649</v>
       </c>
       <c r="C19" t="n">
-        <v>29294</v>
+        <v>30251</v>
       </c>
       <c r="D19" t="n">
-        <v>24569</v>
+        <v>24879</v>
       </c>
       <c r="E19" t="n">
-        <v>20409</v>
+        <v>20089</v>
       </c>
       <c r="F19" t="n">
-        <v>22259</v>
+        <v>22051</v>
       </c>
       <c r="G19" t="n">
-        <v>26397</v>
+        <v>26533</v>
       </c>
       <c r="H19" t="n">
-        <v>28116</v>
+        <v>28229</v>
       </c>
       <c r="I19" t="n">
-        <v>28521</v>
+        <v>28588</v>
       </c>
       <c r="J19" t="n">
-        <v>29021</v>
+        <v>29094</v>
       </c>
       <c r="K19" t="n">
-        <v>29374</v>
+        <v>29451</v>
       </c>
       <c r="L19" t="n">
-        <v>29628</v>
+        <v>29706</v>
       </c>
       <c r="M19" t="n">
-        <v>29813</v>
+        <v>29891</v>
       </c>
       <c r="N19" t="n">
-        <v>30181</v>
+        <v>30246</v>
       </c>
       <c r="O19" t="n">
-        <v>30167</v>
+        <v>30205</v>
       </c>
       <c r="P19" t="n">
-        <v>30109</v>
+        <v>30111</v>
       </c>
       <c r="Q19" t="n">
-        <v>30222</v>
+        <v>30183</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31287</v>
+        <v>32290</v>
       </c>
       <c r="C20" t="n">
-        <v>28452</v>
+        <v>29294</v>
       </c>
       <c r="D20" t="n">
-        <v>24002</v>
+        <v>24569</v>
       </c>
       <c r="E20" t="n">
-        <v>20199</v>
+        <v>20409</v>
       </c>
       <c r="F20" t="n">
-        <v>22182</v>
+        <v>22259</v>
       </c>
       <c r="G20" t="n">
-        <v>26352</v>
+        <v>26397</v>
       </c>
       <c r="H20" t="n">
-        <v>28057</v>
+        <v>28116</v>
       </c>
       <c r="I20" t="n">
-        <v>28472</v>
+        <v>28521</v>
       </c>
       <c r="J20" t="n">
-        <v>28982</v>
+        <v>29021</v>
       </c>
       <c r="K20" t="n">
-        <v>29342</v>
+        <v>29374</v>
       </c>
       <c r="L20" t="n">
-        <v>29602</v>
+        <v>29628</v>
       </c>
       <c r="M20" t="n">
-        <v>29792</v>
+        <v>29813</v>
       </c>
       <c r="N20" t="n">
-        <v>30175</v>
+        <v>30181</v>
       </c>
       <c r="O20" t="n">
-        <v>30170</v>
+        <v>30167</v>
       </c>
       <c r="P20" t="n">
-        <v>30117</v>
+        <v>30109</v>
       </c>
       <c r="Q20" t="n">
-        <v>30236</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>31313</v>
-      </c>
-      <c r="C21" t="n">
-        <v>28485</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24044</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20227</v>
-      </c>
-      <c r="F21" t="n">
-        <v>22163</v>
-      </c>
-      <c r="G21" t="n">
-        <v>26278</v>
-      </c>
-      <c r="H21" t="n">
-        <v>27974</v>
-      </c>
-      <c r="I21" t="n">
-        <v>28394</v>
-      </c>
-      <c r="J21" t="n">
-        <v>28904</v>
-      </c>
-      <c r="K21" t="n">
-        <v>29265</v>
-      </c>
-      <c r="L21" t="n">
-        <v>29528</v>
-      </c>
-      <c r="M21" t="n">
-        <v>29720</v>
-      </c>
-      <c r="N21" t="n">
-        <v>30124</v>
-      </c>
-      <c r="O21" t="n">
-        <v>30145</v>
-      </c>
-      <c r="P21" t="n">
-        <v>30126</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>30282</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>31330</v>
-      </c>
-      <c r="C22" t="n">
-        <v>28516</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24092</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20266</v>
-      </c>
-      <c r="F22" t="n">
-        <v>22146</v>
-      </c>
-      <c r="G22" t="n">
-        <v>26201</v>
-      </c>
-      <c r="H22" t="n">
-        <v>27878</v>
-      </c>
-      <c r="I22" t="n">
-        <v>28272</v>
-      </c>
-      <c r="J22" t="n">
-        <v>28757</v>
-      </c>
-      <c r="K22" t="n">
-        <v>29098</v>
-      </c>
-      <c r="L22" t="n">
-        <v>29343</v>
-      </c>
-      <c r="M22" t="n">
-        <v>29520</v>
-      </c>
-      <c r="N22" t="n">
-        <v>29863</v>
-      </c>
-      <c r="O22" t="n">
-        <v>29834</v>
-      </c>
-      <c r="P22" t="n">
-        <v>29763</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>29862</v>
+        <v>30222</v>
       </c>
     </row>
   </sheetData>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,264 +510,264 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B2" t="n">
-        <v>3.6507</v>
+        <v>3.652</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2242</v>
+        <v>3.2228</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5471</v>
+        <v>2.5419</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9302</v>
+        <v>1.9234</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1463</v>
+        <v>2.1446</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6663</v>
+        <v>2.6719</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8498</v>
+        <v>2.8609</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8879</v>
+        <v>2.9025</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9469</v>
+        <v>2.9642</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9889</v>
+        <v>3.0081</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0194</v>
+        <v>3.0401</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0419</v>
+        <v>3.0637</v>
       </c>
       <c r="N2" t="n">
-        <v>3.0894</v>
+        <v>3.1133</v>
       </c>
       <c r="O2" t="n">
-        <v>3.0911</v>
+        <v>3.1145</v>
       </c>
       <c r="P2" t="n">
-        <v>3.085</v>
+        <v>3.1067</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0953</v>
+        <v>3.1147</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B3" t="n">
-        <v>3.6486</v>
+        <v>3.6507</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2232</v>
+        <v>3.2242</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5479</v>
+        <v>2.5471</v>
       </c>
       <c r="E3" t="n">
-        <v>1.932</v>
+        <v>1.9302</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1462</v>
+        <v>2.1463</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6646</v>
+        <v>2.6663</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8506</v>
+        <v>2.8498</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8892</v>
+        <v>2.8879</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9479</v>
+        <v>2.9469</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9897</v>
+        <v>2.9889</v>
       </c>
       <c r="L3" t="n">
-        <v>3.02</v>
+        <v>3.0194</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0422</v>
+        <v>3.0419</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0884</v>
+        <v>3.0894</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0887</v>
+        <v>3.0911</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0811</v>
+        <v>3.085</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0895</v>
+        <v>3.0953</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B4" t="n">
-        <v>3.601</v>
+        <v>3.6486</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1872</v>
+        <v>3.2232</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5308</v>
+        <v>2.5479</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9347</v>
+        <v>1.932</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1488</v>
+        <v>2.1462</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6608</v>
+        <v>2.6646</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8483</v>
+        <v>2.8506</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8884</v>
+        <v>2.8892</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9472</v>
+        <v>2.9479</v>
       </c>
       <c r="K4" t="n">
-        <v>2.989</v>
+        <v>2.9897</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0194</v>
+        <v>3.02</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0417</v>
+        <v>3.0422</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0881</v>
+        <v>3.0884</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0886</v>
+        <v>3.0887</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0812</v>
+        <v>3.0811</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0899</v>
+        <v>3.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B5" t="n">
-        <v>3.5465</v>
+        <v>3.601</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1449</v>
+        <v>3.1872</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5086</v>
+        <v>2.5308</v>
       </c>
       <c r="E5" t="n">
         <v>1.9347</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1504</v>
+        <v>2.1488</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6571</v>
+        <v>2.6608</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8454</v>
+        <v>2.8483</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8865</v>
+        <v>2.8884</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9452</v>
+        <v>2.9472</v>
       </c>
       <c r="K5" t="n">
-        <v>2.987</v>
+        <v>2.989</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0172</v>
+        <v>3.0194</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0394</v>
+        <v>3.0417</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0854</v>
+        <v>3.0881</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0854</v>
+        <v>3.0886</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0775</v>
+        <v>3.0812</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0855</v>
+        <v>3.0899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B6" t="n">
-        <v>3.4975</v>
+        <v>3.5465</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1024</v>
+        <v>3.1449</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4778</v>
+        <v>2.5086</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9206</v>
+        <v>1.9347</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1453</v>
+        <v>2.1504</v>
       </c>
       <c r="G6" t="n">
         <v>2.6571</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8448</v>
+        <v>2.8454</v>
       </c>
       <c r="I6" t="n">
-        <v>2.886</v>
+        <v>2.8865</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9454</v>
+        <v>2.9452</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9875</v>
+        <v>2.987</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0181</v>
+        <v>3.0172</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0405</v>
+        <v>3.0394</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0868</v>
+        <v>3.0854</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0866</v>
+        <v>3.0854</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0781</v>
+        <v>3.0775</v>
       </c>
       <c r="Q6" t="n">
         <v>3.0855</v>
@@ -775,743 +775,796 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4689</v>
+        <v>3.4975</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0562</v>
+        <v>3.1024</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4072</v>
+        <v>2.4778</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8449</v>
+        <v>1.9206</v>
       </c>
       <c r="F7" t="n">
-        <v>2.112</v>
+        <v>2.1453</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6736</v>
+        <v>2.6571</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8496</v>
+        <v>2.8448</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8842</v>
+        <v>2.886</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9453</v>
+        <v>2.9454</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9887</v>
+        <v>2.9875</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0201</v>
+        <v>3.0181</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0432</v>
+        <v>3.0405</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0905</v>
+        <v>3.0868</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0893</v>
+        <v>3.0866</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0789</v>
+        <v>3.0781</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0837</v>
+        <v>3.0855</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D8" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O8" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P8" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L9" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D10" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H10" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L10" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B11" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G11" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L11" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B12" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C12" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L12" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B13" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C13" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G13" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L13" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B14" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C14" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E14" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I14" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P14" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B15" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C15" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N15" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P15" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B16" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C16" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M16" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B17" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C17" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L17" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O17" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P17" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B18" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C18" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F18" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O18" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B19" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C19" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O19" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.3649</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.0251</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.4879</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.0089</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.2051</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.6533</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.8229</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.8588</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.9094</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.9451</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.9706</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.9891</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.0246</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.0205</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.0111</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.0183</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>3.229</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>2.9294</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>2.4569</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>2.0409</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>2.2259</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>2.6397</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>2.8116</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>2.8521</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>2.9021</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>2.9374</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2.9628</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>2.9813</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>3.0181</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>3.0167</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>3.0109</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>3.0222</v>
       </c>
     </row>
@@ -1526,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1619,273 +1672,273 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36507</v>
+        <v>36520</v>
       </c>
       <c r="C2" t="n">
-        <v>32242</v>
+        <v>32228</v>
       </c>
       <c r="D2" t="n">
-        <v>25471</v>
+        <v>25419</v>
       </c>
       <c r="E2" t="n">
-        <v>19302</v>
+        <v>19234</v>
       </c>
       <c r="F2" t="n">
-        <v>21463</v>
+        <v>21446</v>
       </c>
       <c r="G2" t="n">
-        <v>26663</v>
+        <v>26719</v>
       </c>
       <c r="H2" t="n">
-        <v>28498</v>
+        <v>28609</v>
       </c>
       <c r="I2" t="n">
-        <v>28879</v>
+        <v>29025</v>
       </c>
       <c r="J2" t="n">
-        <v>29469</v>
+        <v>29642</v>
       </c>
       <c r="K2" t="n">
-        <v>29889</v>
+        <v>30081</v>
       </c>
       <c r="L2" t="n">
-        <v>30194</v>
+        <v>30401</v>
       </c>
       <c r="M2" t="n">
-        <v>30419</v>
+        <v>30637</v>
       </c>
       <c r="N2" t="n">
-        <v>30894</v>
+        <v>31133</v>
       </c>
       <c r="O2" t="n">
-        <v>30911</v>
+        <v>31145</v>
       </c>
       <c r="P2" t="n">
-        <v>30850</v>
+        <v>31067</v>
       </c>
       <c r="Q2" t="n">
-        <v>30953</v>
+        <v>31147</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36486</v>
+        <v>36507</v>
       </c>
       <c r="C3" t="n">
-        <v>32232</v>
+        <v>32242</v>
       </c>
       <c r="D3" t="n">
-        <v>25479</v>
+        <v>25471</v>
       </c>
       <c r="E3" t="n">
-        <v>19320</v>
+        <v>19302</v>
       </c>
       <c r="F3" t="n">
-        <v>21462</v>
+        <v>21463</v>
       </c>
       <c r="G3" t="n">
-        <v>26646</v>
+        <v>26663</v>
       </c>
       <c r="H3" t="n">
-        <v>28506</v>
+        <v>28498</v>
       </c>
       <c r="I3" t="n">
-        <v>28892</v>
+        <v>28879</v>
       </c>
       <c r="J3" t="n">
-        <v>29479</v>
+        <v>29469</v>
       </c>
       <c r="K3" t="n">
-        <v>29897</v>
+        <v>29889</v>
       </c>
       <c r="L3" t="n">
-        <v>302</v>
+        <v>30194</v>
       </c>
       <c r="M3" t="n">
-        <v>30422</v>
+        <v>30419</v>
       </c>
       <c r="N3" t="n">
-        <v>30884</v>
+        <v>30894</v>
       </c>
       <c r="O3" t="n">
-        <v>30887</v>
+        <v>30911</v>
       </c>
       <c r="P3" t="n">
-        <v>30811</v>
+        <v>30850</v>
       </c>
       <c r="Q3" t="n">
-        <v>30895</v>
+        <v>30953</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36010</v>
+        <v>36486</v>
       </c>
       <c r="C4" t="n">
-        <v>31872</v>
+        <v>32232</v>
       </c>
       <c r="D4" t="n">
-        <v>25308</v>
+        <v>25479</v>
       </c>
       <c r="E4" t="n">
-        <v>19347</v>
+        <v>19320</v>
       </c>
       <c r="F4" t="n">
-        <v>21488</v>
+        <v>21462</v>
       </c>
       <c r="G4" t="n">
-        <v>26608</v>
+        <v>26646</v>
       </c>
       <c r="H4" t="n">
-        <v>28483</v>
+        <v>28506</v>
       </c>
       <c r="I4" t="n">
-        <v>28884</v>
+        <v>28892</v>
       </c>
       <c r="J4" t="n">
-        <v>29472</v>
+        <v>29479</v>
       </c>
       <c r="K4" t="n">
-        <v>29890</v>
+        <v>29897</v>
       </c>
       <c r="L4" t="n">
-        <v>30194</v>
+        <v>302</v>
       </c>
       <c r="M4" t="n">
-        <v>30417</v>
+        <v>30422</v>
       </c>
       <c r="N4" t="n">
-        <v>30881</v>
+        <v>30884</v>
       </c>
       <c r="O4" t="n">
-        <v>30886</v>
+        <v>30887</v>
       </c>
       <c r="P4" t="n">
-        <v>30812</v>
+        <v>30811</v>
       </c>
       <c r="Q4" t="n">
-        <v>30899</v>
+        <v>30895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35465</v>
+        <v>36010</v>
       </c>
       <c r="C5" t="n">
-        <v>31449</v>
+        <v>31872</v>
       </c>
       <c r="D5" t="n">
-        <v>25086</v>
+        <v>25308</v>
       </c>
       <c r="E5" t="n">
         <v>19347</v>
       </c>
       <c r="F5" t="n">
-        <v>21504</v>
+        <v>21488</v>
       </c>
       <c r="G5" t="n">
-        <v>26571</v>
+        <v>26608</v>
       </c>
       <c r="H5" t="n">
-        <v>28454</v>
+        <v>28483</v>
       </c>
       <c r="I5" t="n">
-        <v>28865</v>
+        <v>28884</v>
       </c>
       <c r="J5" t="n">
-        <v>29452</v>
+        <v>29472</v>
       </c>
       <c r="K5" t="n">
-        <v>29870</v>
+        <v>29890</v>
       </c>
       <c r="L5" t="n">
-        <v>30172</v>
+        <v>30194</v>
       </c>
       <c r="M5" t="n">
-        <v>30394</v>
+        <v>30417</v>
       </c>
       <c r="N5" t="n">
-        <v>30854</v>
+        <v>30881</v>
       </c>
       <c r="O5" t="n">
-        <v>30854</v>
+        <v>30886</v>
       </c>
       <c r="P5" t="n">
-        <v>30775</v>
+        <v>30812</v>
       </c>
       <c r="Q5" t="n">
-        <v>30855</v>
+        <v>30899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34975</v>
+        <v>35465</v>
       </c>
       <c r="C6" t="n">
-        <v>31024</v>
+        <v>31449</v>
       </c>
       <c r="D6" t="n">
-        <v>24778</v>
+        <v>25086</v>
       </c>
       <c r="E6" t="n">
-        <v>19206</v>
+        <v>19347</v>
       </c>
       <c r="F6" t="n">
-        <v>21453</v>
+        <v>21504</v>
       </c>
       <c r="G6" t="n">
         <v>26571</v>
       </c>
       <c r="H6" t="n">
-        <v>28448</v>
+        <v>28454</v>
       </c>
       <c r="I6" t="n">
-        <v>28860</v>
+        <v>28865</v>
       </c>
       <c r="J6" t="n">
-        <v>29454</v>
+        <v>29452</v>
       </c>
       <c r="K6" t="n">
-        <v>29875</v>
+        <v>29870</v>
       </c>
       <c r="L6" t="n">
-        <v>30181</v>
+        <v>30172</v>
       </c>
       <c r="M6" t="n">
-        <v>30405</v>
+        <v>30394</v>
       </c>
       <c r="N6" t="n">
-        <v>30868</v>
+        <v>30854</v>
       </c>
       <c r="O6" t="n">
-        <v>30866</v>
+        <v>30854</v>
       </c>
       <c r="P6" t="n">
-        <v>30781</v>
+        <v>30775</v>
       </c>
       <c r="Q6" t="n">
         <v>30855</v>
@@ -1894,770 +1947,825 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34689</v>
+        <v>34975</v>
       </c>
       <c r="C7" t="n">
-        <v>30562</v>
+        <v>31024</v>
       </c>
       <c r="D7" t="n">
-        <v>24072</v>
+        <v>24778</v>
       </c>
       <c r="E7" t="n">
-        <v>18449</v>
+        <v>19206</v>
       </c>
       <c r="F7" t="n">
-        <v>21120</v>
+        <v>21453</v>
       </c>
       <c r="G7" t="n">
-        <v>26736</v>
+        <v>26571</v>
       </c>
       <c r="H7" t="n">
-        <v>28496</v>
+        <v>28448</v>
       </c>
       <c r="I7" t="n">
-        <v>28842</v>
+        <v>28860</v>
       </c>
       <c r="J7" t="n">
-        <v>29453</v>
+        <v>29454</v>
       </c>
       <c r="K7" t="n">
-        <v>29887</v>
+        <v>29875</v>
       </c>
       <c r="L7" t="n">
-        <v>30201</v>
+        <v>30181</v>
       </c>
       <c r="M7" t="n">
-        <v>30432</v>
+        <v>30405</v>
       </c>
       <c r="N7" t="n">
-        <v>30905</v>
+        <v>30868</v>
       </c>
       <c r="O7" t="n">
-        <v>30893</v>
+        <v>30866</v>
       </c>
       <c r="P7" t="n">
-        <v>30789</v>
+        <v>30781</v>
       </c>
       <c r="Q7" t="n">
-        <v>30837</v>
+        <v>30855</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34747</v>
+        <v>34689</v>
       </c>
       <c r="C8" t="n">
-        <v>30605</v>
+        <v>30562</v>
       </c>
       <c r="D8" t="n">
-        <v>24090</v>
+        <v>24072</v>
       </c>
       <c r="E8" t="n">
-        <v>18448</v>
+        <v>18449</v>
       </c>
       <c r="F8" t="n">
-        <v>21132</v>
+        <v>21120</v>
       </c>
       <c r="G8" t="n">
-        <v>26773</v>
+        <v>26736</v>
       </c>
       <c r="H8" t="n">
-        <v>28531</v>
+        <v>28496</v>
       </c>
       <c r="I8" t="n">
-        <v>28872</v>
+        <v>28842</v>
       </c>
       <c r="J8" t="n">
-        <v>29481</v>
+        <v>29453</v>
       </c>
       <c r="K8" t="n">
-        <v>29913</v>
+        <v>29887</v>
       </c>
       <c r="L8" t="n">
-        <v>30226</v>
+        <v>30201</v>
       </c>
       <c r="M8" t="n">
-        <v>30454</v>
+        <v>30432</v>
       </c>
       <c r="N8" t="n">
-        <v>30916</v>
+        <v>30905</v>
       </c>
       <c r="O8" t="n">
-        <v>30890</v>
+        <v>30893</v>
       </c>
       <c r="P8" t="n">
-        <v>30770</v>
+        <v>30789</v>
       </c>
       <c r="Q8" t="n">
-        <v>30799</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C9" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D9" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E9" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F9" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G9" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H9" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I9" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J9" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K9" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L9" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M9" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N9" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O9" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P9" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q9" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C10" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D10" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E10" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F10" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G10" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H10" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I10" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J10" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K10" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L10" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M10" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N10" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O10" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P10" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q10" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C11" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D11" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E11" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F11" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G11" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H11" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I11" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J11" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K11" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L11" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M11" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N11" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O11" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P11" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q11" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C12" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D12" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E12" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F12" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G12" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H12" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I12" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J12" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K12" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L12" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M12" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N12" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O12" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P12" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q12" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C13" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D13" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E13" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F13" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G13" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H13" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I13" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J13" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K13" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L13" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M13" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N13" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O13" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P13" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q13" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C14" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D14" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E14" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F14" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G14" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H14" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I14" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J14" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K14" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L14" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M14" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N14" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O14" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P14" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q14" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C15" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D15" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E15" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F15" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G15" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H15" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I15" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J15" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K15" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L15" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M15" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N15" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O15" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P15" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q15" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C16" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D16" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E16" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F16" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G16" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H16" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I16" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J16" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K16" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L16" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M16" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N16" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O16" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P16" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q16" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C17" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D17" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E17" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F17" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G17" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H17" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I17" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J17" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K17" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L17" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M17" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N17" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O17" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P17" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q17" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C18" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D18" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E18" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F18" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G18" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H18" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I18" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J18" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K18" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L18" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M18" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N18" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O18" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P18" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q18" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C19" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D19" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E19" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F19" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G19" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H19" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I19" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J19" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K19" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L19" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M19" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N19" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O19" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P19" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q19" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>33649</v>
+      </c>
+      <c r="C20" t="n">
+        <v>30251</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24879</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20089</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22051</v>
+      </c>
+      <c r="G20" t="n">
+        <v>26533</v>
+      </c>
+      <c r="H20" t="n">
+        <v>28229</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28588</v>
+      </c>
+      <c r="J20" t="n">
+        <v>29094</v>
+      </c>
+      <c r="K20" t="n">
+        <v>29451</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29706</v>
+      </c>
+      <c r="M20" t="n">
+        <v>29891</v>
+      </c>
+      <c r="N20" t="n">
+        <v>30246</v>
+      </c>
+      <c r="O20" t="n">
+        <v>30205</v>
+      </c>
+      <c r="P20" t="n">
+        <v>30111</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>30183</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>28/09/2026</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>32290</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>29294</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>24569</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>20409</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>22259</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>26397</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>28116</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>28521</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>29021</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>29374</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>29628</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>29813</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>30181</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>30167</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>30109</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>30222</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,317 +510,317 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B2" t="n">
-        <v>3.652</v>
+        <v>3.6819</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2228</v>
+        <v>3.2455</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5419</v>
+        <v>2.5528</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9234</v>
+        <v>1.9218</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1446</v>
+        <v>2.1427</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6719</v>
+        <v>2.6755</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8609</v>
+        <v>2.8684</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9025</v>
+        <v>2.9099</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9642</v>
+        <v>2.9712</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0081</v>
+        <v>3.0146</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0401</v>
+        <v>3.046</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0637</v>
+        <v>3.0689</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1133</v>
+        <v>3.1143</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1145</v>
+        <v>3.1101</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1067</v>
+        <v>3.0959</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1147</v>
+        <v>3.0964</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B3" t="n">
-        <v>3.6507</v>
+        <v>3.652</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2242</v>
+        <v>3.2228</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5471</v>
+        <v>2.5419</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9302</v>
+        <v>1.9234</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1463</v>
+        <v>2.1446</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6663</v>
+        <v>2.6719</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8498</v>
+        <v>2.8609</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8879</v>
+        <v>2.9025</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9469</v>
+        <v>2.9642</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9889</v>
+        <v>3.0081</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0194</v>
+        <v>3.0401</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0419</v>
+        <v>3.0637</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0894</v>
+        <v>3.1133</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0911</v>
+        <v>3.1145</v>
       </c>
       <c r="P3" t="n">
-        <v>3.085</v>
+        <v>3.1067</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0953</v>
+        <v>3.1147</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B4" t="n">
-        <v>3.6486</v>
+        <v>3.6507</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2232</v>
+        <v>3.2242</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5479</v>
+        <v>2.5471</v>
       </c>
       <c r="E4" t="n">
-        <v>1.932</v>
+        <v>1.9302</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1462</v>
+        <v>2.1463</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6646</v>
+        <v>2.6663</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8506</v>
+        <v>2.8498</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8892</v>
+        <v>2.8879</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9479</v>
+        <v>2.9469</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9897</v>
+        <v>2.9889</v>
       </c>
       <c r="L4" t="n">
-        <v>3.02</v>
+        <v>3.0194</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0422</v>
+        <v>3.0419</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0884</v>
+        <v>3.0894</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0887</v>
+        <v>3.0911</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0811</v>
+        <v>3.085</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0895</v>
+        <v>3.0953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B5" t="n">
-        <v>3.601</v>
+        <v>3.6486</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1872</v>
+        <v>3.2232</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5308</v>
+        <v>2.5479</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9347</v>
+        <v>1.932</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1488</v>
+        <v>2.1462</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6608</v>
+        <v>2.6646</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8483</v>
+        <v>2.8506</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8884</v>
+        <v>2.8892</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9472</v>
+        <v>2.9479</v>
       </c>
       <c r="K5" t="n">
-        <v>2.989</v>
+        <v>2.9897</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0194</v>
+        <v>3.02</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0417</v>
+        <v>3.0422</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0881</v>
+        <v>3.0884</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0886</v>
+        <v>3.0887</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0812</v>
+        <v>3.0811</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0899</v>
+        <v>3.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B6" t="n">
-        <v>3.5465</v>
+        <v>3.601</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1449</v>
+        <v>3.1872</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5086</v>
+        <v>2.5308</v>
       </c>
       <c r="E6" t="n">
         <v>1.9347</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1504</v>
+        <v>2.1488</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6571</v>
+        <v>2.6608</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8454</v>
+        <v>2.8483</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8865</v>
+        <v>2.8884</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9452</v>
+        <v>2.9472</v>
       </c>
       <c r="K6" t="n">
-        <v>2.987</v>
+        <v>2.989</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0172</v>
+        <v>3.0194</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0394</v>
+        <v>3.0417</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0854</v>
+        <v>3.0881</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0854</v>
+        <v>3.0886</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0775</v>
+        <v>3.0812</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0855</v>
+        <v>3.0899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B7" t="n">
-        <v>3.4975</v>
+        <v>3.5465</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1024</v>
+        <v>3.1449</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4778</v>
+        <v>2.5086</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9206</v>
+        <v>1.9347</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1453</v>
+        <v>2.1504</v>
       </c>
       <c r="G7" t="n">
         <v>2.6571</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8448</v>
+        <v>2.8454</v>
       </c>
       <c r="I7" t="n">
-        <v>2.886</v>
+        <v>2.8865</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9454</v>
+        <v>2.9452</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9875</v>
+        <v>2.987</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0181</v>
+        <v>3.0172</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0405</v>
+        <v>3.0394</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0868</v>
+        <v>3.0854</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0866</v>
+        <v>3.0854</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0781</v>
+        <v>3.0775</v>
       </c>
       <c r="Q7" t="n">
         <v>3.0855</v>
@@ -828,743 +828,796 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4689</v>
+        <v>3.4975</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0562</v>
+        <v>3.1024</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4072</v>
+        <v>2.4778</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8449</v>
+        <v>1.9206</v>
       </c>
       <c r="F8" t="n">
-        <v>2.112</v>
+        <v>2.1453</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6736</v>
+        <v>2.6571</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8496</v>
+        <v>2.8448</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8842</v>
+        <v>2.886</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9453</v>
+        <v>2.9454</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9887</v>
+        <v>2.9875</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0201</v>
+        <v>3.0181</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0432</v>
+        <v>3.0405</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0905</v>
+        <v>3.0868</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0893</v>
+        <v>3.0866</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0789</v>
+        <v>3.0781</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.0837</v>
+        <v>3.0855</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D9" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O9" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P9" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L10" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O10" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B11" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D11" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L11" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B12" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G12" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L12" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B13" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C13" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L13" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B14" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C14" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G14" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8884</v>
+        <v>2.8901</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9463</v>
+        <v>2.9494</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9869</v>
+        <v>2.9911</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0159</v>
+        <v>3.021</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0368</v>
+        <v>3.0427</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0747</v>
+        <v>3.0831</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0647</v>
+        <v>3.0748</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0451</v>
+        <v>3.0566</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0397</v>
+        <v>3.0526</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B15" t="n">
-        <v>3.5091</v>
+        <v>3.5523</v>
       </c>
       <c r="C15" t="n">
-        <v>3.0914</v>
+        <v>3.112</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4344</v>
+        <v>2.4198</v>
       </c>
       <c r="E15" t="n">
-        <v>1.865</v>
+        <v>1.8216</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1353</v>
+        <v>2.1083</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7001</v>
+        <v>2.704</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8559</v>
+        <v>2.8653</v>
       </c>
       <c r="I15" t="n">
-        <v>2.879</v>
+        <v>2.8884</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9344</v>
+        <v>2.9463</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9734</v>
+        <v>2.9869</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0015</v>
+        <v>3.0159</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0219</v>
+        <v>3.0368</v>
       </c>
       <c r="N15" t="n">
-        <v>3.0613</v>
+        <v>3.0747</v>
       </c>
       <c r="O15" t="n">
-        <v>3.0564</v>
+        <v>3.0647</v>
       </c>
       <c r="P15" t="n">
-        <v>3.044</v>
+        <v>3.0451</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0473</v>
+        <v>3.0397</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B16" t="n">
-        <v>3.4844</v>
+        <v>3.5091</v>
       </c>
       <c r="C16" t="n">
-        <v>3.1097</v>
+        <v>3.0914</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5168</v>
+        <v>2.4344</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9857</v>
+        <v>1.865</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1957</v>
+        <v>2.1353</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6758</v>
+        <v>2.7001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8396</v>
+        <v>2.8559</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8725</v>
+        <v>2.879</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9259</v>
+        <v>2.9344</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9639</v>
+        <v>2.9734</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9917</v>
+        <v>3.0015</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0122</v>
+        <v>3.0219</v>
       </c>
       <c r="N16" t="n">
-        <v>3.057</v>
+        <v>3.0613</v>
       </c>
       <c r="O16" t="n">
-        <v>3.0622</v>
+        <v>3.0564</v>
       </c>
       <c r="P16" t="n">
-        <v>3.063</v>
+        <v>3.044</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.0819</v>
+        <v>3.0473</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B17" t="n">
-        <v>3.4754</v>
+        <v>3.4844</v>
       </c>
       <c r="C17" t="n">
-        <v>3.1048</v>
+        <v>3.1097</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5182</v>
+        <v>2.5168</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9919</v>
+        <v>1.9857</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1983</v>
+        <v>2.1957</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6723</v>
+        <v>2.6758</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8347</v>
+        <v>2.8396</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8678</v>
+        <v>2.8725</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9215</v>
+        <v>2.9259</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9605</v>
+        <v>2.9639</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9897</v>
+        <v>2.9917</v>
       </c>
       <c r="M17" t="n">
-        <v>3.012</v>
+        <v>3.0122</v>
       </c>
       <c r="N17" t="n">
-        <v>3.0695</v>
+        <v>3.057</v>
       </c>
       <c r="O17" t="n">
-        <v>3.0918</v>
+        <v>3.0622</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1134</v>
+        <v>3.063</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1571</v>
+        <v>3.0819</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B18" t="n">
-        <v>3.4773</v>
+        <v>3.4754</v>
       </c>
       <c r="C18" t="n">
-        <v>3.1075</v>
+        <v>3.1048</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5219</v>
+        <v>2.5182</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9945</v>
+        <v>1.9919</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1965</v>
+        <v>2.1983</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6724</v>
+        <v>2.6723</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8569</v>
+        <v>2.8347</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8953</v>
+        <v>2.8678</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9488</v>
+        <v>2.9215</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9867</v>
+        <v>2.9605</v>
       </c>
       <c r="L18" t="n">
-        <v>3.014</v>
+        <v>2.9897</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0339</v>
+        <v>3.012</v>
       </c>
       <c r="N18" t="n">
-        <v>3.0734</v>
+        <v>3.0695</v>
       </c>
       <c r="O18" t="n">
-        <v>3.071</v>
+        <v>3.0918</v>
       </c>
       <c r="P18" t="n">
-        <v>3.0624</v>
+        <v>3.1134</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.0705</v>
+        <v>3.1571</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B19" t="n">
-        <v>3.4784</v>
+        <v>3.4773</v>
       </c>
       <c r="C19" t="n">
-        <v>3.11</v>
+        <v>3.1075</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5262</v>
+        <v>2.5219</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9982</v>
+        <v>1.9945</v>
       </c>
       <c r="F19" t="n">
-        <v>2.195</v>
+        <v>2.1965</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6649</v>
+        <v>2.6724</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8459</v>
+        <v>2.8569</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8808</v>
+        <v>2.8953</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9311</v>
+        <v>2.9488</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9663</v>
+        <v>2.9867</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9912</v>
+        <v>3.014</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0088</v>
+        <v>3.0339</v>
       </c>
       <c r="N19" t="n">
-        <v>3.0387</v>
+        <v>3.0734</v>
       </c>
       <c r="O19" t="n">
-        <v>3.027</v>
+        <v>3.071</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0086</v>
+        <v>3.0624</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.0056</v>
+        <v>3.0705</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B20" t="n">
-        <v>3.3649</v>
+        <v>3.4784</v>
       </c>
       <c r="C20" t="n">
-        <v>3.0251</v>
+        <v>3.11</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4879</v>
+        <v>2.5262</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0089</v>
+        <v>1.9982</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2051</v>
+        <v>2.195</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6533</v>
+        <v>2.6649</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8229</v>
+        <v>2.8459</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8588</v>
+        <v>2.8808</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9094</v>
+        <v>2.9311</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9451</v>
+        <v>2.9663</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9706</v>
+        <v>2.9912</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9891</v>
+        <v>3.0088</v>
       </c>
       <c r="N20" t="n">
-        <v>3.0246</v>
+        <v>3.0387</v>
       </c>
       <c r="O20" t="n">
-        <v>3.0205</v>
+        <v>3.027</v>
       </c>
       <c r="P20" t="n">
-        <v>3.0111</v>
+        <v>3.0086</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.0183</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.3649</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.0251</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.4879</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.0089</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2051</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.6533</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.8229</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8588</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.9094</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9451</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.9706</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.9891</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.0246</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.0205</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.0111</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.0183</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>3.229</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>2.9294</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>2.4569</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>2.0409</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>2.2259</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>2.6397</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>2.8116</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>2.8521</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2.9021</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2.9374</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>2.9628</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>2.9813</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>3.0181</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>3.0167</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>3.0109</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>3.0222</v>
       </c>
     </row>
@@ -1579,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,328 +1725,328 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36520</v>
+        <v>36819</v>
       </c>
       <c r="C2" t="n">
-        <v>32228</v>
+        <v>32455</v>
       </c>
       <c r="D2" t="n">
-        <v>25419</v>
+        <v>25528</v>
       </c>
       <c r="E2" t="n">
-        <v>19234</v>
+        <v>19218</v>
       </c>
       <c r="F2" t="n">
-        <v>21446</v>
+        <v>21427</v>
       </c>
       <c r="G2" t="n">
-        <v>26719</v>
+        <v>26755</v>
       </c>
       <c r="H2" t="n">
-        <v>28609</v>
+        <v>28684</v>
       </c>
       <c r="I2" t="n">
-        <v>29025</v>
+        <v>29099</v>
       </c>
       <c r="J2" t="n">
-        <v>29642</v>
+        <v>29712</v>
       </c>
       <c r="K2" t="n">
-        <v>30081</v>
+        <v>30146</v>
       </c>
       <c r="L2" t="n">
-        <v>30401</v>
+        <v>30460</v>
       </c>
       <c r="M2" t="n">
-        <v>30637</v>
+        <v>30689</v>
       </c>
       <c r="N2" t="n">
-        <v>31133</v>
+        <v>31143</v>
       </c>
       <c r="O2" t="n">
-        <v>31145</v>
+        <v>31101</v>
       </c>
       <c r="P2" t="n">
-        <v>31067</v>
+        <v>30959</v>
       </c>
       <c r="Q2" t="n">
-        <v>31147</v>
+        <v>30964</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36507</v>
+        <v>36520</v>
       </c>
       <c r="C3" t="n">
-        <v>32242</v>
+        <v>32228</v>
       </c>
       <c r="D3" t="n">
-        <v>25471</v>
+        <v>25419</v>
       </c>
       <c r="E3" t="n">
-        <v>19302</v>
+        <v>19234</v>
       </c>
       <c r="F3" t="n">
-        <v>21463</v>
+        <v>21446</v>
       </c>
       <c r="G3" t="n">
-        <v>26663</v>
+        <v>26719</v>
       </c>
       <c r="H3" t="n">
-        <v>28498</v>
+        <v>28609</v>
       </c>
       <c r="I3" t="n">
-        <v>28879</v>
+        <v>29025</v>
       </c>
       <c r="J3" t="n">
-        <v>29469</v>
+        <v>29642</v>
       </c>
       <c r="K3" t="n">
-        <v>29889</v>
+        <v>30081</v>
       </c>
       <c r="L3" t="n">
-        <v>30194</v>
+        <v>30401</v>
       </c>
       <c r="M3" t="n">
-        <v>30419</v>
+        <v>30637</v>
       </c>
       <c r="N3" t="n">
-        <v>30894</v>
+        <v>31133</v>
       </c>
       <c r="O3" t="n">
-        <v>30911</v>
+        <v>31145</v>
       </c>
       <c r="P3" t="n">
-        <v>30850</v>
+        <v>31067</v>
       </c>
       <c r="Q3" t="n">
-        <v>30953</v>
+        <v>31147</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36486</v>
+        <v>36507</v>
       </c>
       <c r="C4" t="n">
-        <v>32232</v>
+        <v>32242</v>
       </c>
       <c r="D4" t="n">
-        <v>25479</v>
+        <v>25471</v>
       </c>
       <c r="E4" t="n">
-        <v>19320</v>
+        <v>19302</v>
       </c>
       <c r="F4" t="n">
-        <v>21462</v>
+        <v>21463</v>
       </c>
       <c r="G4" t="n">
-        <v>26646</v>
+        <v>26663</v>
       </c>
       <c r="H4" t="n">
-        <v>28506</v>
+        <v>28498</v>
       </c>
       <c r="I4" t="n">
-        <v>28892</v>
+        <v>28879</v>
       </c>
       <c r="J4" t="n">
-        <v>29479</v>
+        <v>29469</v>
       </c>
       <c r="K4" t="n">
-        <v>29897</v>
+        <v>29889</v>
       </c>
       <c r="L4" t="n">
-        <v>302</v>
+        <v>30194</v>
       </c>
       <c r="M4" t="n">
-        <v>30422</v>
+        <v>30419</v>
       </c>
       <c r="N4" t="n">
-        <v>30884</v>
+        <v>30894</v>
       </c>
       <c r="O4" t="n">
-        <v>30887</v>
+        <v>30911</v>
       </c>
       <c r="P4" t="n">
-        <v>30811</v>
+        <v>30850</v>
       </c>
       <c r="Q4" t="n">
-        <v>30895</v>
+        <v>30953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36010</v>
+        <v>36486</v>
       </c>
       <c r="C5" t="n">
-        <v>31872</v>
+        <v>32232</v>
       </c>
       <c r="D5" t="n">
-        <v>25308</v>
+        <v>25479</v>
       </c>
       <c r="E5" t="n">
-        <v>19347</v>
+        <v>19320</v>
       </c>
       <c r="F5" t="n">
-        <v>21488</v>
+        <v>21462</v>
       </c>
       <c r="G5" t="n">
-        <v>26608</v>
+        <v>26646</v>
       </c>
       <c r="H5" t="n">
-        <v>28483</v>
+        <v>28506</v>
       </c>
       <c r="I5" t="n">
-        <v>28884</v>
+        <v>28892</v>
       </c>
       <c r="J5" t="n">
-        <v>29472</v>
+        <v>29479</v>
       </c>
       <c r="K5" t="n">
-        <v>29890</v>
+        <v>29897</v>
       </c>
       <c r="L5" t="n">
-        <v>30194</v>
+        <v>302</v>
       </c>
       <c r="M5" t="n">
-        <v>30417</v>
+        <v>30422</v>
       </c>
       <c r="N5" t="n">
-        <v>30881</v>
+        <v>30884</v>
       </c>
       <c r="O5" t="n">
-        <v>30886</v>
+        <v>30887</v>
       </c>
       <c r="P5" t="n">
-        <v>30812</v>
+        <v>30811</v>
       </c>
       <c r="Q5" t="n">
-        <v>30899</v>
+        <v>30895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35465</v>
+        <v>36010</v>
       </c>
       <c r="C6" t="n">
-        <v>31449</v>
+        <v>31872</v>
       </c>
       <c r="D6" t="n">
-        <v>25086</v>
+        <v>25308</v>
       </c>
       <c r="E6" t="n">
         <v>19347</v>
       </c>
       <c r="F6" t="n">
-        <v>21504</v>
+        <v>21488</v>
       </c>
       <c r="G6" t="n">
-        <v>26571</v>
+        <v>26608</v>
       </c>
       <c r="H6" t="n">
-        <v>28454</v>
+        <v>28483</v>
       </c>
       <c r="I6" t="n">
-        <v>28865</v>
+        <v>28884</v>
       </c>
       <c r="J6" t="n">
-        <v>29452</v>
+        <v>29472</v>
       </c>
       <c r="K6" t="n">
-        <v>29870</v>
+        <v>29890</v>
       </c>
       <c r="L6" t="n">
-        <v>30172</v>
+        <v>30194</v>
       </c>
       <c r="M6" t="n">
-        <v>30394</v>
+        <v>30417</v>
       </c>
       <c r="N6" t="n">
-        <v>30854</v>
+        <v>30881</v>
       </c>
       <c r="O6" t="n">
-        <v>30854</v>
+        <v>30886</v>
       </c>
       <c r="P6" t="n">
-        <v>30775</v>
+        <v>30812</v>
       </c>
       <c r="Q6" t="n">
-        <v>30855</v>
+        <v>30899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34975</v>
+        <v>35465</v>
       </c>
       <c r="C7" t="n">
-        <v>31024</v>
+        <v>31449</v>
       </c>
       <c r="D7" t="n">
-        <v>24778</v>
+        <v>25086</v>
       </c>
       <c r="E7" t="n">
-        <v>19206</v>
+        <v>19347</v>
       </c>
       <c r="F7" t="n">
-        <v>21453</v>
+        <v>21504</v>
       </c>
       <c r="G7" t="n">
         <v>26571</v>
       </c>
       <c r="H7" t="n">
-        <v>28448</v>
+        <v>28454</v>
       </c>
       <c r="I7" t="n">
-        <v>28860</v>
+        <v>28865</v>
       </c>
       <c r="J7" t="n">
-        <v>29454</v>
+        <v>29452</v>
       </c>
       <c r="K7" t="n">
-        <v>29875</v>
+        <v>29870</v>
       </c>
       <c r="L7" t="n">
-        <v>30181</v>
+        <v>30172</v>
       </c>
       <c r="M7" t="n">
-        <v>30405</v>
+        <v>30394</v>
       </c>
       <c r="N7" t="n">
-        <v>30868</v>
+        <v>30854</v>
       </c>
       <c r="O7" t="n">
-        <v>30866</v>
+        <v>30854</v>
       </c>
       <c r="P7" t="n">
-        <v>30781</v>
+        <v>30775</v>
       </c>
       <c r="Q7" t="n">
         <v>30855</v>
@@ -2002,770 +2055,825 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34689</v>
+        <v>34975</v>
       </c>
       <c r="C8" t="n">
-        <v>30562</v>
+        <v>31024</v>
       </c>
       <c r="D8" t="n">
-        <v>24072</v>
+        <v>24778</v>
       </c>
       <c r="E8" t="n">
-        <v>18449</v>
+        <v>19206</v>
       </c>
       <c r="F8" t="n">
-        <v>21120</v>
+        <v>21453</v>
       </c>
       <c r="G8" t="n">
-        <v>26736</v>
+        <v>26571</v>
       </c>
       <c r="H8" t="n">
-        <v>28496</v>
+        <v>28448</v>
       </c>
       <c r="I8" t="n">
-        <v>28842</v>
+        <v>28860</v>
       </c>
       <c r="J8" t="n">
-        <v>29453</v>
+        <v>29454</v>
       </c>
       <c r="K8" t="n">
-        <v>29887</v>
+        <v>29875</v>
       </c>
       <c r="L8" t="n">
-        <v>30201</v>
+        <v>30181</v>
       </c>
       <c r="M8" t="n">
-        <v>30432</v>
+        <v>30405</v>
       </c>
       <c r="N8" t="n">
-        <v>30905</v>
+        <v>30868</v>
       </c>
       <c r="O8" t="n">
-        <v>30893</v>
+        <v>30866</v>
       </c>
       <c r="P8" t="n">
-        <v>30789</v>
+        <v>30781</v>
       </c>
       <c r="Q8" t="n">
-        <v>30837</v>
+        <v>30855</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34747</v>
+        <v>34689</v>
       </c>
       <c r="C9" t="n">
-        <v>30605</v>
+        <v>30562</v>
       </c>
       <c r="D9" t="n">
-        <v>24090</v>
+        <v>24072</v>
       </c>
       <c r="E9" t="n">
-        <v>18448</v>
+        <v>18449</v>
       </c>
       <c r="F9" t="n">
-        <v>21132</v>
+        <v>21120</v>
       </c>
       <c r="G9" t="n">
-        <v>26773</v>
+        <v>26736</v>
       </c>
       <c r="H9" t="n">
-        <v>28531</v>
+        <v>28496</v>
       </c>
       <c r="I9" t="n">
-        <v>28872</v>
+        <v>28842</v>
       </c>
       <c r="J9" t="n">
-        <v>29481</v>
+        <v>29453</v>
       </c>
       <c r="K9" t="n">
-        <v>29913</v>
+        <v>29887</v>
       </c>
       <c r="L9" t="n">
-        <v>30226</v>
+        <v>30201</v>
       </c>
       <c r="M9" t="n">
-        <v>30454</v>
+        <v>30432</v>
       </c>
       <c r="N9" t="n">
-        <v>30916</v>
+        <v>30905</v>
       </c>
       <c r="O9" t="n">
-        <v>30890</v>
+        <v>30893</v>
       </c>
       <c r="P9" t="n">
-        <v>30770</v>
+        <v>30789</v>
       </c>
       <c r="Q9" t="n">
-        <v>30799</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34821</v>
+        <v>34747</v>
       </c>
       <c r="C10" t="n">
-        <v>30657</v>
+        <v>30605</v>
       </c>
       <c r="D10" t="n">
-        <v>24108</v>
+        <v>24090</v>
       </c>
       <c r="E10" t="n">
-        <v>18438</v>
+        <v>18448</v>
       </c>
       <c r="F10" t="n">
-        <v>21138</v>
+        <v>21132</v>
       </c>
       <c r="G10" t="n">
-        <v>26815</v>
+        <v>26773</v>
       </c>
       <c r="H10" t="n">
-        <v>28582</v>
+        <v>28531</v>
       </c>
       <c r="I10" t="n">
-        <v>28917</v>
+        <v>28872</v>
       </c>
       <c r="J10" t="n">
-        <v>29522</v>
+        <v>29481</v>
       </c>
       <c r="K10" t="n">
-        <v>29951</v>
+        <v>29913</v>
       </c>
       <c r="L10" t="n">
-        <v>30260</v>
+        <v>30226</v>
       </c>
       <c r="M10" t="n">
-        <v>30485</v>
+        <v>30454</v>
       </c>
       <c r="N10" t="n">
-        <v>30929</v>
+        <v>30916</v>
       </c>
       <c r="O10" t="n">
-        <v>30883</v>
+        <v>30890</v>
       </c>
       <c r="P10" t="n">
-        <v>30741</v>
+        <v>30770</v>
       </c>
       <c r="Q10" t="n">
-        <v>30745</v>
+        <v>30799</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34947</v>
+        <v>34821</v>
       </c>
       <c r="C11" t="n">
-        <v>30738</v>
+        <v>30657</v>
       </c>
       <c r="D11" t="n">
-        <v>24120</v>
+        <v>24108</v>
       </c>
       <c r="E11" t="n">
-        <v>18393</v>
+        <v>18438</v>
       </c>
       <c r="F11" t="n">
-        <v>21128</v>
+        <v>21138</v>
       </c>
       <c r="G11" t="n">
-        <v>26861</v>
+        <v>26815</v>
       </c>
       <c r="H11" t="n">
-        <v>286</v>
+        <v>28582</v>
       </c>
       <c r="I11" t="n">
-        <v>28916</v>
+        <v>28917</v>
       </c>
       <c r="J11" t="n">
-        <v>29518</v>
+        <v>29522</v>
       </c>
       <c r="K11" t="n">
-        <v>29943</v>
+        <v>29951</v>
       </c>
       <c r="L11" t="n">
-        <v>30250</v>
+        <v>30260</v>
       </c>
       <c r="M11" t="n">
-        <v>30473</v>
+        <v>30485</v>
       </c>
       <c r="N11" t="n">
-        <v>30907</v>
+        <v>30929</v>
       </c>
       <c r="O11" t="n">
-        <v>30854</v>
+        <v>30883</v>
       </c>
       <c r="P11" t="n">
-        <v>30704</v>
+        <v>30741</v>
       </c>
       <c r="Q11" t="n">
-        <v>30699</v>
+        <v>30745</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35237</v>
+        <v>34947</v>
       </c>
       <c r="C12" t="n">
-        <v>30955</v>
+        <v>30738</v>
       </c>
       <c r="D12" t="n">
-        <v>24217</v>
+        <v>24120</v>
       </c>
       <c r="E12" t="n">
-        <v>18365</v>
+        <v>18393</v>
       </c>
       <c r="F12" t="n">
-        <v>21101</v>
+        <v>21128</v>
       </c>
       <c r="G12" t="n">
-        <v>26880</v>
+        <v>26861</v>
       </c>
       <c r="H12" t="n">
-        <v>28617</v>
+        <v>286</v>
       </c>
       <c r="I12" t="n">
-        <v>28917</v>
+        <v>28916</v>
       </c>
       <c r="J12" t="n">
-        <v>29512</v>
+        <v>29518</v>
       </c>
       <c r="K12" t="n">
-        <v>29933</v>
+        <v>29943</v>
       </c>
       <c r="L12" t="n">
-        <v>30235</v>
+        <v>30250</v>
       </c>
       <c r="M12" t="n">
-        <v>30454</v>
+        <v>30473</v>
       </c>
       <c r="N12" t="n">
-        <v>30875</v>
+        <v>30907</v>
       </c>
       <c r="O12" t="n">
-        <v>30812</v>
+        <v>30854</v>
       </c>
       <c r="P12" t="n">
-        <v>30652</v>
+        <v>30704</v>
       </c>
       <c r="Q12" t="n">
-        <v>30638</v>
+        <v>30699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35625</v>
+        <v>35237</v>
       </c>
       <c r="C13" t="n">
-        <v>31161</v>
+        <v>30955</v>
       </c>
       <c r="D13" t="n">
-        <v>24142</v>
+        <v>24217</v>
       </c>
       <c r="E13" t="n">
-        <v>18072</v>
+        <v>18365</v>
       </c>
       <c r="F13" t="n">
-        <v>20971</v>
+        <v>21101</v>
       </c>
       <c r="G13" t="n">
-        <v>27002</v>
+        <v>26880</v>
       </c>
       <c r="H13" t="n">
-        <v>28655</v>
+        <v>28617</v>
       </c>
       <c r="I13" t="n">
-        <v>28901</v>
+        <v>28917</v>
       </c>
       <c r="J13" t="n">
-        <v>29494</v>
+        <v>29512</v>
       </c>
       <c r="K13" t="n">
-        <v>29911</v>
+        <v>29933</v>
       </c>
       <c r="L13" t="n">
-        <v>30210</v>
+        <v>30235</v>
       </c>
       <c r="M13" t="n">
-        <v>30427</v>
+        <v>30454</v>
       </c>
       <c r="N13" t="n">
-        <v>30831</v>
+        <v>30875</v>
       </c>
       <c r="O13" t="n">
-        <v>30748</v>
+        <v>30812</v>
       </c>
       <c r="P13" t="n">
-        <v>30566</v>
+        <v>30652</v>
       </c>
       <c r="Q13" t="n">
-        <v>30526</v>
+        <v>30638</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35523</v>
+        <v>35625</v>
       </c>
       <c r="C14" t="n">
-        <v>31120</v>
+        <v>31161</v>
       </c>
       <c r="D14" t="n">
-        <v>24198</v>
+        <v>24142</v>
       </c>
       <c r="E14" t="n">
-        <v>18216</v>
+        <v>18072</v>
       </c>
       <c r="F14" t="n">
-        <v>21083</v>
+        <v>20971</v>
       </c>
       <c r="G14" t="n">
-        <v>27040</v>
+        <v>27002</v>
       </c>
       <c r="H14" t="n">
-        <v>28653</v>
+        <v>28655</v>
       </c>
       <c r="I14" t="n">
-        <v>28884</v>
+        <v>28901</v>
       </c>
       <c r="J14" t="n">
-        <v>29463</v>
+        <v>29494</v>
       </c>
       <c r="K14" t="n">
-        <v>29869</v>
+        <v>29911</v>
       </c>
       <c r="L14" t="n">
-        <v>30159</v>
+        <v>30210</v>
       </c>
       <c r="M14" t="n">
-        <v>30368</v>
+        <v>30427</v>
       </c>
       <c r="N14" t="n">
-        <v>30747</v>
+        <v>30831</v>
       </c>
       <c r="O14" t="n">
-        <v>30647</v>
+        <v>30748</v>
       </c>
       <c r="P14" t="n">
-        <v>30451</v>
+        <v>30566</v>
       </c>
       <c r="Q14" t="n">
-        <v>30397</v>
+        <v>30526</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35091</v>
+        <v>35523</v>
       </c>
       <c r="C15" t="n">
-        <v>30914</v>
+        <v>31120</v>
       </c>
       <c r="D15" t="n">
-        <v>24344</v>
+        <v>24198</v>
       </c>
       <c r="E15" t="n">
-        <v>18650</v>
+        <v>18216</v>
       </c>
       <c r="F15" t="n">
-        <v>21353</v>
+        <v>21083</v>
       </c>
       <c r="G15" t="n">
-        <v>27001</v>
+        <v>27040</v>
       </c>
       <c r="H15" t="n">
-        <v>28559</v>
+        <v>28653</v>
       </c>
       <c r="I15" t="n">
-        <v>28790</v>
+        <v>28884</v>
       </c>
       <c r="J15" t="n">
-        <v>29344</v>
+        <v>29463</v>
       </c>
       <c r="K15" t="n">
-        <v>29734</v>
+        <v>29869</v>
       </c>
       <c r="L15" t="n">
-        <v>30015</v>
+        <v>30159</v>
       </c>
       <c r="M15" t="n">
-        <v>30219</v>
+        <v>30368</v>
       </c>
       <c r="N15" t="n">
-        <v>30613</v>
+        <v>30747</v>
       </c>
       <c r="O15" t="n">
-        <v>30564</v>
+        <v>30647</v>
       </c>
       <c r="P15" t="n">
-        <v>30440</v>
+        <v>30451</v>
       </c>
       <c r="Q15" t="n">
-        <v>30473</v>
+        <v>30397</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34844</v>
+        <v>35091</v>
       </c>
       <c r="C16" t="n">
-        <v>31097</v>
+        <v>30914</v>
       </c>
       <c r="D16" t="n">
-        <v>25168</v>
+        <v>24344</v>
       </c>
       <c r="E16" t="n">
-        <v>19857</v>
+        <v>18650</v>
       </c>
       <c r="F16" t="n">
-        <v>21957</v>
+        <v>21353</v>
       </c>
       <c r="G16" t="n">
-        <v>26758</v>
+        <v>27001</v>
       </c>
       <c r="H16" t="n">
-        <v>28396</v>
+        <v>28559</v>
       </c>
       <c r="I16" t="n">
-        <v>28725</v>
+        <v>28790</v>
       </c>
       <c r="J16" t="n">
-        <v>29259</v>
+        <v>29344</v>
       </c>
       <c r="K16" t="n">
-        <v>29639</v>
+        <v>29734</v>
       </c>
       <c r="L16" t="n">
-        <v>29917</v>
+        <v>30015</v>
       </c>
       <c r="M16" t="n">
-        <v>30122</v>
+        <v>30219</v>
       </c>
       <c r="N16" t="n">
-        <v>30570</v>
+        <v>30613</v>
       </c>
       <c r="O16" t="n">
-        <v>30622</v>
+        <v>30564</v>
       </c>
       <c r="P16" t="n">
-        <v>30630</v>
+        <v>30440</v>
       </c>
       <c r="Q16" t="n">
-        <v>30819</v>
+        <v>30473</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34754</v>
+        <v>34844</v>
       </c>
       <c r="C17" t="n">
-        <v>31048</v>
+        <v>31097</v>
       </c>
       <c r="D17" t="n">
-        <v>25182</v>
+        <v>25168</v>
       </c>
       <c r="E17" t="n">
-        <v>19919</v>
+        <v>19857</v>
       </c>
       <c r="F17" t="n">
-        <v>21983</v>
+        <v>21957</v>
       </c>
       <c r="G17" t="n">
-        <v>26723</v>
+        <v>26758</v>
       </c>
       <c r="H17" t="n">
-        <v>28347</v>
+        <v>28396</v>
       </c>
       <c r="I17" t="n">
-        <v>28678</v>
+        <v>28725</v>
       </c>
       <c r="J17" t="n">
-        <v>29215</v>
+        <v>29259</v>
       </c>
       <c r="K17" t="n">
-        <v>29605</v>
+        <v>29639</v>
       </c>
       <c r="L17" t="n">
-        <v>29897</v>
+        <v>29917</v>
       </c>
       <c r="M17" t="n">
-        <v>30120</v>
+        <v>30122</v>
       </c>
       <c r="N17" t="n">
-        <v>30695</v>
+        <v>30570</v>
       </c>
       <c r="O17" t="n">
-        <v>30918</v>
+        <v>30622</v>
       </c>
       <c r="P17" t="n">
-        <v>31134</v>
+        <v>30630</v>
       </c>
       <c r="Q17" t="n">
-        <v>31571</v>
+        <v>30819</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34773</v>
+        <v>34754</v>
       </c>
       <c r="C18" t="n">
-        <v>31075</v>
+        <v>31048</v>
       </c>
       <c r="D18" t="n">
-        <v>25219</v>
+        <v>25182</v>
       </c>
       <c r="E18" t="n">
-        <v>19945</v>
+        <v>19919</v>
       </c>
       <c r="F18" t="n">
-        <v>21965</v>
+        <v>21983</v>
       </c>
       <c r="G18" t="n">
-        <v>26724</v>
+        <v>26723</v>
       </c>
       <c r="H18" t="n">
-        <v>28569</v>
+        <v>28347</v>
       </c>
       <c r="I18" t="n">
-        <v>28953</v>
+        <v>28678</v>
       </c>
       <c r="J18" t="n">
-        <v>29488</v>
+        <v>29215</v>
       </c>
       <c r="K18" t="n">
-        <v>29867</v>
+        <v>29605</v>
       </c>
       <c r="L18" t="n">
-        <v>30140</v>
+        <v>29897</v>
       </c>
       <c r="M18" t="n">
-        <v>30339</v>
+        <v>30120</v>
       </c>
       <c r="N18" t="n">
-        <v>30734</v>
+        <v>30695</v>
       </c>
       <c r="O18" t="n">
-        <v>30710</v>
+        <v>30918</v>
       </c>
       <c r="P18" t="n">
-        <v>30624</v>
+        <v>31134</v>
       </c>
       <c r="Q18" t="n">
-        <v>30705</v>
+        <v>31571</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34784</v>
+        <v>34773</v>
       </c>
       <c r="C19" t="n">
-        <v>311</v>
+        <v>31075</v>
       </c>
       <c r="D19" t="n">
-        <v>25262</v>
+        <v>25219</v>
       </c>
       <c r="E19" t="n">
-        <v>19982</v>
+        <v>19945</v>
       </c>
       <c r="F19" t="n">
-        <v>21950</v>
+        <v>21965</v>
       </c>
       <c r="G19" t="n">
-        <v>26649</v>
+        <v>26724</v>
       </c>
       <c r="H19" t="n">
-        <v>28459</v>
+        <v>28569</v>
       </c>
       <c r="I19" t="n">
-        <v>28808</v>
+        <v>28953</v>
       </c>
       <c r="J19" t="n">
-        <v>29311</v>
+        <v>29488</v>
       </c>
       <c r="K19" t="n">
-        <v>29663</v>
+        <v>29867</v>
       </c>
       <c r="L19" t="n">
-        <v>29912</v>
+        <v>30140</v>
       </c>
       <c r="M19" t="n">
-        <v>30088</v>
+        <v>30339</v>
       </c>
       <c r="N19" t="n">
-        <v>30387</v>
+        <v>30734</v>
       </c>
       <c r="O19" t="n">
-        <v>30270</v>
+        <v>30710</v>
       </c>
       <c r="P19" t="n">
-        <v>30086</v>
+        <v>30624</v>
       </c>
       <c r="Q19" t="n">
-        <v>30056</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33649</v>
+        <v>34784</v>
       </c>
       <c r="C20" t="n">
-        <v>30251</v>
+        <v>311</v>
       </c>
       <c r="D20" t="n">
-        <v>24879</v>
+        <v>25262</v>
       </c>
       <c r="E20" t="n">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="F20" t="n">
-        <v>22051</v>
+        <v>21950</v>
       </c>
       <c r="G20" t="n">
-        <v>26533</v>
+        <v>26649</v>
       </c>
       <c r="H20" t="n">
-        <v>28229</v>
+        <v>28459</v>
       </c>
       <c r="I20" t="n">
-        <v>28588</v>
+        <v>28808</v>
       </c>
       <c r="J20" t="n">
-        <v>29094</v>
+        <v>29311</v>
       </c>
       <c r="K20" t="n">
-        <v>29451</v>
+        <v>29663</v>
       </c>
       <c r="L20" t="n">
-        <v>29706</v>
+        <v>29912</v>
       </c>
       <c r="M20" t="n">
-        <v>29891</v>
+        <v>30088</v>
       </c>
       <c r="N20" t="n">
-        <v>30246</v>
+        <v>30387</v>
       </c>
       <c r="O20" t="n">
-        <v>30205</v>
+        <v>30270</v>
       </c>
       <c r="P20" t="n">
-        <v>30111</v>
+        <v>30086</v>
       </c>
       <c r="Q20" t="n">
-        <v>30183</v>
+        <v>30056</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>33649</v>
+      </c>
+      <c r="C21" t="n">
+        <v>30251</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24879</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20089</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22051</v>
+      </c>
+      <c r="G21" t="n">
+        <v>26533</v>
+      </c>
+      <c r="H21" t="n">
+        <v>28229</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28588</v>
+      </c>
+      <c r="J21" t="n">
+        <v>29094</v>
+      </c>
+      <c r="K21" t="n">
+        <v>29451</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29706</v>
+      </c>
+      <c r="M21" t="n">
+        <v>29891</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30246</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30205</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30111</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>30183</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>28/09/2026</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>32290</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>29294</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>24569</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>20409</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>22259</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>26397</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>28116</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>28521</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>29021</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>29374</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>29628</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>29813</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>30181</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>30167</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>30109</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>30222</v>
       </c>
     </row>

--- a/update/historicos/curva_pesos_uyu_ui_temp.xlsx
+++ b/update/historicos/curva_pesos_uyu_ui_temp.xlsx
@@ -510,370 +510,370 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B2" t="n">
-        <v>3.6819</v>
+        <v>3.6919</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2455</v>
+        <v>3.2513</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5528</v>
+        <v>2.5521</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9218</v>
+        <v>1.916</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1427</v>
+        <v>2.1406</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6755</v>
+        <v>2.6774</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8684</v>
+        <v>2.8644</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9099</v>
+        <v>2.9042</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9712</v>
+        <v>2.9657</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0146</v>
+        <v>3.0093</v>
       </c>
       <c r="L2" t="n">
-        <v>3.046</v>
+        <v>3.041</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0689</v>
+        <v>3.0641</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1143</v>
+        <v>3.111</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1101</v>
+        <v>3.1086</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0959</v>
+        <v>3.0966</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.0964</v>
+        <v>3.0995</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B3" t="n">
-        <v>3.652</v>
+        <v>3.6819</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2228</v>
+        <v>3.2455</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5419</v>
+        <v>2.5528</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9234</v>
+        <v>1.9218</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1446</v>
+        <v>2.1427</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6719</v>
+        <v>2.6755</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8609</v>
+        <v>2.8684</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9025</v>
+        <v>2.9099</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9642</v>
+        <v>2.9712</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0081</v>
+        <v>3.0146</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0401</v>
+        <v>3.046</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0637</v>
+        <v>3.0689</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1133</v>
+        <v>3.1143</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1145</v>
+        <v>3.1101</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1067</v>
+        <v>3.0959</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1147</v>
+        <v>3.0964</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="B4" t="n">
-        <v>3.6507</v>
+        <v>3.652</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2242</v>
+        <v>3.2228</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5471</v>
+        <v>2.5419</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9302</v>
+        <v>1.9234</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1463</v>
+        <v>2.1446</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6663</v>
+        <v>2.6719</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8498</v>
+        <v>2.8609</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8879</v>
+        <v>2.9025</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9469</v>
+        <v>2.9642</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9889</v>
+        <v>3.0081</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0194</v>
+        <v>3.0401</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0419</v>
+        <v>3.0637</v>
       </c>
       <c r="N4" t="n">
-        <v>3.0894</v>
+        <v>3.1133</v>
       </c>
       <c r="O4" t="n">
-        <v>3.0911</v>
+        <v>3.1145</v>
       </c>
       <c r="P4" t="n">
-        <v>3.085</v>
+        <v>3.1067</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.0953</v>
+        <v>3.1147</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B5" t="n">
-        <v>3.6486</v>
+        <v>3.6507</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2232</v>
+        <v>3.2242</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5479</v>
+        <v>2.5471</v>
       </c>
       <c r="E5" t="n">
-        <v>1.932</v>
+        <v>1.9302</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1462</v>
+        <v>2.1463</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6646</v>
+        <v>2.6663</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8506</v>
+        <v>2.8498</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8892</v>
+        <v>2.8879</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9479</v>
+        <v>2.9469</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9897</v>
+        <v>2.9889</v>
       </c>
       <c r="L5" t="n">
-        <v>3.02</v>
+        <v>3.0194</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0422</v>
+        <v>3.0419</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0884</v>
+        <v>3.0894</v>
       </c>
       <c r="O5" t="n">
-        <v>3.0887</v>
+        <v>3.0911</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0811</v>
+        <v>3.085</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.0895</v>
+        <v>3.0953</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B6" t="n">
-        <v>3.601</v>
+        <v>3.6486</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1872</v>
+        <v>3.2232</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5308</v>
+        <v>2.5479</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9347</v>
+        <v>1.932</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1488</v>
+        <v>2.1462</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6608</v>
+        <v>2.6646</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8483</v>
+        <v>2.8506</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8884</v>
+        <v>2.8892</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9472</v>
+        <v>2.9479</v>
       </c>
       <c r="K6" t="n">
-        <v>2.989</v>
+        <v>2.9897</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0194</v>
+        <v>3.02</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0417</v>
+        <v>3.0422</v>
       </c>
       <c r="N6" t="n">
-        <v>3.0881</v>
+        <v>3.0884</v>
       </c>
       <c r="O6" t="n">
-        <v>3.0886</v>
+        <v>3.0887</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0812</v>
+        <v>3.0811</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.0899</v>
+        <v>3.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B7" t="n">
-        <v>3.5465</v>
+        <v>3.601</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1449</v>
+        <v>3.1872</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5086</v>
+        <v>2.5308</v>
       </c>
       <c r="E7" t="n">
         <v>1.9347</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1504</v>
+        <v>2.1488</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6571</v>
+        <v>2.6608</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8454</v>
+        <v>2.8483</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8865</v>
+        <v>2.8884</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9452</v>
+        <v>2.9472</v>
       </c>
       <c r="K7" t="n">
-        <v>2.987</v>
+        <v>2.989</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0172</v>
+        <v>3.0194</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0394</v>
+        <v>3.0417</v>
       </c>
       <c r="N7" t="n">
-        <v>3.0854</v>
+        <v>3.0881</v>
       </c>
       <c r="O7" t="n">
-        <v>3.0854</v>
+        <v>3.0886</v>
       </c>
       <c r="P7" t="n">
-        <v>3.0775</v>
+        <v>3.0812</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.0855</v>
+        <v>3.0899</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B8" t="n">
-        <v>3.4975</v>
+        <v>3.5465</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1024</v>
+        <v>3.1449</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4778</v>
+        <v>2.5086</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9206</v>
+        <v>1.9347</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1453</v>
+        <v>2.1504</v>
       </c>
       <c r="G8" t="n">
         <v>2.6571</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8448</v>
+        <v>2.8454</v>
       </c>
       <c r="I8" t="n">
-        <v>2.886</v>
+        <v>2.8865</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9454</v>
+        <v>2.9452</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9875</v>
+        <v>2.987</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0181</v>
+        <v>3.0172</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0405</v>
+        <v>3.0394</v>
       </c>
       <c r="N8" t="n">
-        <v>3.0868</v>
+        <v>3.0854</v>
       </c>
       <c r="O8" t="n">
-        <v>3.0866</v>
+        <v>3.0854</v>
       </c>
       <c r="P8" t="n">
-        <v>3.0781</v>
+        <v>3.0775</v>
       </c>
       <c r="Q8" t="n">
         <v>3.0855</v>
@@ -881,744 +881,744 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B9" t="n">
-        <v>3.4689</v>
+        <v>3.4975</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0562</v>
+        <v>3.1024</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4072</v>
+        <v>2.4778</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8449</v>
+        <v>1.9206</v>
       </c>
       <c r="F9" t="n">
-        <v>2.112</v>
+        <v>2.1453</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6736</v>
+        <v>2.6571</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8496</v>
+        <v>2.8448</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8842</v>
+        <v>2.886</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9453</v>
+        <v>2.9454</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9887</v>
+        <v>2.9875</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0201</v>
+        <v>3.0181</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0432</v>
+        <v>3.0405</v>
       </c>
       <c r="N9" t="n">
-        <v>3.0905</v>
+        <v>3.0868</v>
       </c>
       <c r="O9" t="n">
-        <v>3.0893</v>
+        <v>3.0866</v>
       </c>
       <c r="P9" t="n">
-        <v>3.0789</v>
+        <v>3.0781</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0837</v>
+        <v>3.0855</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4747</v>
+        <v>3.4689</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0605</v>
+        <v>3.0562</v>
       </c>
       <c r="D10" t="n">
-        <v>2.409</v>
+        <v>2.4072</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1132</v>
+        <v>2.112</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6773</v>
+        <v>2.6736</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8531</v>
+        <v>2.8496</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8872</v>
+        <v>2.8842</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9481</v>
+        <v>2.9453</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9913</v>
+        <v>2.9887</v>
       </c>
       <c r="L10" t="n">
-        <v>3.0226</v>
+        <v>3.0201</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0454</v>
+        <v>3.0432</v>
       </c>
       <c r="N10" t="n">
-        <v>3.0916</v>
+        <v>3.0905</v>
       </c>
       <c r="O10" t="n">
-        <v>3.089</v>
+        <v>3.0893</v>
       </c>
       <c r="P10" t="n">
-        <v>3.077</v>
+        <v>3.0789</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.0799</v>
+        <v>3.0837</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B11" t="n">
-        <v>3.4821</v>
+        <v>3.4747</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0657</v>
+        <v>3.0605</v>
       </c>
       <c r="D11" t="n">
-        <v>2.4108</v>
+        <v>2.409</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8438</v>
+        <v>1.8448</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1138</v>
+        <v>2.1132</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6815</v>
+        <v>2.6773</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8582</v>
+        <v>2.8531</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8917</v>
+        <v>2.8872</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9522</v>
+        <v>2.9481</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9951</v>
+        <v>2.9913</v>
       </c>
       <c r="L11" t="n">
-        <v>3.026</v>
+        <v>3.0226</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0485</v>
+        <v>3.0454</v>
       </c>
       <c r="N11" t="n">
-        <v>3.0929</v>
+        <v>3.0916</v>
       </c>
       <c r="O11" t="n">
-        <v>3.0883</v>
+        <v>3.089</v>
       </c>
       <c r="P11" t="n">
-        <v>3.0741</v>
+        <v>3.077</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.0745</v>
+        <v>3.0799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B12" t="n">
-        <v>3.4947</v>
+        <v>3.4821</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0738</v>
+        <v>3.0657</v>
       </c>
       <c r="D12" t="n">
-        <v>2.412</v>
+        <v>2.4108</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8393</v>
+        <v>1.8438</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1128</v>
+        <v>2.1138</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6861</v>
+        <v>2.6815</v>
       </c>
       <c r="H12" t="n">
-        <v>2.86</v>
+        <v>2.8582</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8916</v>
+        <v>2.8917</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9518</v>
+        <v>2.9522</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9943</v>
+        <v>2.9951</v>
       </c>
       <c r="L12" t="n">
-        <v>3.025</v>
+        <v>3.026</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0473</v>
+        <v>3.0485</v>
       </c>
       <c r="N12" t="n">
-        <v>3.0907</v>
+        <v>3.0929</v>
       </c>
       <c r="O12" t="n">
-        <v>3.0854</v>
+        <v>3.0883</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0704</v>
+        <v>3.0741</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.0699</v>
+        <v>3.0745</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B13" t="n">
-        <v>3.5237</v>
+        <v>3.4947</v>
       </c>
       <c r="C13" t="n">
-        <v>3.0955</v>
+        <v>3.0738</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4217</v>
+        <v>2.412</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8365</v>
+        <v>1.8393</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1101</v>
+        <v>2.1128</v>
       </c>
       <c r="G13" t="n">
-        <v>2.688</v>
+        <v>2.6861</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8617</v>
+        <v>2.86</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8917</v>
+        <v>2.8916</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9512</v>
+        <v>2.9518</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9933</v>
+        <v>2.9943</v>
       </c>
       <c r="L13" t="n">
-        <v>3.0235</v>
+        <v>3.025</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0454</v>
+        <v>3.0473</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0875</v>
+        <v>3.0907</v>
       </c>
       <c r="O13" t="n">
-        <v>3.0812</v>
+        <v>3.0854</v>
       </c>
       <c r="P13" t="n">
-        <v>3.0652</v>
+        <v>3.0704</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.0638</v>
+        <v>3.0699</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B14" t="n">
-        <v>3.5625</v>
+        <v>3.5237</v>
       </c>
       <c r="C14" t="n">
-        <v>3.1161</v>
+        <v>3.0955</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4142</v>
+        <v>2.4217</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8072</v>
+        <v>1.8365</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0971</v>
+        <v>2.1101</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7002</v>
+        <v>2.688</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8655</v>
+        <v>2.8617</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8901</v>
+        <v>2.8917</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9494</v>
+        <v>2.9512</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9911</v>
+        <v>2.9933</v>
       </c>
       <c r="L14" t="n">
-        <v>3.021</v>
+        <v>3.0235</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0427</v>
+        <v>3.0454</v>
       </c>
       <c r="N14" t="n">
-        <v>3.0831</v>
+        <v>3.0875</v>
       </c>
       <c r="O14" t="n">
-        <v>3.0748</v>
+        <v>3.0812</v>
       </c>
       <c r="P14" t="n">
-        <v>3.0566</v>
+        <v>3.0652</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.0526</v>
+        <v>3.0638</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B15" t="n">
-        <v>3.5523</v>
+        <v>3.5625</v>
       </c>
       <c r="C15" t="n">
-        <v>3.112</v>
+        <v>3.1161</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4198</v>
+        <v>2.4142</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8216</v>
+        <v>1.8072</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1083</v>
+        <v>2.0971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.704</v>
+        <v>2.7002</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8653</v>
+        <v>2.8655</v>
       </c>
     